--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-63.29</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>6228071.0</t>
+          <t>18250465.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>5515891.4</t>
+          <t>8602139.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4717976.9</t>
+          <t>5872938.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>4364026.48</t>
+          <t>4689205.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>797914</t>
+          <t>2729201</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-67117.91295227519</t>
+          <t>98866.31487243115</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>47849.72</v>
+        <v>1011779.57</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1182,27 +1182,27 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,195 +1455,195 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7750736.781069363</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC3" t="n">
+        <v>47849.72</v>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>7722335.969609261</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>-42788.19</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-16</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>-9.090993476762565</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
-        <is>
-          <t>-8.401647968798956</t>
-        </is>
-      </c>
-      <c r="BO3" t="inlineStr">
-        <is>
-          <t>-9.81505123066132</t>
-        </is>
-      </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ3" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR3" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,79 +1871,79 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS4" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-287170.2</v>
+        <v>-42788.19</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2044,22 +2044,22 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2069,12 +2069,12 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,67 +2302,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-307741.99</v>
+        <v>-287170.2</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2475,22 +2475,22 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.4</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-66.01</t>
+          <t>-65.83</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2819224.0</t>
+          <t>6873408.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3143736.8</t>
+          <t>3357407.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4432498.0</t>
+          <t>4637970.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>4205877.3</t>
+          <t>4261713.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1288761</t>
+          <t>-1280562</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-16766.15389747573</t>
+          <t>-61531.66789068234</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-597144.59</v>
+        <v>-307741.99</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2906,22 +2906,22 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,7 +2986,7 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
@@ -2996,12 +2996,12 @@
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
+          <t>-16766.15389747573</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-554873.4300000001</v>
+        <v>-597144.59</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3337,37 +3337,37 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>33.524</t>
+          <t>42.907</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-66.65</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2206063.0</t>
+          <t>2801059.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3884078.6</t>
+          <t>3920062.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>6285945.2</t>
+          <t>4619894.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4180675.98</t>
+          <t>4185109.42</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2401866</t>
+          <t>-699832</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>205780.9490764229</t>
+          <t>88757.19878210942</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-472722.89</v>
+        <v>-554873.4300000001</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3768,17 +3768,17 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>31.804</t>
+          <t>33.524</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.51</t>
+          <t>-38.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>62.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-71.20</t>
+          <t>-68.37</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2087283.0</t>
+          <t>2206063.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3748982.2</t>
+          <t>3884078.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6520766.3</t>
+          <t>6285945.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4162974.52</t>
+          <t>4180675.98</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2771784</t>
+          <t>-2401866</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>329145.2834516519</t>
+          <t>205780.9490764229</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-274732.45</v>
+        <v>-472722.89</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4199,27 +4199,27 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>87.858</t>
+          <t>31.804</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.5</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-12.84</t>
+          <t>-42.51</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.24</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.68</t>
+          <t>62.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.34</t>
+          <t>-71.20</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>5805055.0</t>
+          <t>2087283.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>5918533.2</t>
+          <t>3748982.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6790344.8</t>
+          <t>6520766.3</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4136666.06</t>
+          <t>4162974.52</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-871811</t>
+          <t>-2771784</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>438941.2344408286</t>
+          <t>329145.2834516519</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>30649.34</v>
+        <v>-274732.45</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4630,22 +4630,22 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4715,17 +4715,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>65.7</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>66.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>102.971</t>
+          <t>87.858</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-13.54</t>
+          <t>-12.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>62.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>53.80</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>-74.34</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6700852.0</t>
+          <t>5805055.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5721259.2</t>
+          <t>5918533.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6616852.8</t>
+          <t>6790344.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4138922.52</t>
+          <t>4136666.06</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-895593</t>
+          <t>-871811</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>513176.123486937</t>
+          <t>438941.2344408286</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>67481.71000000001</v>
+        <v>30649.34</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5061,22 +5061,22 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.53</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40.558</t>
+          <t>102.971</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>3.0</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-20.58</t>
+          <t>-13.54</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-16 00:00:00</t>
+          <t>2025-11-18 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5298,98 +5298,98 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.27</t>
+          <t>26.07</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.77</t>
+          <t>1.55</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>True</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>5</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>94</t>
+          <t>272</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>38.46</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.07</t>
+          <t>69.96</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.27</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>64.96000000000001</t>
+          <t>65.12</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>63.92</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>63.79</t>
+          <t>63.83</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.51</t>
+          <t>62.6</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>44.63</t>
+          <t>47.84</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.39</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.44</t>
+          <t>-77.79</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7722335.969609261</t>
+          <t>7750736.781069363</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2621140.0</t>
+          <t>6700852.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5319726.8</t>
+          <t>5721259.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6698222.7</t>
+          <t>6616852.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4068798.08</t>
+          <t>4138922.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1378495</t>
+          <t>-895593</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>594211.4707858774</t>
+          <t>513176.123486937</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>21711.07</v>
+        <v>67481.71000000001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-16</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>-0.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5492,22 +5492,22 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>-9.090993476762565</t>
+          <t>-6.762392378742623</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>-8.401647968798956</t>
+          <t>-2.51519879485662</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>-9.81505123066132</t>
+          <t>-8.12262189377373</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.13</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>41.29</t>
+          <t>39.29</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7043</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>1011779.57</v>
+        <v>562855.5</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.68</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-63.29</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>6228071.0</t>
+          <t>18250465.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>5515891.4</t>
+          <t>8602139.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4717976.9</t>
+          <t>5872938.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>4364026.48</t>
+          <t>4689205.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>797914</t>
+          <t>2729201</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-67117.91295227519</t>
+          <t>98866.31487243115</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>47849.72</v>
+        <v>1011779.57</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,12 +1628,12 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1643,7 +1643,7 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,195 +1886,195 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7747356.335497836</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC4" t="n">
+        <v>47849.72</v>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>7750736.781069363</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>-42788.19</v>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI4" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ4" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK4" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BO4" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ4" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,79 +2302,79 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS5" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-287170.2</v>
+        <v>-42788.19</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2490,7 +2490,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,12 +2500,12 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2607,7 +2607,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,67 +2733,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-307741.99</v>
+        <v>-287170.2</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-66.01</t>
+          <t>-65.83</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2819224.0</t>
+          <t>6873408.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3143736.8</t>
+          <t>3357407.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4432498.0</t>
+          <t>4637970.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>4205877.3</t>
+          <t>4261713.24</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1288761</t>
+          <t>-1280562</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-16766.15389747573</t>
+          <t>-61531.66789068234</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-597144.59</v>
+        <v>-307741.99</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
+          <t>-16766.15389747573</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-554873.4300000001</v>
+        <v>-597144.59</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,22 +3783,22 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>33.524</t>
+          <t>42.907</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-66.65</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2206063.0</t>
+          <t>2801059.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3884078.6</t>
+          <t>3920062.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>6285945.2</t>
+          <t>4619894.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4180675.98</t>
+          <t>4185109.42</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2401866</t>
+          <t>-699832</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>205780.9490764229</t>
+          <t>88757.19878210942</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-472722.89</v>
+        <v>-554873.4300000001</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>31.804</t>
+          <t>33.524</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.51</t>
+          <t>-38.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>62.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-71.20</t>
+          <t>-68.37</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2087283.0</t>
+          <t>2206063.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3748982.2</t>
+          <t>3884078.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6520766.3</t>
+          <t>6285945.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4162974.52</t>
+          <t>4180675.98</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2771784</t>
+          <t>-2401866</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>329145.2834516519</t>
+          <t>205780.9490764229</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-274732.45</v>
+        <v>-472722.89</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4660,7 +4660,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>87.858</t>
+          <t>31.804</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-12.84</t>
+          <t>-42.51</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.24</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.68</t>
+          <t>62.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.34</t>
+          <t>-71.20</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5805055.0</t>
+          <t>2087283.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>5918533.2</t>
+          <t>3748982.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6790344.8</t>
+          <t>6520766.3</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4136666.06</t>
+          <t>4162974.52</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-871811</t>
+          <t>-2771784</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>438941.2344408286</t>
+          <t>329145.2834516519</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>30649.34</v>
+        <v>-274732.45</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5146,17 +5146,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>65.7</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>66.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.53</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>102.971</t>
+          <t>87.858</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-13.54</t>
+          <t>-12.84</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-18 00:00:00</t>
+          <t>2025-11-19 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>26.07</t>
+          <t>22.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>1.55</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>272</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>69.96</t>
+          <t>79.49</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>1.41</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.27</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.93</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.12</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>63.83</t>
+          <t>63.9</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.6</t>
+          <t>62.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>47.84</t>
+          <t>53.80</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.36</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-77.79</t>
+          <t>-74.34</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7750736.781069363</t>
+          <t>7747356.335497836</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>6700852.0</t>
+          <t>5805055.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5721259.2</t>
+          <t>5918533.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6616852.8</t>
+          <t>6790344.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4138922.52</t>
+          <t>4136666.06</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-895593</t>
+          <t>-871811</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>513176.123486937</t>
+          <t>438941.2344408286</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>67481.71000000001</v>
+        <v>30649.34</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>6.1</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>12.13</t>
+          <t>11.93</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>39.29</t>
+          <t>38.1</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>7043</t>
+          <t>6927</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>64.6</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,67 +1009,67 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>65.46</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.37</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,45 +1099,45 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>7948536.4</t>
+          <t>7729394.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>4679912.24</t>
+          <t>4624311.5</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>562855.5</v>
+        <v>207756.56</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1207,12 +1207,12 @@
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.68</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,77 +1440,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>1011779.57</v>
+        <v>562855.5</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1673,7 +1673,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-63.29</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>6228071.0</t>
+          <t>18250465.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>5515891.4</t>
+          <t>8602139.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4717976.9</t>
+          <t>5872938.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>4364026.48</t>
+          <t>4689205.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>797914</t>
+          <t>2729201</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-67117.91295227519</t>
+          <t>98866.31487243115</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>47849.72</v>
+        <v>1011779.57</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2059,12 +2059,12 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2074,7 +2074,7 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,195 +2317,195 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>7743213.853746397</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC5" t="n">
+        <v>47849.72</v>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>7747356.335497836</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>-42788.19</v>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2535,7 +2535,7 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,79 +2733,79 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS6" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,45 +2823,45 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-287170.2</v>
+        <v>-42788.19</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2966,7 +2966,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3038,7 +3038,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,67 +3164,67 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-307741.99</v>
+        <v>-287170.2</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3397,7 +3397,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-66.01</t>
+          <t>-65.83</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2819224.0</t>
+          <t>6873408.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3143736.8</t>
+          <t>3357407.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4432498.0</t>
+          <t>4637970.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4205877.3</t>
+          <t>4261713.24</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1288761</t>
+          <t>-1280562</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-16766.15389747573</t>
+          <t>-61531.66789068234</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-597144.59</v>
+        <v>-307741.99</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3828,7 +3828,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
@@ -3858,12 +3858,12 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
+          <t>-16766.15389747573</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-554873.4300000001</v>
+        <v>-597144.59</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>33.524</t>
+          <t>42.907</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-66.65</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2206063.0</t>
+          <t>2801059.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3884078.6</t>
+          <t>3920062.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>6285945.2</t>
+          <t>4619894.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4180675.98</t>
+          <t>4185109.42</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2401866</t>
+          <t>-699832</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>205780.9490764229</t>
+          <t>88757.19878210942</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-472722.89</v>
+        <v>-554873.4300000001</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>31.804</t>
+          <t>33.524</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,102 +4782,102 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-38.21</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>8.49</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
           <t>-0.15</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-42.51</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2025-11-05</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>8.05</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>62.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-71.20</t>
+          <t>-68.37</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2087283.0</t>
+          <t>2206063.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3748982.2</t>
+          <t>3884078.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6520766.3</t>
+          <t>6285945.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4162974.52</t>
+          <t>4180675.98</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2771784</t>
+          <t>-2401866</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>329145.2834516519</t>
+          <t>205780.9490764229</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-274732.45</v>
+        <v>-472722.89</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5091,7 +5091,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5121,7 +5121,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>87.858</t>
+          <t>31.804</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-12.84</t>
+          <t>-42.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-19 00:00:00</t>
+          <t>2025-11-20 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>22.24</t>
+          <t>8.05</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>55</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>73.68</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>79.49</t>
+          <t>91.23</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.41</t>
+          <t>0.43</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.93</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.42</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.24</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>63.9</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.68</t>
+          <t>62.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>53.80</t>
+          <t>43.58</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.40</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.34</t>
+          <t>-71.20</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7747356.335497836</t>
+          <t>7743213.853746397</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5805055.0</t>
+          <t>2087283.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>5918533.2</t>
+          <t>3748982.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6790344.8</t>
+          <t>6520766.3</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4136666.06</t>
+          <t>4162974.52</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-871811</t>
+          <t>-2771784</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>438941.2344408286</t>
+          <t>329145.2834516519</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>30649.34</v>
+        <v>-274732.45</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.1</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>11.93</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5552,7 +5552,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6927</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5577,17 +5577,17 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
           <t>65.7</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>66.2</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +913,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -973,7 +973,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,147 +1014,147 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>65.55</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7737822.699280576</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>6799297.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>4629531.48</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC2" t="n">
+        <v>-89812.24000000001</v>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>65.46</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>64.37</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7743213.853746397</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>7729394.2</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>4624311.5</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>207756.56</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,7 +1197,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1212,7 +1212,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1445,62 +1445,62 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>65.46</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.37</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,45 +1530,45 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>7948536.4</t>
+          <t>7729394.2</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>4679912.24</t>
+          <t>4624311.5</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>562855.5</v>
+        <v>207756.56</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,7 +1628,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1638,12 +1638,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CD3" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,7 +1765,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1775,7 +1775,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1795,7 +1795,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1835,7 +1835,7 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1876,72 +1876,72 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,45 +1961,45 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>1011779.57</v>
+        <v>562855.5</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,7 +2196,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2307,7 +2307,7 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-63.29</t>
+          <t>-61.41</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,45 +2392,45 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>6228071.0</t>
+          <t>18250465.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>5515891.4</t>
+          <t>8602139.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4717976.9</t>
+          <t>5872938.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>4364026.48</t>
+          <t>4689205.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>797914</t>
+          <t>2729201</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-67117.91295227519</t>
+          <t>98866.31487243115</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>47849.72</v>
+        <v>1011779.57</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,12 +2490,12 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2505,7 +2505,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2627,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2657,7 +2657,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2697,7 +2697,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,195 +2748,195 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7737822.699280576</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC6" t="n">
+        <v>47849.72</v>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>7743213.853746397</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>-42788.19</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3128,7 +3128,7 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3169,74 +3169,74 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS7" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,45 +3254,45 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-287170.2</v>
+        <v>-42788.19</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,12 +3362,12 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3469,7 +3469,7 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3489,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3499,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3519,7 +3519,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3559,7 +3559,7 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3600,62 +3600,62 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,45 +3685,45 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-307741.99</v>
+        <v>-287170.2</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3920,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3930,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -3990,7 +3990,7 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4031,72 +4031,72 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.49</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-66.01</t>
+          <t>-65.83</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,45 +4116,45 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2819224.0</t>
+          <t>6873408.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3143736.8</t>
+          <t>3357407.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4432498.0</t>
+          <t>4637970.3</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4205877.3</t>
+          <t>4261713.24</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1288761</t>
+          <t>-1280562</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-16766.15389747573</t>
+          <t>-61531.66789068234</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-597144.59</v>
+        <v>-307741.99</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,7 +4279,7 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
@@ -4289,12 +4289,12 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4361,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4421,7 +4421,7 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4462,72 +4462,72 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,45 +4547,45 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
+          <t>-16766.15389747573</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-554873.4300000001</v>
+        <v>-597144.59</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>33.524</t>
+          <t>42.907</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4792,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4852,7 +4852,7 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4893,72 +4893,72 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-66.65</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,45 +4978,45 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2206063.0</t>
+          <t>2801059.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3884078.6</t>
+          <t>3920062.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6285945.2</t>
+          <t>4619894.6</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4180675.98</t>
+          <t>4185109.42</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2401866</t>
+          <t>-699832</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>205780.9490764229</t>
+          <t>88757.19878210942</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>-472722.89</v>
+        <v>-554873.4300000001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>31.804</t>
+          <t>33.524</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5213,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.51</t>
+          <t>-38.21</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5243,7 +5243,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-11-20 00:00:00</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.05</t>
+          <t>8.49</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5324,72 +5324,72 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>73.68</t>
+          <t>75.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>91.23</t>
+          <t>82.89</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.43</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.90</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.42</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.24</t>
+          <t>64.35</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.77</t>
+          <t>62.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>43.58</t>
+          <t>35.73</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.58</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.40</t>
+          <t>0.44</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-71.20</t>
+          <t>-68.37</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,45 +5409,45 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7743213.853746397</t>
+          <t>7737822.699280576</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2087283.0</t>
+          <t>2206063.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3748982.2</t>
+          <t>3884078.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6520766.3</t>
+          <t>6285945.2</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4162974.52</t>
+          <t>4180675.98</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2771784</t>
+          <t>-2401866</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>329145.2834516519</t>
+          <t>205780.9490764229</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>-274732.45</v>
+        <v>-472722.89</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.05</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>12.02</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>38.1</t>
+          <t>38.93</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6980</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>66.1</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CI12"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -701,165 +701,170 @@
       </c>
       <c r="BC1" s="1" t="inlineStr">
         <is>
-          <t>Volume_Price_Change_sum</t>
+          <t>VPC_MACD</t>
         </is>
       </c>
       <c r="BD1" s="1" t="inlineStr">
         <is>
+          <t>Volume_Price_Change</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -878,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -953,7 +958,7 @@
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
@@ -973,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,72 +1014,72 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>65.55</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1089,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,198 +1104,203 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>6799297.0</t>
+          <t>6067262.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>4629531.48</t>
+          <t>4635115.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
-        </is>
-      </c>
-      <c r="BC2" t="n">
-        <v>-89812.24000000001</v>
-      </c>
-      <c r="BD2" t="inlineStr">
+          <t>67705.00222436106</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-303090.7388503868</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>2567899</v>
+      </c>
+      <c r="BE2" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>1.69</t>
-        </is>
-      </c>
       <c r="BH2" t="inlineStr">
         <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BJ2" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BL2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM2" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV2" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1309,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1344,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1384,7 +1394,7 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
@@ -1404,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,288 +1450,293 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>65.55</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7732239.403017242</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>6799297.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>4629531.48</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>2664241</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>65.46</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>64.37</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>7737822.699280576</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>7729394.2</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>4624311.5</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC3" t="n">
-        <v>207756.56</v>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BJ3" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BL3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM3" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ3" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
       <c r="BT3" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV3" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1740,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,84 +1780,84 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>33.98</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>40.61</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>2.34</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>1.10</t>
@@ -1850,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,67 +1886,67 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>65.46</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.37</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1951,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,198 +1976,203 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>7948536.4</t>
+          <t>7729394.2</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>4679912.24</t>
+          <t>4624311.5</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
-        </is>
-      </c>
-      <c r="BC4" t="n">
-        <v>562855.5</v>
-      </c>
-      <c r="BD4" t="inlineStr">
+          <t>176019.6183496227</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>207756.5576164974</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>3248316</v>
+      </c>
+      <c r="BE4" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
       <c r="BH4" t="inlineStr">
         <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BJ4" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BL4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM4" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
-        </is>
-      </c>
       <c r="BQ4" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV4" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2171,127 +2191,127 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>54.821</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>271.696</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>63.6</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>63.4</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1.10</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13.88</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
         <is>
           <t>-0.91</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>63.6</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>63.4</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>4.06</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>1.10</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>68.78</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>-1.50</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,175 +2412,175 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
-        </is>
-      </c>
-      <c r="BC5" t="n">
-        <v>1011779.57</v>
-      </c>
-      <c r="BD5" t="inlineStr">
+          <t>170249.2657556455</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>562855.4956133245</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>3605392</v>
+      </c>
+      <c r="BE5" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
       <c r="BH5" t="inlineStr">
         <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BJ5" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BL5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM5" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV5" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2570,20 +2590,25 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2602,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2637,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2677,7 +2702,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -2697,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,273 +2773,278 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7732239.403017242</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>8602139.6</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>4689205.28</t>
+        </is>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD6" t="n">
+        <v>18250465</v>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-63.29</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>7737822.699280576</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>5515891.4</t>
-        </is>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>4717976.9</t>
-        </is>
-      </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>4364026.48</t>
-        </is>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>797914</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-67117.91295227519</t>
-        </is>
-      </c>
-      <c r="BC6" t="n">
-        <v>47849.72</v>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
       <c r="BT6" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV6" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3033,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3138,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3128,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,273 +3209,278 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7732239.403017242</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>47849.72233300749</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>6228071</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>7737822.699280576</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC7" t="n">
-        <v>-42788.19</v>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
       <c r="BT7" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV7" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3464,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3499,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3539,7 +3574,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3559,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,79 +3630,79 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS8" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -3675,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,172 +3720,172 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
-        </is>
-      </c>
-      <c r="BC8" t="n">
-        <v>-287170.2</v>
-      </c>
-      <c r="BD8" t="inlineStr">
+          <t>-88021.11936778114</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-42788.19000075478</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>7314727</v>
+      </c>
+      <c r="BE8" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>0.92</t>
-        </is>
-      </c>
       <c r="BH8" t="inlineStr">
         <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BJ8" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BL8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM8" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ8" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV8" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
       <c r="CD8" t="inlineStr">
         <is>
           <t>65.6</t>
@@ -3858,7 +3893,7 @@
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
@@ -3868,15 +3903,20 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3900,7 +3940,7 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3930,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3970,7 +4010,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3990,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,67 +4066,67 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4106,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,198 +4156,203 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
-        </is>
-      </c>
-      <c r="BC9" t="n">
-        <v>-307741.99</v>
-      </c>
-      <c r="BD9" t="inlineStr">
+          <t>-96245.2883436041</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-287170.2008346738</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>4344027</v>
+      </c>
+      <c r="BE9" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BJ9" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BL9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM9" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ9" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV9" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4326,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4361,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4401,7 +4446,7 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4421,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,288 +4502,293 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-65.83</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>7732239.403017242</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>6873408.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>3357407.4</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>4637970.3</t>
+        </is>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>4261713.24</t>
+        </is>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-1280562</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-61531.66789068234</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-307741.9948533187</t>
+        </is>
+      </c>
+      <c r="BD10" t="n">
+        <v>6873408</v>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-66.01</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>7737822.699280576</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>2819224.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>3143736.8</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>4432498.0</t>
-        </is>
-      </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>4205877.3</t>
-        </is>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-1288761</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>-16766.15389747573</t>
-        </is>
-      </c>
-      <c r="BC10" t="n">
-        <v>-597144.59</v>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>37.83</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>6.05</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>6980</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>65.3</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>64.8</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4757,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4792,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4832,7 +4882,7 @@
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
@@ -4852,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,198 +5028,203 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
-        </is>
-      </c>
-      <c r="BC11" t="n">
-        <v>-554873.4300000001</v>
-      </c>
-      <c r="BD11" t="inlineStr">
+          <t>-16766.15389747573</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-597144.593635194</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>2819224</v>
+      </c>
+      <c r="BE11" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>0.31</t>
-        </is>
-      </c>
       <c r="BH11" t="inlineStr">
         <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BJ11" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BL11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM11" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
       <c r="BQ11" t="inlineStr">
         <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>1.28</t>
-        </is>
-      </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV11" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5188,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>33.524</t>
+          <t>42.907</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5223,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-38.21</t>
+          <t>-15.15</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5263,7 +5318,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5283,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>8.49</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>39</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>75.0</t>
+          <t>37.5</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>82.89</t>
+          <t>62.06</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.71</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.35</t>
+          <t>64.45</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.0</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.86</t>
+          <t>62.96</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>35.73</t>
+          <t>20.66</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.37</t>
+          <t>-66.65</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,198 +5464,203 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7737822.699280576</t>
+          <t>7732239.403017242</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2206063.0</t>
+          <t>2801059.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3884078.6</t>
+          <t>3920062.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6285945.2</t>
+          <t>4619894.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4180675.98</t>
+          <t>4185109.42</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2401866</t>
+          <t>-699832</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>205780.9490764229</t>
-        </is>
-      </c>
-      <c r="BC12" t="n">
-        <v>-472722.89</v>
-      </c>
-      <c r="BD12" t="inlineStr">
+          <t>88757.19878210942</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-554873.4278366147</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>2801059</v>
+      </c>
+      <c r="BE12" t="inlineStr">
         <is>
           <t>2025-11-21</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>1.23</t>
-        </is>
-      </c>
       <c r="BH12" t="inlineStr">
         <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BJ12" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BL12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BM12" t="inlineStr">
         <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BR12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>1.29</t>
-        </is>
-      </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>6.05</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>12.02</t>
-        </is>
-      </c>
       <c r="BV12" t="inlineStr">
         <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>38.93</t>
-        </is>
-      </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>6980</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>65.9</t>
-        </is>
-      </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
+          <t>65.2</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
+        <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>63.6</t>
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,182 +1014,182 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>64.48</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7732640.304878049</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>3485392.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>4691358.28</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>5341112</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7732239.403017242</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>6067262.6</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>4635115.64</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>2567899</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,72 +1450,72 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.55</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>6799297.0</t>
+          <t>6067262.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>4629531.48</t>
+          <t>4635115.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>2664241</v>
+        <v>2567899</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,157 +1886,157 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>65.55</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7732640.304878049</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>6799297.0</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>4629531.48</t>
+        </is>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD4" t="n">
+        <v>2664241</v>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>65.46</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>64.37</t>
-        </is>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>7732239.403017242</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>7729394.2</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>4624311.5</t>
-        </is>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD4" t="n">
-        <v>3248316</v>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF4" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG4" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH4" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI4" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2094,7 +2094,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,67 +2322,67 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>65.46</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.37</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>7948536.4</t>
+          <t>7729394.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>4679912.24</t>
+          <t>4624311.5</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>3605392</v>
+        <v>3248316</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2525,12 +2525,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>1011779.567908316</t>
+          <t>562855.4956133245</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>18250465</v>
+        <v>3605392</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.37</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,167 +3209,167 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7732640.304878049</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>8602139.6</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>4689205.28</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD7" t="n">
+        <v>18250465</v>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-63.29</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>7732239.403017242</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>5515891.4</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>4717976.9</t>
-        </is>
-      </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>4364026.48</t>
-        </is>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>797914</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-67117.91295227519</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>47849.72233300749</t>
-        </is>
-      </c>
-      <c r="BD7" t="n">
-        <v>6228071</v>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -3387,12 +3387,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3402,7 +3402,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,7 +3524,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,200 +3645,200 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7732640.304878049</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>47849.72233300749</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>6228071</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>7732239.403017242</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-42788.19000075478</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>7314727</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,79 +4066,79 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS9" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-287170.2008346738</t>
+          <t>-42788.19000075478</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>4344027</v>
+        <v>7314727</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,7 +4259,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4269,12 +4269,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4376,7 +4376,7 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,67 +4502,67 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-307741.9948533187</t>
+          <t>-287170.2008346738</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>6873408</v>
+        <v>4344027</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,267 +4938,267 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-65.83</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>7732640.304878049</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>6873408.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>3357407.4</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>4637970.3</t>
+        </is>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>4261713.24</t>
+        </is>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>-1280562</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-61531.66789068234</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-307741.9948533187</t>
+        </is>
+      </c>
+      <c r="BD11" t="n">
+        <v>6873408</v>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-66.01</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>7732239.403017242</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>2819224.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>3143736.8</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>4432498.0</t>
-        </is>
-      </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>4205877.3</t>
-        </is>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>-1288761</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-16766.15389747573</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>-597144.593635194</t>
-        </is>
-      </c>
-      <c r="BD11" t="n">
-        <v>2819224</v>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX11" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY11" t="inlineStr">
+        <is>
+          <t>37.76</t>
+        </is>
+      </c>
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB11" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO11" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP11" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ11" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR11" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS11" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="BT11" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="BU11" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV11" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="BW11" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX11" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY11" t="inlineStr">
-        <is>
-          <t>37.83</t>
-        </is>
-      </c>
-      <c r="BZ11" t="inlineStr">
-        <is>
-          <t>6938</t>
-        </is>
-      </c>
-      <c r="CA11" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB11" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC11" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD11" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
       <c r="CE11" t="inlineStr">
         <is>
           <t>65.3</t>
@@ -5206,12 +5206,12 @@
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>42.907</t>
+          <t>43.322</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>2.11</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-15.15</t>
+          <t>-29.08</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>1.40</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>10.97</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>39</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>37.5</t>
+          <t>25.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>62.06</t>
+          <t>45.83</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.71</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.58</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.45</t>
+          <t>64.54</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.07</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>62.96</t>
+          <t>63.06</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>20.66</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-66.65</t>
+          <t>-66.01</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7732239.403017242</t>
+          <t>7732640.304878049</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2801059.0</t>
+          <t>2819224.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>3920062.4</t>
+          <t>3143736.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>4619894.6</t>
+          <t>4432498.0</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>4185109.42</t>
+          <t>4205877.3</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-699832</t>
+          <t>-1288761</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>88757.19878210942</t>
+          <t>-16766.15389747573</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-554873.4278366147</t>
+          <t>-597144.593635194</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>2801059</v>
+        <v>2819224</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.27</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>37.83</t>
+          <t>37.76</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>64.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>65.2</t>
+          <t>65.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,280 +1014,280 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>64.55</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>3298712.0</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>4598588.42</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD2" t="n">
+        <v>2671992</v>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>12.09</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>38.64</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>64.48</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>3485392.0</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>4691358.28</t>
-        </is>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD2" t="n">
-        <v>5341112</v>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO2" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP2" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX2" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY2" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
-      </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>7012</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB2" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,74 +1334,74 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-08-25 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-08-25 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
       <c r="T3" t="inlineStr">
         <is>
           <t>63.6</t>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,182 +1450,182 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>65.62</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>64.43</t>
+          <t>64.48</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>3485392.0</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>4691358.28</t>
+        </is>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD3" t="n">
+        <v>5341112</v>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR3" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>6067262.6</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>4635115.64</t>
-        </is>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD3" t="n">
-        <v>2567899</v>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -1643,17 +1643,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,7 +1780,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1790,7 +1790,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1850,12 +1850,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,72 +1886,72 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>65.55</t>
+          <t>65.62</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.43</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7732640.304878049</t>
+          <t>7727304.126790831</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>6799297.0</t>
+          <t>6067262.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>4629531.48</t>
+          <t>4635115.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>2664241</v>
+        <v>2567899</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,7 +2216,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2226,7 +2226,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2286,12 +2286,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,157 +2322,157 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>65.55</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>6799297.0</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>4629531.48</t>
+        </is>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD5" t="n">
+        <v>2664241</v>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>65.46</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>64.37</t>
-        </is>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>7729394.2</t>
-        </is>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>4624311.5</t>
-        </is>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD5" t="n">
-        <v>3248316</v>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI5" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2662,7 +2662,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2722,12 +2722,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,67 +2758,67 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>65.35</t>
+          <t>65.46</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>64.34</t>
+          <t>64.37</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7732640.304878049</t>
+          <t>7727304.126790831</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>7948536.4</t>
+          <t>7729394.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>4679912.24</t>
+          <t>4624311.5</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>3605392</v>
+        <v>3248316</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3098,7 +3098,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>46.47</t>
+          <t>40.61</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,77 +3194,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>65.28</t>
+          <t>65.35</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>64.3</t>
+          <t>64.34</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7732640.304878049</t>
+          <t>7727304.126790831</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>8602139.6</t>
+          <t>7948536.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>4689205.28</t>
+          <t>4679912.24</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>1011779.567908316</t>
+          <t>562855.4956133245</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>18250465</v>
+        <v>3605392</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3534,7 +3534,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.91</t>
+          <t>46.47</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,167 +3645,167 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>65.15</t>
+          <t>65.28</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>64.23</t>
+          <t>64.3</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>8602139.6</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>4689205.28</t>
+        </is>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD8" t="n">
+        <v>18250465</v>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-63.29</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>5515891.4</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>4717976.9</t>
-        </is>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>4364026.48</t>
-        </is>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>797914</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>-67117.91295227519</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>47849.72233300749</t>
-        </is>
-      </c>
-      <c r="BD8" t="n">
-        <v>6228071</v>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,7 +3960,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4030,12 +4030,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,197 +4081,197 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>65.15</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>64.23</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>5515891.4</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>4364026.48</t>
+        </is>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>47849.72233300749</t>
+        </is>
+      </c>
+      <c r="BD9" t="n">
+        <v>6228071</v>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>65.02</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>64.17</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>4830489.0</t>
-        </is>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>4334160.7</t>
-        </is>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-42788.19000075478</t>
-        </is>
-      </c>
-      <c r="BD9" t="n">
-        <v>7314727</v>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BT9" t="inlineStr">
         <is>
           <t>6.02</t>
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>66.455</t>
+          <t>110.599</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,7 +4396,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.79</t>
+          <t>10.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4466,12 +4466,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16.82</t>
+          <t>28.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,79 +4502,79 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>62.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>43.75</t>
+          <t>68.75</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.86</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>65.38000000000001</t>
+          <t>65.47999999999999</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>64.82</t>
+          <t>65.02</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>64.13</t>
+          <t>64.17</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.22</t>
+          <t>63.3</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>9.79</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
           <t>0.49</t>
         </is>
       </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
       <c r="AS10" t="inlineStr">
         <is>
           <t>1.39</t>
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-65.66</t>
+          <t>-64.80</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7732640.304878049</t>
+          <t>7727304.126790831</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>4344027.0</t>
+          <t>7314727.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>3808756.2</t>
+          <t>4830489.0</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>3778869.2</t>
+          <t>4357283.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>4237654.6</t>
+          <t>4334160.7</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>29887</t>
+          <t>473205</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-96245.2883436041</t>
+          <t>-88021.11936778114</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-287170.2008346738</t>
+          <t>-42788.19000075478</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>4344027</v>
+        <v>7314727</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4812,7 +4812,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>105.944</t>
+          <t>66.455</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,7 +4832,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4842,7 +4842,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-27.61</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4902,12 +4902,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>26.82</t>
+          <t>16.82</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,67 +4938,67 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
+          <t>62.5</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
           <t>43.75</t>
         </is>
       </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>35.42</t>
-        </is>
-      </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.34</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.13</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.4</t>
+          <t>65.38000000000001</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>64.67</t>
+          <t>64.82</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>64.1</t>
+          <t>64.13</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.14</t>
+          <t>63.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-65.83</t>
+          <t>-65.66</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7732640.304878049</t>
+          <t>7727304.126790831</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>6873408.0</t>
+          <t>4344027.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>3357407.4</t>
+          <t>3808756.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>4637970.3</t>
+          <t>3778869.2</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>4261713.24</t>
+          <t>4237654.6</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1280562</t>
+          <t>29887</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61531.66789068234</t>
+          <t>-96245.2883436041</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-307741.9948533187</t>
+          <t>-287170.2008346738</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>6873408</v>
+        <v>4344027</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>12.09</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>37.76</t>
+          <t>38.64</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>7022</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>65.3</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>65.3</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>65.3</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>43.322</t>
+          <t>105.944</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,7 +5268,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>2.11</t>
+          <t>1.8</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5278,7 +5278,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-29.08</t>
+          <t>-27.61</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5338,12 +5338,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>1.40</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.97</t>
+          <t>26.82</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,267 +5374,267 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>81</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>25.0</t>
+          <t>43.75</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>45.83</t>
+          <t>35.42</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>1.13</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.58</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>64.54</t>
+          <t>64.67</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>64.07</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.06</t>
+          <t>63.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-65.83</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/10/20</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7727304.126790831</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>6873408.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>3357407.4</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>4637970.3</t>
+        </is>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>4261713.24</t>
+        </is>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>-1280562</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-61531.66789068234</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-307741.9948533187</t>
+        </is>
+      </c>
+      <c r="BD12" t="n">
+        <v>6873408</v>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-66.01</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/10/20</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>7732640.304878049</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>2819224.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>3143736.8</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>4432498.0</t>
-        </is>
-      </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>4205877.3</t>
-        </is>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>-1288761</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-16766.15389747573</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-597144.593635194</t>
-        </is>
-      </c>
-      <c r="BD12" t="n">
-        <v>2819224</v>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>12.09</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>38.64</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>7022</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.27</t>
-        </is>
-      </c>
-      <c r="BT12" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="BU12" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV12" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="BW12" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX12" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY12" t="inlineStr">
-        <is>
-          <t>37.76</t>
-        </is>
-      </c>
-      <c r="BZ12" t="inlineStr">
-        <is>
-          <t>7012</t>
-        </is>
-      </c>
-      <c r="CA12" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB12" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC12" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD12" t="inlineStr">
-        <is>
-          <t>65.2</t>
-        </is>
-      </c>
       <c r="CE12" t="inlineStr">
         <is>
           <t>65.3</t>
@@ -5642,12 +5642,12 @@
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>64.8</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>65.0</t>
+          <t>65.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -871,11 +871,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A2" t="inlineStr"/>
       <c r="B2" t="inlineStr">
         <is>
           <t>2459</t>
@@ -1057,41 +1053,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AM2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1112,20 +1104,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>0</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>0</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1130,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>0</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ2"/>
+  <dimension ref="A1:CJ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -871,7 +871,11 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr"/>
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
       <c r="B2" t="inlineStr">
         <is>
           <t>2459</t>
@@ -879,77 +883,77 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>42.513</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-33.48</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>40.0</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26 00:00:00</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28 00:00:00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-21 00:00:00</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-21 00:00:00</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
@@ -959,22 +963,22 @@
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>64.1</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -984,27 +988,27 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr"/>
@@ -1015,282 +1019,4582 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>53</t>
+          <t>43</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>0.33</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>0.70</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.85</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>66.38000000000001</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>65.92</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>64.66</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>64.12</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-61.32</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>2836015.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>3388720.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>5094008.9</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4576609.36</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-1705288</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-157046.4899894924</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-476778.2581685148</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>2836015.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG2" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13.40</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>0.31</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>84.85</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>66.28000000000002</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>65.84</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>64.59999999999999</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>64.03</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-61.38</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>3526586.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>3354366</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>5541880.1</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4584363.04</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-2187514</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-98913.4412296701</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-414488.4934931798</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>3526586.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN3" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO3" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP3" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS3" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BT3" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU3" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV3" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW3" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX3" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY3" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ3" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA3" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB3" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC3" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>40.234</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-41.34</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>81.82</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>61.04</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF4" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG4" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH4" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI4" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ4" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK4" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL4" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM4" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN4" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO4" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP4" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS4" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT4" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU4" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV4" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW4" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX4" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY4" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ4" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA4" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB4" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC4" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI4" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>81.351</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>20.60</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>72.73</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>55.33</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>3485392</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4691358.28</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>65.1</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>-0.61</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>39.131</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1.35</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4.76</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>9.91</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>28.57</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>54.62</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>-0.54</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.67</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>1.04</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>66.06</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>65.62</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>64.43000000000001</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>63.77</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-60.85</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2567899.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>6067262.6</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>5791577.0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4635115.64</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>275685</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>67705.00222436106</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-303090.7388503868</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2567899.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>65.9</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>40.248</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>16.93</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>3.12</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>10.19</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>-0.75</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>64.71</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>56.86</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>-0.21</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BJ7" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BL7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>49.503</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>33.98</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3.28</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>12.53</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>70.59</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>68.63</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>-0.12</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.18</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>66.28</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>65.45999999999999</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>64.37</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>63.62</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>4.63</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-60.28</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>3248316.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>7729394.2</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5769075.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4624311.5</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>1960319</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>176019.6183496227</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>207756.5576164974</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>3248316.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>-1.66</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>54.821</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>13.88</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>35.29</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>78.43</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1.23</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1.58</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.26</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>66.16</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>65.34999999999999</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>64.34</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>63.54</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>6.74</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.58</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-60.74</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>3605392.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>7948536.4</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5652971.9</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4679912.24</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>2295564</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>170249.2657556455</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>562855.4956133245</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>3605392.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>0.92</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.29</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>65.4</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>271.696</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>46.47</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>68.78</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>0.91</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>1.54</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>65.28</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>64.3</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>63.47</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>19.48</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.64</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>8602139.6</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4689205.28</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>68.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>93.683</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>16.91</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-11-14</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>23.72</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>5515891.4</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4364026.48</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>47849.72233300749</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN11" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO11" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP11" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BS11" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="BT11" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU11" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
-        <is>
-          <t>12.13</t>
-        </is>
-      </c>
-      <c r="BW2" t="inlineStr">
+      <c r="BV11" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW11" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>39.43</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
-        <is>
-          <t>7043</t>
-        </is>
-      </c>
-      <c r="CA2" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA11" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
-        <is>
-          <t>其他電子業右下上市</t>
-        </is>
-      </c>
-      <c r="CD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CC11" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD11" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CH11" t="inlineStr">
+        <is>
+          <t>51.01</t>
+        </is>
+      </c>
+      <c r="CI11" t="inlineStr">
+        <is>
+          <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
+        </is>
+      </c>
+      <c r="CJ11" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>【b】</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2459</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>110.599</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CG2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH2" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>10.86</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-11-13</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>28.00</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>68.75</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1.25</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>65.47999999999999</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>65.02</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.17</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>63.3</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>9.79</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-64.80</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7718860.26</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>7314727.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>4830489</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>4357283.8</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4334160.7</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>473205</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-88021.11936778114</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-42788.19000075478</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>7314727.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT12" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU12" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV12" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW12" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX12" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY12" t="inlineStr">
+        <is>
+          <t>39.43</t>
+        </is>
+      </c>
+      <c r="BZ12" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA12" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB12" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC12" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD12" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CH12" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,107 +883,107 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,48 +1029,48 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1266,17 +1266,17 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,94 +1328,94 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
         <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
+      <c r="W3" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,63 +1444,63 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,12 +1631,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1671,7 +1671,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG3" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,109 +1743,109 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2101,7 +2101,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2198,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2248,32 +2248,32 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,274 +2304,274 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>81.82</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>61.04</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>0.48</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>0.65</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>7711886.537803138</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>72.73</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>55.33</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG5" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH5" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ5" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK5" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL5" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN5" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO5" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP5" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS5" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT5" t="inlineStr">
+        <is>
+          <t>6.01</t>
+        </is>
+      </c>
+      <c r="BU5" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV5" t="inlineStr">
+        <is>
+          <t>12.11</t>
+        </is>
+      </c>
+      <c r="BW5" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX5" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY5" t="inlineStr">
+        <is>
+          <t>39.75</t>
+        </is>
+      </c>
+      <c r="BZ5" t="inlineStr">
+        <is>
+          <t>7033</t>
+        </is>
+      </c>
+      <c r="CA5" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB5" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC5" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM5" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>7718860.26</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF5" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG5" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH5" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI5" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ5" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK5" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL5" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO5" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP5" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ5" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR5" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS5" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT5" t="inlineStr">
-        <is>
-          <t>6.01</t>
-        </is>
-      </c>
-      <c r="BU5" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV5" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="BW5" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX5" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY5" t="inlineStr">
-        <is>
-          <t>39.43</t>
-        </is>
-      </c>
-      <c r="BZ5" t="inlineStr">
-        <is>
-          <t>7033</t>
-        </is>
-      </c>
-      <c r="CA5" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB5" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC5" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD5" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,92 +2618,92 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,176 +2734,176 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>72.73</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>55.33</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>0.46</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>65.7</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>64.48</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>63.86</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7711886.537803138</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>3485392</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4691358.28</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>28.57</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>54.62</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>1.04</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>66.06</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>65.62</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>64.43000000000001</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>63.77</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
         <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>7718860.26</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>6067262.6</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4635115.64</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN6" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2961,7 +2961,7 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,7 +3058,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3068,7 +3068,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3108,7 +3108,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -3128,12 +3128,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,151 +3594,151 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7711886.537803138</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM8" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>7718860.26</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>7729394.2</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4624311.5</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI8" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -3781,7 +3781,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3968,7 +3968,7 @@
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,63 +4024,63 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.34999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.34</v>
+        <v>64.37</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>7948536.4</v>
+        <v>7729394.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4679912.24</v>
+        <v>4624311.5</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4221,7 +4221,7 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,67 +4338,67 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1.5</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.28</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.3</v>
+        <v>64.34</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7718860.26</t>
+          <t>7711886.537803138</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>8602139.6</v>
+        <v>7948536.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4689205.28</v>
+        <v>4679912.24</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>1011779.567908316</t>
+          <t>562855.4956133245</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4681,7 +4681,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,69 +4768,69 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>46.47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="S11" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,161 +4899,161 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.15000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.23</v>
+        <v>64.3</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>7711886.537803138</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>8602139.6</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4689205.28</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ11" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK11" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL11" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM11" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-63.29</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>7718860.26</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>5515891.4</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>4717976.9</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4364026.48</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>797914</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>-67117.91295227519</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>47849.72233300749</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BI11" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ11" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK11" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL11" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN11" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>110.599</t>
+          <t>93.683</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>10.86</t>
+          <t>16.91</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>28.00</t>
+          <t>23.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>43</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,191 +5329,191 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.75</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>1.43</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>65.76</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>65.15000000000001</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.23</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>63.38</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>16.53</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.60</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-63.29</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7711886.537803138</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>5515891.4</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>4717976.9</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4364026.48</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>797914</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>-67117.91295227519</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>47849.72233300749</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6228071.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN12" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO12" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP12" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS12" t="inlineStr">
+        <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>65.47999999999999</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>65.02</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>64.17</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>63.3</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>9.79</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-64.80</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>7718860.26</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>4830489</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>4357283.8</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4334160.7</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>473205</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-88021.11936778114</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>-42788.19000075478</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>7314727.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2.00</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO12" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP12" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ12" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
-        </is>
-      </c>
-      <c r="BR12" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS12" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
       <c r="BT12" t="inlineStr">
         <is>
           <t>6.01</t>
@@ -5541,7 +5541,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.43</t>
+          <t>39.75</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>66.9</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>65.8</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>66.3</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,89 +883,89 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -978,12 +978,12 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,14 +1266,14 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF2" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,104 +1313,104 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,48 +1459,48 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1646,7 +1646,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,17 +1696,17 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,94 +1758,94 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
         <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
+      <c r="W4" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X4" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,63 +1874,63 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF4" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG4" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,109 +2173,109 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,68 +2304,68 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,7 +2628,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2638,7 +2638,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,274 +2734,274 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7703922.44017094</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF6" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG6" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH6" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ6" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK6" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL6" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM6" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN6" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO6" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP6" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS6" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT6" t="inlineStr">
+        <is>
+          <t>6.03</t>
+        </is>
+      </c>
+      <c r="BU6" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV6" t="inlineStr">
+        <is>
+          <t>12.05</t>
+        </is>
+      </c>
+      <c r="BW6" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX6" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY6" t="inlineStr">
+        <is>
+          <t>39.32</t>
+        </is>
+      </c>
+      <c r="BZ6" t="inlineStr">
+        <is>
+          <t>7001</t>
+        </is>
+      </c>
+      <c r="CA6" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB6" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC6" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM6" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>7711886.537803138</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF6" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG6" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH6" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ6" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK6" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL6" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO6" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP6" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ6" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR6" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS6" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT6" t="inlineStr">
-        <is>
-          <t>6.01</t>
-        </is>
-      </c>
-      <c r="BU6" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV6" t="inlineStr">
-        <is>
-          <t>12.11</t>
-        </is>
-      </c>
-      <c r="BW6" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX6" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY6" t="inlineStr">
-        <is>
-          <t>39.75</t>
-        </is>
-      </c>
-      <c r="BZ6" t="inlineStr">
-        <is>
-          <t>7033</t>
-        </is>
-      </c>
-      <c r="CA6" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB6" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC6" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD6" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,92 +3048,92 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,176 +3164,176 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7703922.44017094</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>3485392</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4691358.28</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>7711886.537803138</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>6067262.6</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4635115.64</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN7" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3558,12 +3558,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,151 +4024,151 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7703922.44017094</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7711886.537803138</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>7729394.2</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4624311.5</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI9" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -4211,7 +4211,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4226,7 +4226,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1.5</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,63 +4454,63 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.34999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.34</v>
+        <v>64.37</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>7948536.4</v>
+        <v>7729394.2</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4679912.24</v>
+        <v>4624311.5</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,64 +4768,64 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1.06</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>66.6</t>
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.28</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.3</v>
+        <v>64.34</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7711886.537803138</t>
+          <t>7703922.44017094</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>8602139.6</v>
+        <v>7948536.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4689205.28</v>
+        <v>4679912.24</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>1011779.567908316</t>
+          <t>562855.4956133245</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>93.683</t>
+          <t>271.696</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,69 +5198,69 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>46.47</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>16.91</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>23.72</t>
+          <t>68.78</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>21</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,161 +5329,161 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.34</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>65.76</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.15000000000001</v>
+        <v>65.28</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.23</v>
+        <v>64.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.38</t>
+          <t>63.47</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>19.48</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.60</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-61.41</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7703922.44017094</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>8602139.6</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>5872938.2</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4689205.28</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>2729201</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>98866.31487243115</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>1011779.567908316</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>18250465.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="BI12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ12" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK12" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL12" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM12" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-63.29</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>7711886.537803138</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>5515891.4</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>4717976.9</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4364026.48</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>797914</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>-67117.91295227519</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>47849.72233300749</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>6228071.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BI12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ12" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK12" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL12" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN12" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.03</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.05</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.75</t>
+          <t>39.32</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>68.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,68 +1014,68 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,109 +1313,109 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="S3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
         <is>
           <t>-0.45</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
       <c r="X3" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,14 +1696,14 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF3" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -1711,7 +1711,7 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,104 +1743,104 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W4" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,12 +1874,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1889,48 +1889,48 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2076,7 +2076,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,17 +2126,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2173,89 +2173,89 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>42.513</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
           <t>0.3</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>52.918</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -2268,14 +2268,14 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X5" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,63 +2304,63 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF5" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG5" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,34 +2603,34 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
       <c r="I6" t="inlineStr">
         <is>
           <t>0.0</t>
@@ -2638,12 +2638,12 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-41.34</t>
+          <t>-39.47</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -2683,7 +2683,7 @@
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,68 +2734,68 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2820,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,84 +3058,84 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-41.34</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-42.33</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-0.30</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,274 +3164,274 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7703581.655761024</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF7" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG7" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH7" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ7" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK7" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL7" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM7" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN7" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO7" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP7" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS7" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT7" t="inlineStr">
+        <is>
+          <t>5.99</t>
+        </is>
+      </c>
+      <c r="BU7" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV7" t="inlineStr">
+        <is>
+          <t>12.15</t>
+        </is>
+      </c>
+      <c r="BW7" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX7" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY7" t="inlineStr">
+        <is>
+          <t>39.11</t>
+        </is>
+      </c>
+      <c r="BZ7" t="inlineStr">
+        <is>
+          <t>7054</t>
+        </is>
+      </c>
+      <c r="CA7" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB7" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC7" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM7" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>7703922.44017094</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF7" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG7" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH7" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ7" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK7" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL7" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO7" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP7" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ7" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR7" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS7" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT7" t="inlineStr">
-        <is>
-          <t>6.03</t>
-        </is>
-      </c>
-      <c r="BU7" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV7" t="inlineStr">
-        <is>
-          <t>12.05</t>
-        </is>
-      </c>
-      <c r="BW7" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX7" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY7" t="inlineStr">
-        <is>
-          <t>39.32</t>
-        </is>
-      </c>
-      <c r="BZ7" t="inlineStr">
-        <is>
-          <t>7001</t>
-        </is>
-      </c>
-      <c r="CA7" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB7" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC7" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD7" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,92 +3478,92 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>0.9</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,176 +3594,176 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7703581.655761024</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>3485392</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4691358.28</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>7703922.44017094</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>6067262.6</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4635115.64</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN8" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,7 +3918,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3928,7 +3928,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,68 +4024,68 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4348,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,151 +4454,151 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>7703581.655761024</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM10" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>7703922.44017094</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>7729394.2</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4624311.5</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI10" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,63 +4884,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.34999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.34</v>
+        <v>64.37</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>7948536.4</v>
+        <v>7729394.2</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4679912.24</v>
+        <v>4624311.5</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>271.696</t>
+          <t>54.821</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,64 +5198,64 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>1.8</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>40.61</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-10-21</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>46.47</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>66.6</t>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>68.78</t>
+          <t>13.88</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>21</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>35.29</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>78.43</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.26</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.16</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.28</v>
+        <v>65.34999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.3</v>
+        <v>64.34</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.47</t>
+          <t>63.54</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>19.48</t>
+          <t>6.74</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.58</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.41</t>
+          <t>-60.74</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7703922.44017094</t>
+          <t>7703581.655761024</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>8602139.6</v>
+        <v>7948536.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5872938.2</t>
+          <t>5652971.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4689205.28</v>
+        <v>4679912.24</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2729201</t>
+          <t>2295564</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>98866.31487243115</t>
+          <t>170249.2657556455</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>1011779.567908316</t>
+          <t>562855.4956133245</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18250465.0</t>
+          <t>3605392.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.03</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.05</t>
+          <t>12.15</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.32</t>
+          <t>39.11</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>68.0</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.4</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,176 +1014,176 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
+          <t>0.47</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-63.03</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7695838.374289772</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>1501541.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>2522940.8</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2938653.4</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4638644.26</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-415712</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-352265.903679029</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-549764.6346373484</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>1501541.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-62.28</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7703581.655761024</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>4976234.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2927949.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>3113330.9</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4657185.68</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-185381</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-316357.043504789</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-453732.0077251205</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>4976234.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2.77</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1276,12 +1276,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,68 +1444,68 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,89 +1743,89 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T4" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -1838,12 +1838,12 @@
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,48 +1960,48 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
@@ -2071,12 +2071,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,14 +2126,14 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF4" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -2141,7 +2141,7 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,104 +2173,104 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,12 +2304,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2319,48 +2319,48 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2506,7 +2506,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,17 +2556,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,74 +2618,74 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -2698,14 +2698,14 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X6" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,63 +2734,63 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF6" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG6" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,109 +3033,109 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,68 +3164,68 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,48 +3250,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3498,7 +3498,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,274 +3594,274 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM8" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>7695838.374289772</t>
+        </is>
+      </c>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX8" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ8" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA8" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB8" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC8" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF8" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG8" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH8" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ8" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK8" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL8" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM8" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="BN8" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO8" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP8" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS8" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT8" t="inlineStr">
+        <is>
+          <t>6.02</t>
+        </is>
+      </c>
+      <c r="BU8" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV8" t="inlineStr">
+        <is>
+          <t>12.07</t>
+        </is>
+      </c>
+      <c r="BW8" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX8" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY8" t="inlineStr">
+        <is>
+          <t>39.48</t>
+        </is>
+      </c>
+      <c r="BZ8" t="inlineStr">
+        <is>
+          <t>7012</t>
+        </is>
+      </c>
+      <c r="CA8" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB8" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC8" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM8" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN8" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>7703581.655761024</t>
-        </is>
-      </c>
-      <c r="AW8" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX8" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ8" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA8" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB8" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC8" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD8" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF8" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG8" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH8" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ8" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK8" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL8" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO8" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP8" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ8" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR8" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS8" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT8" t="inlineStr">
-        <is>
-          <t>5.99</t>
-        </is>
-      </c>
-      <c r="BU8" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV8" t="inlineStr">
-        <is>
-          <t>12.15</t>
-        </is>
-      </c>
-      <c r="BW8" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX8" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY8" t="inlineStr">
-        <is>
-          <t>39.11</t>
-        </is>
-      </c>
-      <c r="BZ8" t="inlineStr">
-        <is>
-          <t>7054</t>
-        </is>
-      </c>
-      <c r="CA8" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB8" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC8" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD8" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,92 +3908,92 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,176 +4024,176 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-61.26</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7695838.374289772</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>3485392</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>6043765.8</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4691358.28</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-2558373</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>20855.39480073467</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-236817.4460292105</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5341112.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
           <t>0.51</t>
         </is>
       </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-60.85</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7703581.655761024</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>6067262.6</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>5791577.0</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4635115.64</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>275685</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>67705.00222436106</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-303090.7388503868</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>2567899.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>1.08</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN9" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4313,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,68 +4454,68 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,151 +4884,151 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM11" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>7695838.374289772</t>
+        </is>
+      </c>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX11" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ11" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA11" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB11" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC11" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE11" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF11" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG11" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH11" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL11" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM11" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="AN11" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="AO11" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP11" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS11" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>7703581.655761024</t>
-        </is>
-      </c>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX11" t="n">
-        <v>7729394.2</v>
-      </c>
-      <c r="AY11" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ11" t="n">
-        <v>4624311.5</v>
-      </c>
-      <c r="BA11" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB11" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC11" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD11" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="BE11" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF11" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG11" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH11" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI11" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.66</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>54.821</t>
+          <t>49.503</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.8</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>40.61</t>
+          <t>33.98</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>3.28</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.88</t>
+          <t>12.53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>0.92</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,63 +5314,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>35.29</t>
+          <t>70.59</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>78.43</t>
+          <t>68.63</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-0.12</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>1.18</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.16</t>
+          <t>66.28</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.34999999999999</v>
+        <v>65.45999999999999</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.34</v>
+        <v>64.37</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.54</t>
+          <t>63.62</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>6.74</t>
+          <t>4.63</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-60.74</t>
+          <t>-60.28</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7703581.655761024</t>
+          <t>7695838.374289772</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>7948536.4</v>
+        <v>7729394.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5652971.9</t>
+          <t>5769075.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4679912.24</v>
+        <v>4624311.5</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>2295564</t>
+          <t>1960319</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>170249.2657556455</t>
+          <t>176019.6183496227</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>562855.4956133245</t>
+          <t>207756.5576164974</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3605392.0</t>
+          <t>3248316.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.15</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.11</t>
+          <t>39.48</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7054</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>65.6</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>65.5</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>66.2</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>65.4</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>65.6</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,176 +1014,176 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-20.99</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.47</t>
+          <t>0.39</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
+          <t>0.49</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-64.87</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7697434.725531915</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>3131906.6</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>3260313.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4743373.54</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>-128407</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-340347.400437636</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-274795.6326099746</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-63.03</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7695838.374289772</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2522940.8</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>2938653.4</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4638644.26</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-415712</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-352265.903679029</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-549764.6346373484</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF2" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG2" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH2" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ2" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK2" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL2" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
       <c r="BN2" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.47</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1706,12 +1706,12 @@
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1768,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,68 +1874,68 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.36</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.50</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,89 +2173,89 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T5" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -2268,12 +2268,12 @@
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.06</t>
+          <t>-0.36</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.50</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.54</t>
+          <t>0.53</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,48 +2390,48 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
@@ -2501,12 +2501,12 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,14 +2556,14 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF5" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -2571,7 +2571,7 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,104 +2603,104 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-0.3</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W6" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,12 +2734,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2749,48 +2749,48 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.33</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>0.70</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,17 +2986,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,74 +3048,74 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -3128,14 +3128,14 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X7" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,63 +3164,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.33</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,12 +3351,12 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF7" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG7" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3453,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,109 +3463,109 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-1.52</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,68 +3594,68 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>0.65</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.53</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,48 +3680,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,274 +4024,274 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>0.53</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>0.54</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7697434.725531915</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF9" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG9" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH9" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>6.09</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>11.95</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>41.15</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>6938</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB9" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC9" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM9" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7695838.374289772</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF9" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG9" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH9" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>6.02</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>12.07</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>39.48</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>7012</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB9" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC9" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD9" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,92 +4338,92 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.07</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.54</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>0.67</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.54</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-60.85</t>
+          <t>-61.26</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,48 +4540,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>6067262.6</v>
+        <v>3485392</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5791577.0</t>
+          <t>6043765.8</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4635115.64</v>
+        <v>4691358.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>275685</t>
+          <t>-2558373</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>67705.00222436106</t>
+          <t>20855.39480073467</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-303090.7388503868</t>
+          <t>-236817.4460292105</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4743,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,7 +4778,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4848,12 +4848,12 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,68 +4884,68 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>56.86</t>
+          <t>54.62</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.21</t>
+          <t>-0.54</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>0.67</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>1.05</t>
+          <t>-6.86</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.56</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7695838.374289772</t>
+          <t>7697434.725531915</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>49.503</t>
+          <t>40.248</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5208,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5218,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>33.98</t>
+          <t>16.93</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5278,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.28</t>
+          <t>3.12</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>12.53</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.92</t>
+          <t>-0.75</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,151 +5314,151 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>89</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>70.59</t>
+          <t>64.71</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>68.63</t>
+          <t>56.86</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.12</t>
+          <t>-0.21</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>1.11</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM12" t="n">
+        <v>65.55</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>64.40000000000001</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>63.7</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>1.05</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>0.56</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>0.55</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>-60.18</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>7697434.725531915</t>
+        </is>
+      </c>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="AX12" t="n">
+        <v>6799297</v>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>5814893.0</t>
+        </is>
+      </c>
+      <c r="AZ12" t="n">
+        <v>4629531.48</v>
+      </c>
+      <c r="BA12" t="inlineStr">
+        <is>
+          <t>984404</t>
+        </is>
+      </c>
+      <c r="BB12" t="inlineStr">
+        <is>
+          <t>135122.4096924971</t>
+        </is>
+      </c>
+      <c r="BC12" t="inlineStr">
+        <is>
+          <t>-89812.2379216943</t>
+        </is>
+      </c>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>2664241.0</t>
+        </is>
+      </c>
+      <c r="BE12" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="BF12" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG12" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH12" t="inlineStr">
+        <is>
           <t>1.69</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>1.18</t>
-        </is>
-      </c>
-      <c r="AL12" t="inlineStr">
-        <is>
-          <t>66.28</t>
-        </is>
-      </c>
-      <c r="AM12" t="n">
-        <v>65.45999999999999</v>
-      </c>
-      <c r="AN12" t="n">
-        <v>64.37</v>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>63.62</t>
-        </is>
-      </c>
-      <c r="AP12" t="inlineStr">
-        <is>
-          <t>4.63</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.58</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
-      </c>
-      <c r="AS12" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr">
-        <is>
-          <t>-60.28</t>
-        </is>
-      </c>
-      <c r="AU12" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV12" t="inlineStr">
-        <is>
-          <t>7695838.374289772</t>
-        </is>
-      </c>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="AX12" t="n">
-        <v>7729394.2</v>
-      </c>
-      <c r="AY12" t="inlineStr">
-        <is>
-          <t>5769075.2</t>
-        </is>
-      </c>
-      <c r="AZ12" t="n">
-        <v>4624311.5</v>
-      </c>
-      <c r="BA12" t="inlineStr">
-        <is>
-          <t>1960319</t>
-        </is>
-      </c>
-      <c r="BB12" t="inlineStr">
-        <is>
-          <t>176019.6183496227</t>
-        </is>
-      </c>
-      <c r="BC12" t="inlineStr">
-        <is>
-          <t>207756.5576164974</t>
-        </is>
-      </c>
-      <c r="BD12" t="inlineStr">
-        <is>
-          <t>3248316.0</t>
-        </is>
-      </c>
-      <c r="BE12" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="BF12" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG12" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH12" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
       <c r="BI12" t="inlineStr">
         <is>
           <t>敦吉</t>
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.02</t>
+          <t>6.09</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.07</t>
+          <t>11.95</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>39.48</t>
+          <t>41.15</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6938</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,92 +898,92 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="V2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,33 +1014,29 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>-0.99</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.37</t>
-        </is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.13</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
@@ -1049,39 +1045,35 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.24000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.11</v>
+        <v>66.16</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.92</v>
+        <v>64.97</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-20.99</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>0.39</t>
-        </is>
-      </c>
-      <c r="AR2" t="inlineStr">
-        <is>
-          <t>0.49</t>
-        </is>
+          <t>-26.34</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.46</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1090,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-67.04</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3131906.6</v>
+        <v>2948729.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3260313.7</t>
+          <t>3100620.6</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4743373.54</v>
+        <v>4708957.14</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-128407</t>
+          <t>-151891</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-340347.400437636</t>
+          <t>-356245.9758127016</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-274795.6326099746</t>
+          <t>-443688.1403755629</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,12 +1193,12 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1216,7 +1208,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1348,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,176 +1436,168 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>74.55</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>0.64</t>
-        </is>
+          <t>54.55</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.37</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AQ3" t="inlineStr">
-        <is>
-          <t>0.47</t>
-        </is>
-      </c>
-      <c r="AR3" t="inlineStr">
+          <t>-20.99</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-64.87</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7688594.806657224</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>3131906.6</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>3260313.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4743373.54</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-128407</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-340347.400437636</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-274795.6326099746</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF3" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG3" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH3" t="inlineStr">
+        <is>
+          <t>1.08</t>
+        </is>
+      </c>
+      <c r="BI3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ3" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK3" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL3" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM3" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-63.03</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>7697434.725531915</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>2522940.8</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>2938653.4</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4638644.26</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>-415712</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-352265.903679029</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-549764.6346373484</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF3" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG3" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH3" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ3" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK3" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL3" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
       <c r="BN3" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
@@ -1631,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1778,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,74 +1858,66 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>83.64</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>0.30</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>0.78</t>
-        </is>
+          <t>74.55</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.64</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-3.69</t>
-        </is>
-      </c>
-      <c r="AQ4" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AR4" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+          <t>-8.08</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.52</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1950,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,7 +2102,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2136,12 +2112,12 @@
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2208,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,74 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>80.61</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>-0.36</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
+          <t>83.64</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.78</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-5.79</t>
-        </is>
-      </c>
-      <c r="AQ5" t="inlineStr">
-        <is>
-          <t>0.50</t>
-        </is>
-      </c>
-      <c r="AR5" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
+          <t>-3.69</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.53</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2380,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,89 +2571,89 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="S6" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T6" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -2698,12 +2666,12 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,74 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>93.94</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0.06</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
+          <t>80.61</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AQ6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR6" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.53</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2810,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,48 +2780,48 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
@@ -2876,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,7 +2881,7 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
@@ -2931,12 +2891,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,14 +2946,14 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF6" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -3001,7 +2961,7 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3023,7 +2983,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3033,104 +2993,104 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W7" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -3143,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,12 +3124,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3179,59 +3139,51 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>90.91</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>0.33</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>0.70</t>
-        </is>
+          <t>93.94</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.82</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="AQ7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR7" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+          <t>-0.56</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.54</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3240,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3351,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3366,7 +3318,7 @@
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,17 +3368,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3453,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3463,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,74 +3430,74 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.91</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-1.52</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -3558,14 +3510,14 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X8" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3573,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,74 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>84.85</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>0.63</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
+          <t>90.91</t>
+        </is>
+      </c>
+      <c r="AH8" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="AI8" t="n">
+        <v>0.7</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.87</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR8" t="n">
+        <v>0.54</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3670,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,12 +3725,12 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3796,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF8" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG8" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3883,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3893,109 +3837,109 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.06</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4003,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,74 +3968,66 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>61.04</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>0.48</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>0.65</t>
-        </is>
+          <t>84.85</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>0.63</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.67</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-2.08</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.54</v>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
@@ -4100,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,48 +4046,48 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
@@ -4166,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4274,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,7 +4284,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -4358,7 +4294,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4359,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,274 +4390,266 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>55.33</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>0.61</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>0.46</t>
-        </is>
+          <t>61.04</t>
+        </is>
+      </c>
+      <c r="AH10" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="AI10" t="n">
+        <v>0.65</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
+          <t>66.18</t>
+        </is>
+      </c>
+      <c r="AM10" t="n">
+        <v>65.76000000000001</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>64.55</v>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>63.95</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>-2.08</t>
+        </is>
+      </c>
+      <c r="AQ10" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AR10" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>-61.46</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>7688594.806657224</t>
+        </is>
+      </c>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="AX10" t="n">
+        <v>3298712</v>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>5623624.2</t>
+        </is>
+      </c>
+      <c r="AZ10" t="n">
+        <v>4598588.42</v>
+      </c>
+      <c r="BA10" t="inlineStr">
+        <is>
+          <t>-2324912</t>
+        </is>
+      </c>
+      <c r="BB10" t="inlineStr">
+        <is>
+          <t>-41536.15899994106</t>
+        </is>
+      </c>
+      <c r="BC10" t="inlineStr">
+        <is>
+          <t>-384689.7049036575</t>
+        </is>
+      </c>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>2671992.0</t>
+        </is>
+      </c>
+      <c r="BE10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF10" t="inlineStr">
+        <is>
+          <t>65.0</t>
+        </is>
+      </c>
+      <c r="BG10" t="inlineStr">
+        <is>
+          <t>2025/10/29</t>
+        </is>
+      </c>
+      <c r="BH10" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BI10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BJ10" t="inlineStr">
+        <is>
+          <t>敦吉</t>
+        </is>
+      </c>
+      <c r="BK10" t="inlineStr">
+        <is>
+          <t>其他電子業</t>
+        </is>
+      </c>
+      <c r="BL10" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM10" t="inlineStr">
+        <is>
+          <t>0.52</t>
+        </is>
+      </c>
+      <c r="BN10" t="inlineStr">
+        <is>
+          <t>-6.762392378742623</t>
+        </is>
+      </c>
+      <c r="BO10" t="inlineStr">
+        <is>
+          <t>-2.51519879485662</t>
+        </is>
+      </c>
+      <c r="BP10" t="inlineStr">
+        <is>
+          <t>-8.12262189377373</t>
+        </is>
+      </c>
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS10" t="inlineStr">
+        <is>
+          <t>1.30</t>
+        </is>
+      </c>
+      <c r="BT10" t="inlineStr">
+        <is>
+          <t>6.06</t>
+        </is>
+      </c>
+      <c r="BU10" t="inlineStr">
+        <is>
+          <t>11.84</t>
+        </is>
+      </c>
+      <c r="BV10" t="inlineStr">
+        <is>
+          <t>12.0</t>
+        </is>
+      </c>
+      <c r="BW10" t="inlineStr">
+        <is>
+          <t>31.81%</t>
+        </is>
+      </c>
+      <c r="BX10" t="inlineStr">
+        <is>
+          <t>15.81%</t>
+        </is>
+      </c>
+      <c r="BY10" t="inlineStr">
+        <is>
+          <t>42.22</t>
+        </is>
+      </c>
+      <c r="BZ10" t="inlineStr">
+        <is>
+          <t>6969</t>
+        </is>
+      </c>
+      <c r="CA10" t="inlineStr">
+        <is>
+          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB10" t="inlineStr">
+        <is>
+          <t>敦吉-其他電子業-上市</t>
+        </is>
+      </c>
+      <c r="CC10" t="inlineStr">
+        <is>
+          <t>其他電子業平上市</t>
+        </is>
+      </c>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="AM10" t="n">
-        <v>65.7</v>
-      </c>
-      <c r="AN10" t="n">
-        <v>64.48</v>
-      </c>
-      <c r="AO10" t="inlineStr">
-        <is>
-          <t>63.86</t>
-        </is>
-      </c>
-      <c r="AP10" t="inlineStr">
-        <is>
-          <t>-4.25</t>
-        </is>
-      </c>
-      <c r="AQ10" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="AR10" t="inlineStr">
-        <is>
-          <t>0.54</t>
-        </is>
-      </c>
-      <c r="AS10" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr">
-        <is>
-          <t>-61.26</t>
-        </is>
-      </c>
-      <c r="AU10" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV10" t="inlineStr">
-        <is>
-          <t>7697434.725531915</t>
-        </is>
-      </c>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="AX10" t="n">
-        <v>3485392</v>
-      </c>
-      <c r="AY10" t="inlineStr">
-        <is>
-          <t>6043765.8</t>
-        </is>
-      </c>
-      <c r="AZ10" t="n">
-        <v>4691358.28</v>
-      </c>
-      <c r="BA10" t="inlineStr">
-        <is>
-          <t>-2558373</t>
-        </is>
-      </c>
-      <c r="BB10" t="inlineStr">
-        <is>
-          <t>20855.39480073467</t>
-        </is>
-      </c>
-      <c r="BC10" t="inlineStr">
-        <is>
-          <t>-236817.4460292105</t>
-        </is>
-      </c>
-      <c r="BD10" t="inlineStr">
-        <is>
-          <t>5341112.0</t>
-        </is>
-      </c>
-      <c r="BE10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF10" t="inlineStr">
-        <is>
-          <t>65.0</t>
-        </is>
-      </c>
-      <c r="BG10" t="inlineStr">
-        <is>
-          <t>2025/10/29</t>
-        </is>
-      </c>
-      <c r="BH10" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
-      </c>
-      <c r="BI10" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BJ10" t="inlineStr">
-        <is>
-          <t>敦吉</t>
-        </is>
-      </c>
-      <c r="BK10" t="inlineStr">
-        <is>
-          <t>其他電子業</t>
-        </is>
-      </c>
-      <c r="BL10" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0.52</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
-        <is>
-          <t>-6.762392378742623</t>
-        </is>
-      </c>
-      <c r="BO10" t="inlineStr">
-        <is>
-          <t>-2.51519879485662</t>
-        </is>
-      </c>
-      <c r="BP10" t="inlineStr">
-        <is>
-          <t>-8.12262189377373</t>
-        </is>
-      </c>
-      <c r="BQ10" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR10" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS10" t="inlineStr">
-        <is>
-          <t>1.30</t>
-        </is>
-      </c>
-      <c r="BT10" t="inlineStr">
-        <is>
-          <t>6.09</t>
-        </is>
-      </c>
-      <c r="BU10" t="inlineStr">
-        <is>
-          <t>11.84</t>
-        </is>
-      </c>
-      <c r="BV10" t="inlineStr">
-        <is>
-          <t>11.95</t>
-        </is>
-      </c>
-      <c r="BW10" t="inlineStr">
-        <is>
-          <t>31.81%</t>
-        </is>
-      </c>
-      <c r="BX10" t="inlineStr">
-        <is>
-          <t>15.81%</t>
-        </is>
-      </c>
-      <c r="BY10" t="inlineStr">
-        <is>
-          <t>41.15</t>
-        </is>
-      </c>
-      <c r="BZ10" t="inlineStr">
-        <is>
-          <t>6938</t>
-        </is>
-      </c>
-      <c r="CA10" t="inlineStr">
-        <is>
-          <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB10" t="inlineStr">
-        <is>
-          <t>敦吉-其他電子業-上市</t>
-        </is>
-      </c>
-      <c r="CC10" t="inlineStr">
-        <is>
-          <t>其他電子業平上市</t>
-        </is>
-      </c>
-      <c r="CD10" t="inlineStr">
-        <is>
-          <t>65.5</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>66.4</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>65.1</t>
-        </is>
-      </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,107 +4681,107 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>81.351</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
           <t>-0.61</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>39.131</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,74 +4812,66 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>54.62</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>-0.54</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
+          <t>55.33</t>
+        </is>
+      </c>
+      <c r="AH11" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="AI11" t="n">
+        <v>0.46</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-6.86</t>
-        </is>
-      </c>
-      <c r="AQ11" t="inlineStr">
-        <is>
-          <t>0.51</t>
-        </is>
-      </c>
-      <c r="AR11" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+          <t>-4.25</t>
+        </is>
+      </c>
+      <c r="AQ11" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AR11" t="n">
+        <v>0.54</v>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
@@ -4960,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-60.85</t>
+          <t>-61.26</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>6067262.6</v>
+        <v>3485392</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5791577.0</t>
+          <t>6043765.8</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4635115.64</v>
+        <v>4691358.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>275685</t>
+          <t>-2558373</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>67705.00222436106</t>
+          <t>20855.39480073467</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-303090.7388503868</t>
+          <t>-236817.4460292105</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -5026,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5173,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【b】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5183,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>40.248</t>
+          <t>39.131</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5218,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>16.93</t>
+          <t>4.76</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5278,12 +5198,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>3.12</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>9.91</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.75</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,74 +5234,66 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>64.71</t>
+          <t>28.57</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>56.86</t>
-        </is>
-      </c>
-      <c r="AH12" t="inlineStr">
-        <is>
-          <t>-0.21</t>
-        </is>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>1.05</t>
-        </is>
+          <t>54.62</t>
+        </is>
+      </c>
+      <c r="AH12" t="n">
+        <v>-0.54</v>
+      </c>
+      <c r="AI12" t="n">
+        <v>0.67</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>1.04</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.55</v>
+        <v>65.62</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.40000000000001</v>
+        <v>64.43000000000001</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.7</t>
+          <t>63.77</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>1.05</t>
-        </is>
-      </c>
-      <c r="AQ12" t="inlineStr">
-        <is>
-          <t>0.56</t>
-        </is>
-      </c>
-      <c r="AR12" t="inlineStr">
-        <is>
-          <t>0.55</t>
-        </is>
+          <t>-6.86</t>
+        </is>
+      </c>
+      <c r="AQ12" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="AR12" t="n">
+        <v>0.55</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5390,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-60.18</t>
+          <t>-60.85</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7697434.725531915</t>
+          <t>7688594.806657224</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6799297</v>
+        <v>6067262.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5814893.0</t>
+          <t>5791577.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4629531.48</v>
+        <v>4635115.64</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>984404</t>
+          <t>275685</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>135122.4096924971</t>
+          <t>67705.00222436106</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-89812.2379216943</t>
+          <t>-303090.7388503868</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2664241.0</t>
+          <t>2567899.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.09</t>
+          <t>6.06</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.95</t>
+          <t>12.0</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.15</t>
+          <t>42.22</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6938</t>
+          <t>6969</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>66.9</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>14.779</t>
+          <t>22.824</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,28 +1019,28 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -1050,30 +1050,30 @@
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.16</v>
+        <v>66.22</v>
       </c>
       <c r="AN2" t="n">
-        <v>64.97</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.34</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-67.04</t>
+          <t>-69.15</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2948729.4</v>
+        <v>2967914.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>3100620.6</t>
+          <t>2717507.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4708957.14</v>
+        <v>4702861.12</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-151891</t>
+          <t>250406</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-356245.9758127016</t>
+          <t>-379961.1206572224</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-443688.1403755629</t>
+          <t>-510394.4173020865</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,92 +1320,92 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.99</v>
+        <v>-0.36</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
@@ -1467,35 +1467,35 @@
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.24000000000001</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.11</v>
+        <v>66.16</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.92</v>
+        <v>64.97</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-20.99</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-67.04</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>3131906.6</v>
+        <v>2948729.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3260313.7</t>
+          <t>3100620.6</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4743373.54</v>
+        <v>4708957.14</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-128407</t>
+          <t>-151891</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-340347.400437636</t>
+          <t>-356245.9758127016</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-274795.6326099746</t>
+          <t>-443688.1403755629</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1630,7 +1630,7 @@
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.21</v>
+        <v>-0.99</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-20.99</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-63.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2522940.8</v>
+        <v>3131906.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2938653.4</t>
+          <t>3260313.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4638644.26</v>
+        <v>4743373.54</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-415712</t>
+          <t>-128407</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-352265.903679029</t>
+          <t>-340347.400437636</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-549764.6346373484</t>
+          <t>-274795.6326099746</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,61 +2285,61 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>0.3</v>
+        <v>-0.21</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,7 +2524,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,58 +2707,58 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AR6" t="n">
         <v>0.53</v>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,89 +2993,89 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="S7" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T7" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -3088,12 +3088,12 @@
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,48 +3202,48 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,7 +3303,7 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
@@ -3313,12 +3313,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,14 +3368,14 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF7" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -3383,7 +3383,7 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3405,7 +3405,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3415,104 +3415,104 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W8" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3561,44 +3561,44 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ8" t="n">
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,17 +3790,17 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,74 +3852,74 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-0.6</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -3932,14 +3932,14 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X9" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,54 +3973,54 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,12 +4147,12 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF9" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG9" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,109 +4259,109 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,58 +4395,58 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AR10" t="n">
         <v>0.54</v>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,7 +4696,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4706,7 +4706,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -4716,7 +4716,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4781,7 +4781,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,58 +4817,58 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.18</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.7</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.48</v>
+        <v>64.55</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="AR11" t="n">
         <v>0.54</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.26</t>
+          <t>-61.46</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>5341112.0</t>
+          <t>2671992.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3485392</v>
+        <v>3298712</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>6043765.8</t>
+          <t>5623624.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4691358.28</v>
+        <v>4598588.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2558373</t>
+          <t>-2324912</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>20855.39480073467</t>
+          <t>-41536.15899994106</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-236817.4460292105</t>
+          <t>-384689.7049036575</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>5341112.0</t>
+          <t>2671992.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>39.131</t>
+          <t>81.351</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,92 +5118,92 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-42.33</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.45</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>4.76</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-10-21</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
-      </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>9.91</t>
+          <t>20.60</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,61 +5239,61 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>23</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>28.57</t>
+          <t>72.73</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>54.62</t>
+          <t>55.33</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>-0.54</v>
+        <v>0.61</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.67</v>
+        <v>0.46</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>1.04</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.62</v>
+        <v>65.7</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.43000000000001</v>
+        <v>64.48</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.77</t>
+          <t>63.86</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-6.86</t>
+          <t>-4.25</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="AR12" t="n">
-        <v>0.55</v>
+        <v>0.54</v>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-60.85</t>
+          <t>-61.26</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7688594.806657224</t>
+          <t>7680923.495049505</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>6067262.6</v>
+        <v>3485392</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5791577.0</t>
+          <t>6043765.8</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4635115.64</v>
+        <v>4691358.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>275685</t>
+          <t>-2558373</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>67705.00222436106</t>
+          <t>20855.39480073467</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-303090.7388503868</t>
+          <t>-236817.4460292105</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2567899.0</t>
+          <t>5341112.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.52</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.06</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.0</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>42.22</t>
+          <t>41.61</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6969</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>65.1</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>22.824</t>
+          <t>18.974</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,12 +993,12 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -1014,66 +1014,66 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>-0.03</v>
+        <v>-0.33</v>
       </c>
       <c r="AI2" t="n">
-        <v>0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.22</t>
+          <t>66.02000000000001</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.22</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN2" t="n">
-        <v>65.01000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>64.59</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-35.06</t>
         </is>
       </c>
       <c r="AQ2" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-69.15</t>
+          <t>-71.63</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>2967914.4</v>
+        <v>2222219.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2717507.9</t>
+          <t>2575084.7</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4702861.12</v>
+        <v>4689074.64</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>250406</t>
+          <t>-352865</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-379961.1206572224</t>
+          <t>-408274.1522050498</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-510394.4173020865</t>
+          <t>-563995.8257181002</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1173,7 +1173,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>14.779</t>
+          <t>22.824</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1436,33 +1436,33 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
@@ -1472,30 +1472,30 @@
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.16</v>
+        <v>66.22</v>
       </c>
       <c r="AN3" t="n">
-        <v>64.97</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-26.34</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-67.04</t>
+          <t>-69.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2948729.4</v>
+        <v>2967914.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>3100620.6</t>
+          <t>2717507.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4708957.14</v>
+        <v>4702861.12</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-151891</t>
+          <t>250406</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-356245.9758127016</t>
+          <t>-379961.1206572224</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-443688.1403755629</t>
+          <t>-510394.4173020865</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1595,7 +1595,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,84 +1742,84 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,29 +1858,29 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.99</v>
+        <v>-0.36</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
@@ -1889,35 +1889,35 @@
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.24000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.11</v>
+        <v>66.16</v>
       </c>
       <c r="AN4" t="n">
-        <v>64.92</v>
+        <v>64.97</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-20.99</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-67.04</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>3131906.6</v>
+        <v>2948729.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>3260313.7</t>
+          <t>3100620.6</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4743373.54</v>
+        <v>4708957.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-128407</t>
+          <t>-151891</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-340347.400437636</t>
+          <t>-356245.9758127016</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-274795.6326099746</t>
+          <t>-443688.1403755629</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2017,7 +2017,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2037,12 +2037,12 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2052,7 +2052,7 @@
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,66 +2280,66 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.21</v>
+        <v>-0.99</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-20.99</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-63.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2522940.8</v>
+        <v>3131906.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>2938653.4</t>
+          <t>3260313.7</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4638644.26</v>
+        <v>4743373.54</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-415712</t>
+          <t>-128407</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-352265.903679029</t>
+          <t>-340347.400437636</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-549764.6346373484</t>
+          <t>-274795.6326099746</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2439,7 +2439,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,66 +2702,66 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>0.3</v>
+        <v>-0.21</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2861,7 +2861,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -2956,12 +2956,12 @@
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,63 +3124,63 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AR7" t="n">
         <v>0.53</v>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3283,7 +3283,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,87 +3415,87 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>-0.76</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
@@ -3510,12 +3510,12 @@
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,66 +3546,66 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,48 +3624,48 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3705,7 +3705,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3725,7 +3725,7 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
@@ -3735,12 +3735,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,14 +3790,14 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF8" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -3805,7 +3805,7 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3827,7 +3827,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3837,104 +3837,104 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W9" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,12 +3968,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -3983,44 +3983,44 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ9" t="n">
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4127,7 +4127,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4162,7 +4162,7 @@
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,17 +4212,17 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4259,12 +4259,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4274,74 +4274,74 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>-1.22</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-0.76</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T10" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -4354,14 +4354,14 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X10" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,59 +4390,59 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4549,7 +4549,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,22 +4634,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF10" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG10" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,109 +4681,109 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-1.37</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-0.45</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,63 +4812,63 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ11" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AR11" t="n">
         <v>0.54</v>
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,48 +4890,48 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5001,12 +5001,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>81.351</t>
+          <t>40.234</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5128,7 +5128,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -5138,7 +5138,7 @@
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-42.33</t>
+          <t>-41.34</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>20.60</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,63 +5234,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>23</t>
+          <t>19</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>72.73</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>55.33</t>
+          <t>61.04</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.61</v>
+        <v>0.48</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.46</v>
+        <v>0.65</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.18</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.7</v>
+        <v>65.76000000000001</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.48</v>
+        <v>64.55</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.86</t>
+          <t>63.95</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-4.25</t>
+          <t>-2.08</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="AR12" t="n">
         <v>0.54</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.26</t>
+          <t>-61.46</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7680923.495049505</t>
+          <t>7672718.292372881</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>5341112.0</t>
+          <t>2671992.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3485392</v>
+        <v>3298712</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>6043765.8</t>
+          <t>5623624.2</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4691358.28</v>
+        <v>4598588.42</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2558373</t>
+          <t>-2324912</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>20855.39480073467</t>
+          <t>-41536.15899994106</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-236817.4460292105</t>
+          <t>-384689.7049036575</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>5341112.0</t>
+          <t>2671992.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5393,7 +5393,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>0.51</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.08</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.96</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.61</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6948</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.7</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>65.1</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18.974</t>
+          <t>88.077</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,128 +1014,128 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>81.82</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>45.45</t>
+        </is>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>1.81</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0.78</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>66.06</t>
+        </is>
+      </c>
+      <c r="AM2" t="n">
+        <v>66.29000000000001</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>65.11</v>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>64.61</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>-26.17</t>
+        </is>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0.27</v>
+      </c>
+      <c r="AR2" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>-73.37</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>5851506.0</t>
+        </is>
+      </c>
+      <c r="AX2" t="n">
+        <v>3092212.6</v>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>2807576.7</t>
+        </is>
+      </c>
+      <c r="AZ2" t="n">
+        <v>4754950.82</v>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>284635</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>-382714.431245251</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>-242135.9659663578</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5851506.0</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>9.09</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AH2" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="AI2" t="n">
-        <v>-0.33</v>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>66.02000000000001</t>
-        </is>
-      </c>
-      <c r="AM2" t="n">
-        <v>66.23999999999999</v>
-      </c>
-      <c r="AN2" t="n">
-        <v>65.06</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>64.59</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>-35.06</t>
-        </is>
-      </c>
-      <c r="AQ2" t="n">
-        <v>0.26</v>
-      </c>
-      <c r="AR2" t="n">
-        <v>0.4</v>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>-71.63</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>1247760.0</t>
-        </is>
-      </c>
-      <c r="AX2" t="n">
-        <v>2222219.6</v>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>2575084.7</t>
-        </is>
-      </c>
-      <c r="AZ2" t="n">
-        <v>4689074.64</v>
-      </c>
-      <c r="BA2" t="inlineStr">
-        <is>
-          <t>-352865</t>
-        </is>
-      </c>
-      <c r="BB2" t="inlineStr">
-        <is>
-          <t>-408274.1522050498</t>
-        </is>
-      </c>
-      <c r="BC2" t="inlineStr">
-        <is>
-          <t>-563995.8257181002</t>
-        </is>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
-          <t>1247760.0</t>
-        </is>
-      </c>
-      <c r="BE2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF2" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,22 +1193,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,22 +1258,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CF2" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>22.824</t>
+          <t>18.974</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.2</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -1436,128 +1436,128 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>9.09</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AH3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>66.02000000000001</t>
+        </is>
+      </c>
+      <c r="AM3" t="n">
+        <v>66.23999999999999</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>65.06</v>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>64.59</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>-35.06</t>
+        </is>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="AR3" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>-71.63</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>1247760.0</t>
+        </is>
+      </c>
+      <c r="AX3" t="n">
+        <v>2222219.6</v>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>2575084.7</t>
+        </is>
+      </c>
+      <c r="AZ3" t="n">
+        <v>4689074.64</v>
+      </c>
+      <c r="BA3" t="inlineStr">
+        <is>
+          <t>-352865</t>
+        </is>
+      </c>
+      <c r="BB3" t="inlineStr">
+        <is>
+          <t>-408274.1522050498</t>
+        </is>
+      </c>
+      <c r="BC3" t="inlineStr">
+        <is>
+          <t>-563995.8257181002</t>
+        </is>
+      </c>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>1247760.0</t>
+        </is>
+      </c>
+      <c r="BE3" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>45.45</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>24.24</t>
-        </is>
-      </c>
-      <c r="AH3" t="n">
-        <v>-0.03</v>
-      </c>
-      <c r="AI3" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>66.22</t>
-        </is>
-      </c>
-      <c r="AM3" t="n">
-        <v>66.22</v>
-      </c>
-      <c r="AN3" t="n">
-        <v>65.01000000000001</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>64.55</t>
-        </is>
-      </c>
-      <c r="AP3" t="inlineStr">
-        <is>
-          <t>-27.32</t>
-        </is>
-      </c>
-      <c r="AQ3" t="n">
-        <v>0.31</v>
-      </c>
-      <c r="AR3" t="n">
-        <v>0.43</v>
-      </c>
-      <c r="AS3" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT3" t="inlineStr">
-        <is>
-          <t>-69.15</t>
-        </is>
-      </c>
-      <c r="AU3" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV3" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>1509985.0</t>
-        </is>
-      </c>
-      <c r="AX3" t="n">
-        <v>2967914.4</v>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>2717507.9</t>
-        </is>
-      </c>
-      <c r="AZ3" t="n">
-        <v>4702861.12</v>
-      </c>
-      <c r="BA3" t="inlineStr">
-        <is>
-          <t>250406</t>
-        </is>
-      </c>
-      <c r="BB3" t="inlineStr">
-        <is>
-          <t>-379961.1206572224</t>
-        </is>
-      </c>
-      <c r="BC3" t="inlineStr">
-        <is>
-          <t>-510394.4173020865</t>
-        </is>
-      </c>
-      <c r="BD3" t="inlineStr">
-        <is>
-          <t>1509985.0</t>
-        </is>
-      </c>
-      <c r="BE3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF3" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14.779</t>
+          <t>22.824</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.6</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,17 +1837,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1858,128 +1858,128 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>45.45</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>24.24</t>
+        </is>
+      </c>
+      <c r="AH4" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>66.22</t>
+        </is>
+      </c>
+      <c r="AM4" t="n">
+        <v>66.22</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>65.01000000000001</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>64.55</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>-27.32</t>
+        </is>
+      </c>
+      <c r="AQ4" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="AR4" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>-69.15</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>1509985.0</t>
+        </is>
+      </c>
+      <c r="AX4" t="n">
+        <v>2967914.4</v>
+      </c>
+      <c r="AY4" t="inlineStr">
+        <is>
+          <t>2717507.9</t>
+        </is>
+      </c>
+      <c r="AZ4" t="n">
+        <v>4702861.12</v>
+      </c>
+      <c r="BA4" t="inlineStr">
+        <is>
+          <t>250406</t>
+        </is>
+      </c>
+      <c r="BB4" t="inlineStr">
+        <is>
+          <t>-379961.1206572224</t>
+        </is>
+      </c>
+      <c r="BC4" t="inlineStr">
+        <is>
+          <t>-510394.4173020865</t>
+        </is>
+      </c>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>1509985.0</t>
+        </is>
+      </c>
+      <c r="BE4" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>27.27</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>30.3</t>
-        </is>
-      </c>
-      <c r="AH4" t="n">
-        <v>-0.36</v>
-      </c>
-      <c r="AI4" t="n">
-        <v>0.13</v>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0.72</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>66.24000000000001</t>
-        </is>
-      </c>
-      <c r="AM4" t="n">
-        <v>66.16</v>
-      </c>
-      <c r="AN4" t="n">
-        <v>64.97</v>
-      </c>
-      <c r="AO4" t="inlineStr">
-        <is>
-          <t>64.5</t>
-        </is>
-      </c>
-      <c r="AP4" t="inlineStr">
-        <is>
-          <t>-26.34</t>
-        </is>
-      </c>
-      <c r="AQ4" t="n">
-        <v>0.34</v>
-      </c>
-      <c r="AR4" t="n">
-        <v>0.46</v>
-      </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>-67.04</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW4" t="inlineStr">
-        <is>
-          <t>970968.0</t>
-        </is>
-      </c>
-      <c r="AX4" t="n">
-        <v>2948729.4</v>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>3100620.6</t>
-        </is>
-      </c>
-      <c r="AZ4" t="n">
-        <v>4708957.14</v>
-      </c>
-      <c r="BA4" t="inlineStr">
-        <is>
-          <t>-151891</t>
-        </is>
-      </c>
-      <c r="BB4" t="inlineStr">
-        <is>
-          <t>-356245.9758127016</t>
-        </is>
-      </c>
-      <c r="BC4" t="inlineStr">
-        <is>
-          <t>-443688.1403755629</t>
-        </is>
-      </c>
-      <c r="BD4" t="inlineStr">
-        <is>
-          <t>970968.0</t>
-        </is>
-      </c>
-      <c r="BE4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF4" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,92 +2164,92 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0.9</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2280,128 +2280,128 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>27.27</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>30.3</t>
+        </is>
+      </c>
+      <c r="AH5" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI5" t="n">
+        <v>0.13</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>66.24000000000001</t>
+        </is>
+      </c>
+      <c r="AM5" t="n">
+        <v>66.16</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>64.97</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>64.5</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>-26.34</t>
+        </is>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="AR5" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>-67.04</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>970968.0</t>
+        </is>
+      </c>
+      <c r="AX5" t="n">
+        <v>2948729.4</v>
+      </c>
+      <c r="AY5" t="inlineStr">
+        <is>
+          <t>3100620.6</t>
+        </is>
+      </c>
+      <c r="AZ5" t="n">
+        <v>4708957.14</v>
+      </c>
+      <c r="BA5" t="inlineStr">
+        <is>
+          <t>-151891</t>
+        </is>
+      </c>
+      <c r="BB5" t="inlineStr">
+        <is>
+          <t>-356245.9758127016</t>
+        </is>
+      </c>
+      <c r="BC5" t="inlineStr">
+        <is>
+          <t>-443688.1403755629</t>
+        </is>
+      </c>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>970968.0</t>
+        </is>
+      </c>
+      <c r="BE5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>54.55</t>
-        </is>
-      </c>
-      <c r="AH5" t="n">
-        <v>-0.99</v>
-      </c>
-      <c r="AI5" t="n">
-        <v>0.37</v>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>0.73</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>66.36</t>
-        </is>
-      </c>
-      <c r="AM5" t="n">
-        <v>66.11</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>64.92</v>
-      </c>
-      <c r="AO5" t="inlineStr">
-        <is>
-          <t>64.46</t>
-        </is>
-      </c>
-      <c r="AP5" t="inlineStr">
-        <is>
-          <t>-20.99</t>
-        </is>
-      </c>
-      <c r="AQ5" t="n">
-        <v>0.39</v>
-      </c>
-      <c r="AR5" t="n">
-        <v>0.49</v>
-      </c>
-      <c r="AS5" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT5" t="inlineStr">
-        <is>
-          <t>-64.87</t>
-        </is>
-      </c>
-      <c r="AU5" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV5" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW5" t="inlineStr">
-        <is>
-          <t>5880844.0</t>
-        </is>
-      </c>
-      <c r="AX5" t="n">
-        <v>3131906.6</v>
-      </c>
-      <c r="AY5" t="inlineStr">
-        <is>
-          <t>3260313.7</t>
-        </is>
-      </c>
-      <c r="AZ5" t="n">
-        <v>4743373.54</v>
-      </c>
-      <c r="BA5" t="inlineStr">
-        <is>
-          <t>-128407</t>
-        </is>
-      </c>
-      <c r="BB5" t="inlineStr">
-        <is>
-          <t>-340347.400437636</t>
-        </is>
-      </c>
-      <c r="BC5" t="inlineStr">
-        <is>
-          <t>-274795.6326099746</t>
-        </is>
-      </c>
-      <c r="BD5" t="inlineStr">
-        <is>
-          <t>5880844.0</t>
-        </is>
-      </c>
-      <c r="BE5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF5" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,12 +2459,12 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2474,7 +2474,7 @@
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.91</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -2606,7 +2606,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2702,128 +2702,128 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>54.55</t>
+        </is>
+      </c>
+      <c r="AH6" t="n">
+        <v>-0.99</v>
+      </c>
+      <c r="AI6" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>66.36</t>
+        </is>
+      </c>
+      <c r="AM6" t="n">
+        <v>66.11</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>64.92</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>64.46</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>-20.99</t>
+        </is>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="AR6" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>-64.87</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="AX6" t="n">
+        <v>3131906.6</v>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>3260313.7</t>
+        </is>
+      </c>
+      <c r="AZ6" t="n">
+        <v>4743373.54</v>
+      </c>
+      <c r="BA6" t="inlineStr">
+        <is>
+          <t>-128407</t>
+        </is>
+      </c>
+      <c r="BB6" t="inlineStr">
+        <is>
+          <t>-340347.400437636</t>
+        </is>
+      </c>
+      <c r="BC6" t="inlineStr">
+        <is>
+          <t>-274795.6326099746</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>5880844.0</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>63.64</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>74.55</t>
-        </is>
-      </c>
-      <c r="AH6" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="AI6" t="n">
-        <v>0.64</v>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>1.89</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>0.77</t>
-        </is>
-      </c>
-      <c r="AL6" t="inlineStr">
-        <is>
-          <t>66.54</t>
-        </is>
-      </c>
-      <c r="AM6" t="n">
-        <v>66.12</v>
-      </c>
-      <c r="AN6" t="n">
-        <v>64.89</v>
-      </c>
-      <c r="AO6" t="inlineStr">
-        <is>
-          <t>64.4</t>
-        </is>
-      </c>
-      <c r="AP6" t="inlineStr">
-        <is>
-          <t>-8.08</t>
-        </is>
-      </c>
-      <c r="AQ6" t="n">
-        <v>0.47</v>
-      </c>
-      <c r="AR6" t="n">
-        <v>0.52</v>
-      </c>
-      <c r="AS6" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT6" t="inlineStr">
-        <is>
-          <t>-63.03</t>
-        </is>
-      </c>
-      <c r="AU6" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV6" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW6" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="AX6" t="n">
-        <v>2522940.8</v>
-      </c>
-      <c r="AY6" t="inlineStr">
-        <is>
-          <t>2938653.4</t>
-        </is>
-      </c>
-      <c r="AZ6" t="n">
-        <v>4638644.26</v>
-      </c>
-      <c r="BA6" t="inlineStr">
-        <is>
-          <t>-415712</t>
-        </is>
-      </c>
-      <c r="BB6" t="inlineStr">
-        <is>
-          <t>-352265.903679029</t>
-        </is>
-      </c>
-      <c r="BC6" t="inlineStr">
-        <is>
-          <t>-549764.6346373484</t>
-        </is>
-      </c>
-      <c r="BD6" t="inlineStr">
-        <is>
-          <t>1501541.0</t>
-        </is>
-      </c>
-      <c r="BE6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF6" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,22 +2881,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3124,128 +3124,128 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>63.64</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>74.55</t>
+        </is>
+      </c>
+      <c r="AH7" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>0.64</v>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>1.89</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>0.77</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>66.54</t>
+        </is>
+      </c>
+      <c r="AM7" t="n">
+        <v>66.12</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>64.89</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>64.4</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>-8.08</t>
+        </is>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="AR7" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>-63.03</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>1501541.0</t>
+        </is>
+      </c>
+      <c r="AX7" t="n">
+        <v>2522940.8</v>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>2938653.4</t>
+        </is>
+      </c>
+      <c r="AZ7" t="n">
+        <v>4638644.26</v>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>-415712</t>
+        </is>
+      </c>
+      <c r="BB7" t="inlineStr">
+        <is>
+          <t>-352265.903679029</t>
+        </is>
+      </c>
+      <c r="BC7" t="inlineStr">
+        <is>
+          <t>-549764.6346373484</t>
+        </is>
+      </c>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>1501541.0</t>
+        </is>
+      </c>
+      <c r="BE7" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>83.64</t>
-        </is>
-      </c>
-      <c r="AH7" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>0.78</v>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>0.81</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="AM7" t="n">
-        <v>66.09</v>
-      </c>
-      <c r="AN7" t="n">
-        <v>64.84999999999999</v>
-      </c>
-      <c r="AO7" t="inlineStr">
-        <is>
-          <t>64.33</t>
-        </is>
-      </c>
-      <c r="AP7" t="inlineStr">
-        <is>
-          <t>-3.69</t>
-        </is>
-      </c>
-      <c r="AQ7" t="n">
-        <v>0.51</v>
-      </c>
-      <c r="AR7" t="n">
-        <v>0.53</v>
-      </c>
-      <c r="AS7" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT7" t="inlineStr">
-        <is>
-          <t>-62.28</t>
-        </is>
-      </c>
-      <c r="AU7" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV7" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>4976234.0</t>
-        </is>
-      </c>
-      <c r="AX7" t="n">
-        <v>2927949.8</v>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>3113330.9</t>
-        </is>
-      </c>
-      <c r="AZ7" t="n">
-        <v>4657185.68</v>
-      </c>
-      <c r="BA7" t="inlineStr">
-        <is>
-          <t>-185381</t>
-        </is>
-      </c>
-      <c r="BB7" t="inlineStr">
-        <is>
-          <t>-316357.043504789</t>
-        </is>
-      </c>
-      <c r="BC7" t="inlineStr">
-        <is>
-          <t>-453732.0077251205</t>
-        </is>
-      </c>
-      <c r="BD7" t="inlineStr">
-        <is>
-          <t>4976234.0</t>
-        </is>
-      </c>
-      <c r="BE7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="BF7" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,7 +3368,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.76</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3546,63 +3546,63 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AR8" t="n">
         <v>0.53</v>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7672718.292372881</t>
+          <t>7674276.177715092</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,22 +3790,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,89 +3837,89 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="S9" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T9" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -3932,12 +3932,12 @@
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3968,128 +3968,128 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>60.0</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>80.61</t>
+        </is>
+      </c>
+      <c r="AH9" t="n">
+        <v>-0.36</v>
+      </c>
+      <c r="AI9" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>0.82</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>66.53999999999999</t>
+        </is>
+      </c>
+      <c r="AM9" t="n">
+        <v>66.05</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>64.78</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>64.26</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>-5.79</t>
+        </is>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AR9" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>1.39</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>-61.93</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>2025/11/26</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>7674276.177715092</t>
+        </is>
+      </c>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>1414060.0</t>
+        </is>
+      </c>
+      <c r="AX9" t="n">
+        <v>2467101.4</v>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>2976246.7</t>
+        </is>
+      </c>
+      <c r="AZ9" t="n">
+        <v>4582639.88</v>
+      </c>
+      <c r="BA9" t="inlineStr">
+        <is>
+          <t>-509145</t>
+        </is>
+      </c>
+      <c r="BB9" t="inlineStr">
+        <is>
+          <t>-291379.7772829105</t>
+        </is>
+      </c>
+      <c r="BC9" t="inlineStr">
+        <is>
+          <t>-672626.3618603265</t>
+        </is>
+      </c>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>1414060.0</t>
+        </is>
+      </c>
+      <c r="BE9" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>90.91</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>93.94</t>
-        </is>
-      </c>
-      <c r="AH9" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="AI9" t="n">
-        <v>0.82</v>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>1.99</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>0.84</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>66.56000000000002</t>
-        </is>
-      </c>
-      <c r="AM9" t="n">
-        <v>66.02</v>
-      </c>
-      <c r="AN9" t="n">
-        <v>64.73</v>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>64.19</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>-0.56</t>
-        </is>
-      </c>
-      <c r="AQ9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AR9" t="n">
-        <v>0.54</v>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>1.39</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>-61.38</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>2025/11/26</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>7672718.292372881</t>
-        </is>
-      </c>
-      <c r="AW9" t="inlineStr">
-        <is>
-          <t>1886854.0</t>
-        </is>
-      </c>
-      <c r="AX9" t="n">
-        <v>3252511.8</v>
-      </c>
-      <c r="AY9" t="inlineStr">
-        <is>
-          <t>4659887.2</t>
-        </is>
-      </c>
-      <c r="AZ9" t="n">
-        <v>4592706.68</v>
-      </c>
-      <c r="BA9" t="inlineStr">
-        <is>
-          <t>-1407375</t>
-        </is>
-      </c>
-      <c r="BB9" t="inlineStr">
-        <is>
-          <t>-222062.2164506531</t>
-        </is>
-      </c>
-      <c r="BC9" t="inlineStr">
-        <is>
-          <t>-579648.7119870372</t>
-        </is>
-      </c>
-      <c r="BD9" t="inlineStr">
-        <is>
-          <t>1886854.0</t>
-        </is>
-      </c>
-      <c r="BE9" t="inlineStr">
-        <is>
-          <t>2025-11-28</t>
-        </is>
-      </c>
       <c r="BF9" t="inlineStr">
         <is>
           <t>65.0</t>
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,7 +4147,7 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,14 +4212,14 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF9" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4249,7 +4249,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4259,104 +4259,104 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>-1.22</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W10" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4390,12 +4390,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4405,44 +4405,44 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ10" t="n">
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,43 +4468,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7672718.292372881</t>
+          <t>7674276.177715092</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4584,7 +4584,7 @@
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,17 +4634,17 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4696,74 +4696,74 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>-1.37</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
       <c r="T11" t="inlineStr">
         <is>
           <t>64.1</t>
@@ -4776,14 +4776,14 @@
       </c>
       <c r="V11" t="inlineStr">
         <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X11" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4812,59 +4812,59 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7672718.292372881</t>
+          <t>7674276.177715092</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4946,7 +4946,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,22 +5056,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE11" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF11" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG11" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE11" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF11" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG11" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5093,7 +5093,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【b1】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5103,109 +5103,109 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>52.918</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-39.47</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>0.00</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
           <t>0.15</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>40.234</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>66.5</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>-1.06</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-41.34</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>13.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5234,63 +5234,63 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>88</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>61.04</t>
+          <t>84.85</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.48</v>
+        <v>0.63</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.65</v>
+        <v>0.67</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.94</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.18</t>
+          <t>66.28000000000002</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.76000000000001</v>
+        <v>65.84</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.55</v>
+        <v>64.59999999999999</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>63.95</t>
+          <t>64.03</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-2.08</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="AQ12" t="n">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="AR12" t="n">
         <v>0.54</v>
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.46</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,48 +5312,48 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7672718.292372881</t>
+          <t>7674276.177715092</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3298712</v>
+        <v>3354366</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5623624.2</t>
+          <t>5541880.1</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4598588.42</v>
+        <v>4584363.04</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2324912</t>
+          <t>-2187514</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-41536.15899994106</t>
+          <t>-98913.4412296701</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-384689.7049036575</t>
+          <t>-414488.4934931798</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>2671992.0</t>
+          <t>3526586.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="BF12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.62</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5423,12 +5423,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.08</t>
+          <t>6.01</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>11.96</t>
+          <t>12.11</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>41.21</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>6948</t>
+          <t>7033</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>66.7</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>66.5</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>88.077</t>
+          <t>64.21</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,69 +898,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1019,61 +1019,61 @@
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AH2" t="n">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="AI2" t="n">
-        <v>-0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.20000000000002</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>66.29000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AN2" t="n">
-        <v>65.11</v>
+        <v>65.17</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>64.63</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-26.17</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="AQ2" t="n">
         <v>0.27</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-73.37</t>
+          <t>-74.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1092,43 +1092,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>5851506.0</t>
+          <t>4274110.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>3092212.6</v>
+        <v>2770865.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>2807576.7</t>
+          <t>2951386.2</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>4754950.82</v>
+        <v>4790918.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>284635</t>
+          <t>-180520</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-382714.431245251</t>
+          <t>-343694.5748984399</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-242135.9659663578</t>
+          <t>-129085.364990979</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>5851506.0</t>
+          <t>4274110.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1193,7 +1193,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1218,7 +1218,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1233,12 +1233,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1258,7 +1258,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1268,12 +1268,12 @@
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1305,12 +1305,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18.974</t>
+          <t>88.077</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1320,7 +1320,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1330,7 +1330,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1340,7 +1340,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1405,7 +1405,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1415,17 +1415,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1441,61 +1441,61 @@
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AH3" t="n">
-        <v>-0.33</v>
+        <v>0.82</v>
       </c>
       <c r="AI3" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>66.02000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>66.23999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AN3" t="n">
-        <v>65.06</v>
+        <v>65.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>64.61</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-35.06</t>
+          <t>-26.17</t>
         </is>
       </c>
       <c r="AQ3" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-71.63</t>
+          <t>-73.37</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1514,43 +1514,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>1247760.0</t>
+          <t>5851506.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>2222219.6</v>
+        <v>3092212.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>2575084.7</t>
+          <t>2807576.7</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>4689074.64</v>
+        <v>4754950.82</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-352865</t>
+          <t>284635</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-408274.1522050498</t>
+          <t>-382714.431245251</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-563995.8257181002</t>
+          <t>-242135.9659663578</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>1247760.0</t>
+          <t>5851506.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1570,7 +1570,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1615,22 +1615,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1640,7 +1640,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1655,12 +1655,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1680,22 +1680,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CF3" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1727,12 +1727,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>22.824</t>
+          <t>18.974</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1742,7 +1742,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1752,7 +1752,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.9</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1762,7 +1762,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1827,7 +1827,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1837,12 +1837,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1863,61 +1863,61 @@
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AH4" t="n">
-        <v>-0.03</v>
+        <v>-0.33</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>66.22</t>
+          <t>66.02000000000001</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>66.22</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AN4" t="n">
-        <v>65.01000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>64.59</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-35.06</t>
         </is>
       </c>
       <c r="AQ4" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
@@ -1926,7 +1926,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-69.15</t>
+          <t>-71.63</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1936,43 +1936,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>2967914.4</v>
+        <v>2222219.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>2717507.9</t>
+          <t>2575084.7</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>4702861.12</v>
+        <v>4689074.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>250406</t>
+          <t>-352865</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-379961.1206572224</t>
+          <t>-408274.1522050498</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-510394.4173020865</t>
+          <t>-563995.8257181002</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -1992,7 +1992,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2037,22 +2037,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2062,7 +2062,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2077,12 +2077,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2102,22 +2102,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2149,12 +2149,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14.779</t>
+          <t>22.824</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2164,7 +2164,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2174,7 +2174,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2249,7 +2249,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2259,17 +2259,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2285,28 +2285,28 @@
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AH5" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="AI5" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
@@ -2316,30 +2316,30 @@
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>66.16</v>
+        <v>66.22</v>
       </c>
       <c r="AN5" t="n">
-        <v>64.97</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-26.34</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AQ5" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-67.04</t>
+          <t>-69.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2358,43 +2358,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>2948729.4</v>
+        <v>2967914.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>3100620.6</t>
+          <t>2717507.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>4708957.14</v>
+        <v>4702861.12</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-151891</t>
+          <t>250406</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-356245.9758127016</t>
+          <t>-379961.1206572224</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-443688.1403755629</t>
+          <t>-510394.4173020865</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2414,7 +2414,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2459,22 +2459,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2484,7 +2484,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2524,22 +2524,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2571,12 +2571,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2586,84 +2586,84 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0.6</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2671,7 +2671,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>-0.90</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2681,17 +2681,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2707,24 +2707,24 @@
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AH6" t="n">
-        <v>-0.99</v>
+        <v>-0.36</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
@@ -2733,35 +2733,35 @@
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.24000000000001</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>66.11</v>
+        <v>66.16</v>
       </c>
       <c r="AN6" t="n">
-        <v>64.92</v>
+        <v>64.97</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-20.99</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="AQ6" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
@@ -2770,7 +2770,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-67.04</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2780,43 +2780,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>3131906.6</v>
+        <v>2948729.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>3260313.7</t>
+          <t>3100620.6</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>4743373.54</v>
+        <v>4708957.14</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-128407</t>
+          <t>-151891</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-340347.400437636</t>
+          <t>-356245.9758127016</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-274795.6326099746</t>
+          <t>-443688.1403755629</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2836,7 +2836,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2881,12 +2881,12 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2896,7 +2896,7 @@
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2921,12 +2921,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2946,22 +2946,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -2993,12 +2993,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3008,7 +3008,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3018,7 +3018,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>1.05</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3103,17 +3103,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3129,61 +3129,61 @@
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AH7" t="n">
-        <v>-0.21</v>
+        <v>-0.99</v>
       </c>
       <c r="AI7" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AN7" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-20.99</t>
         </is>
       </c>
       <c r="AQ7" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
@@ -3192,7 +3192,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-63.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3202,43 +3202,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>2522940.8</v>
+        <v>3131906.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>2938653.4</t>
+          <t>3260313.7</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>4638644.26</v>
+        <v>4743373.54</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-415712</t>
+          <t>-128407</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-352265.903679029</t>
+          <t>-340347.400437636</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-549764.6346373484</t>
+          <t>-274795.6326099746</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3303,22 +3303,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3343,12 +3343,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3368,22 +3368,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3430,7 +3430,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3440,7 +3440,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -3450,7 +3450,7 @@
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3515,7 +3515,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3525,17 +3525,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3551,61 +3551,61 @@
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AH8" t="n">
-        <v>0.3</v>
+        <v>-0.21</v>
       </c>
       <c r="AI8" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AN8" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AQ8" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
@@ -3614,7 +3614,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3624,43 +3624,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3725,22 +3725,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3750,7 +3750,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3765,12 +3765,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -3800,12 +3800,12 @@
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3837,12 +3837,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3852,7 +3852,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3862,7 +3862,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -3872,7 +3872,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3937,7 +3937,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -3947,17 +3947,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -3973,58 +3973,58 @@
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AH9" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AI9" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AN9" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AQ9" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AR9" t="n">
         <v>0.53</v>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4046,43 +4046,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4102,7 +4102,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4147,22 +4147,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4187,12 +4187,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4212,22 +4212,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4259,87 +4259,87 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0.15</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R10" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
@@ -4354,12 +4354,12 @@
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4369,17 +4369,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4395,61 +4395,61 @@
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AH10" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AN10" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AQ10" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
@@ -4458,7 +4458,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4468,48 +4468,48 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
@@ -4524,7 +4524,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4569,7 +4569,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4579,12 +4579,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4594,7 +4594,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4609,12 +4609,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4634,14 +4634,14 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CF10" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -4649,7 +4649,7 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4671,7 +4671,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>【b1】</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4681,104 +4681,104 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>28.327</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>-30.20</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>42.513</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>-33.48</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>-0.15</t>
-        </is>
-      </c>
       <c r="W11" t="inlineStr">
         <is>
           <t>0.00</t>
@@ -4791,17 +4791,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>10.76</t>
+          <t>7.17</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4817,7 +4817,7 @@
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4827,44 +4827,44 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>93.94</t>
         </is>
       </c>
       <c r="AH11" t="n">
-        <v>0.33</v>
+        <v>0.06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.7</v>
+        <v>0.82</v>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.85</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>66.38000000000001</t>
+          <t>66.56000000000002</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>65.92</v>
+        <v>66.02</v>
       </c>
       <c r="AN11" t="n">
-        <v>64.66</v>
+        <v>64.73</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>64.12</t>
+          <t>64.19</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -4880,7 +4880,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-61.32</t>
+          <t>-61.38</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4890,43 +4890,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>3388720.8</v>
+        <v>3252511.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>5094008.9</t>
+          <t>4659887.2</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>4576609.36</v>
+        <v>4592706.68</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1705288</t>
+          <t>-1407375</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-157046.4899894924</t>
+          <t>-222062.2164506531</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-476778.2581685148</t>
+          <t>-579648.7119870372</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>2836015.0</t>
+          <t>1886854.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5006,7 +5006,7 @@
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5016,7 +5016,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5031,12 +5031,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5056,17 +5056,17 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5103,12 +5103,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.15</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>52.918</t>
+          <t>42.513</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5118,94 +5118,94 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-33.48</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
         <is>
           <t>-0.15</t>
         </is>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-39.47</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
+      <c r="W12" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>0.15</t>
-        </is>
-      </c>
       <c r="X12" t="inlineStr">
         <is>
           <t>1.52</t>
@@ -5213,17 +5213,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13.40</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.31</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5239,54 +5239,54 @@
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>88</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>84.85</t>
+          <t>90.91</t>
         </is>
       </c>
       <c r="AH12" t="n">
-        <v>0.63</v>
+        <v>0.33</v>
       </c>
       <c r="AI12" t="n">
-        <v>0.67</v>
+        <v>0.7</v>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.85</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>66.28000000000002</t>
+          <t>66.38000000000001</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>65.84</v>
+        <v>65.92</v>
       </c>
       <c r="AN12" t="n">
-        <v>64.59999999999999</v>
+        <v>64.66</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>64.03</t>
+          <t>64.12</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>0.87</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="AQ12" t="n">
@@ -5302,7 +5302,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.32</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5312,43 +5312,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>7674276.177715092</t>
+          <t>7672497.147887324</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>3354366</v>
+        <v>3388720.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>5541880.1</t>
+          <t>5094008.9</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>4584363.04</v>
+        <v>4576609.36</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2187514</t>
+          <t>-1705288</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-98913.4412296701</t>
+          <t>-157046.4899894924</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-414488.4934931798</t>
+          <t>-476778.2581685148</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>3526586.0</t>
+          <t>2836015.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5368,7 +5368,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>2.62</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三白兵</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.02</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5438,7 +5438,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.07</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5453,12 +5453,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>41.21</t>
+          <t>41.33</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5478,22 +5478,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CE12" t="inlineStr">
+        <is>
+          <t>67.0</t>
+        </is>
+      </c>
+      <c r="CF12" t="inlineStr">
+        <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CG12" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CE12" t="inlineStr">
-        <is>
-          <t>67.0</t>
-        </is>
-      </c>
-      <c r="CF12" t="inlineStr">
-        <is>
-          <t>66.2</t>
-        </is>
-      </c>
-      <c r="CG12" t="inlineStr">
-        <is>
-          <t>66.7</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -923,12 +923,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>48.667</t>
+          <t>15.593</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -938,69 +938,69 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>4.47</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1023,67 +1023,67 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2025/07/02</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2025/07/02</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>59.9</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>2025-12-12</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>12.32</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>0.30</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
@@ -1099,33 +1099,33 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>55.56</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>75.76</t>
+          <t>67.0</t>
         </is>
       </c>
       <c r="AP2" t="n">
-        <v>0.42</v>
+        <v>-0.18</v>
       </c>
       <c r="AQ2" t="n">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.63</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
@@ -1134,26 +1134,26 @@
         </is>
       </c>
       <c r="AU2" t="n">
-        <v>66.29000000000001</v>
+        <v>66.27</v>
       </c>
       <c r="AV2" t="n">
-        <v>65.23</v>
+        <v>65.28</v>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>64.66</t>
+          <t>64.69</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>-17.54</t>
+          <t>-21.94</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>0.28</v>
+        <v>0.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.34</v>
+        <v>0.32</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-75.91</t>
+          <t>-77.16</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
@@ -1172,43 +1172,43 @@
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>3240604.0</t>
+          <t>1032217.0</t>
         </is>
       </c>
       <c r="BF2" t="n">
-        <v>3224793</v>
+        <v>3129239.4</v>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>3086761.2</t>
+          <t>3048576.9</t>
         </is>
       </c>
       <c r="BH2" t="n">
-        <v>4840807.66</v>
+        <v>4778355.32</v>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>138031</t>
+          <t>80662</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>-309931.6803269014</t>
+          <t>-305844.3707094667</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>-124235.7601834396</t>
+          <t>-283364.1678135758</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>3240604.0</t>
+          <t>1032217.0</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1228,7 +1228,7 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1273,22 +1273,22 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
@@ -1298,7 +1298,7 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>66.5</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CO2" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CP2" t="inlineStr">
@@ -1385,12 +1385,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>64.21</t>
+          <t>48.667</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1410,7 +1410,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -1420,7 +1420,7 @@
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-6.12</t>
+          <t>4.47</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1530,27 +1530,27 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2025-12-11</t>
+          <t>2025-12-12</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>16.26</t>
+          <t>12.32</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
@@ -1561,61 +1561,61 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>51.52</t>
+          <t>75.76</t>
         </is>
       </c>
       <c r="AP3" t="n">
-        <v>0.3</v>
+        <v>0.42</v>
       </c>
       <c r="AQ3" t="n">
-        <v>-0.14</v>
+        <v>0.04</v>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>1.63</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.89</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>66.20000000000002</t>
+          <t>66.32000000000001</t>
         </is>
       </c>
       <c r="AU3" t="n">
-        <v>66.3</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AV3" t="n">
-        <v>65.17</v>
+        <v>65.23</v>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>64.63</t>
+          <t>64.66</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>-23.44</t>
+          <t>-17.54</t>
         </is>
       </c>
       <c r="AY3" t="n">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.35</v>
+        <v>0.34</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1624,7 +1624,7 @@
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-74.85</t>
+          <t>-75.91</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
@@ -1634,43 +1634,43 @@
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>4274110.0</t>
+          <t>3240604.0</t>
         </is>
       </c>
       <c r="BF3" t="n">
-        <v>2770865.8</v>
+        <v>3224793</v>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>2951386.2</t>
+          <t>3086761.2</t>
         </is>
       </c>
       <c r="BH3" t="n">
-        <v>4790918.58</v>
+        <v>4840807.66</v>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-180520</t>
+          <t>138031</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>-343694.5748984399</t>
+          <t>-309931.6803269014</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>-129085.364990979</t>
+          <t>-124235.7601834396</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>4274110.0</t>
+          <t>3240604.0</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1690,7 +1690,7 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
@@ -1735,7 +1735,7 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1745,12 +1745,12 @@
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
@@ -1800,22 +1800,22 @@
       </c>
       <c r="CL3" t="inlineStr">
         <is>
+          <t>66.5</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
           <t>66.6</t>
-        </is>
-      </c>
-      <c r="CM3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="CN3" t="inlineStr">
-        <is>
-          <t>66.3</t>
-        </is>
-      </c>
-      <c r="CO3" t="inlineStr">
-        <is>
-          <t>66.4</t>
         </is>
       </c>
       <c r="CP3" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>88.077</t>
+          <t>64.21</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1862,69 +1862,69 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>-0.3</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>-6.12</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>10.14</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1947,7 +1947,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1992,22 +1992,22 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.04</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2025-12-10</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>22.30</t>
+          <t>16.26</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
@@ -2023,61 +2023,61 @@
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>81.82</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>51.52</t>
         </is>
       </c>
       <c r="AP4" t="n">
-        <v>0.82</v>
+        <v>0.3</v>
       </c>
       <c r="AQ4" t="n">
-        <v>-0.35</v>
+        <v>-0.14</v>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.84</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>66.06</t>
+          <t>66.20000000000002</t>
         </is>
       </c>
       <c r="AU4" t="n">
-        <v>66.29000000000001</v>
+        <v>66.3</v>
       </c>
       <c r="AV4" t="n">
-        <v>65.11</v>
+        <v>65.17</v>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>64.61</t>
+          <t>64.63</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>-26.17</t>
+          <t>-23.44</t>
         </is>
       </c>
       <c r="AY4" t="n">
         <v>0.27</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.37</v>
+        <v>0.35</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-73.37</t>
+          <t>-74.85</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
@@ -2096,43 +2096,43 @@
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>5851506.0</t>
+          <t>4274110.0</t>
         </is>
       </c>
       <c r="BF4" t="n">
-        <v>3092212.6</v>
+        <v>2770865.8</v>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>2807576.7</t>
+          <t>2951386.2</t>
         </is>
       </c>
       <c r="BH4" t="n">
-        <v>4754950.82</v>
+        <v>4790918.58</v>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>284635</t>
+          <t>-180520</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-382714.431245251</t>
+          <t>-343694.5748984399</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-242135.9659663578</t>
+          <t>-129085.364990979</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>5851506.0</t>
+          <t>4274110.0</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2152,7 +2152,7 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
@@ -2197,7 +2197,7 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2207,12 +2207,12 @@
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
@@ -2237,12 +2237,12 @@
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
@@ -2272,12 +2272,12 @@
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>65.9</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CO4" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CP4" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.61</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18.974</t>
+          <t>88.077</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2334,7 +2334,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1.2</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-13.70</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2409,7 +2409,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-1.20</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2454,22 +2454,22 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2025-12-09</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.80</t>
+          <t>22.30</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
@@ -2485,61 +2485,61 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>81.82</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AP5" t="n">
-        <v>-0.33</v>
+        <v>0.82</v>
       </c>
       <c r="AQ5" t="n">
-        <v>-0.33</v>
+        <v>-0.35</v>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>66.02000000000001</t>
+          <t>66.06</t>
         </is>
       </c>
       <c r="AU5" t="n">
-        <v>66.23999999999999</v>
+        <v>66.29000000000001</v>
       </c>
       <c r="AV5" t="n">
-        <v>65.06</v>
+        <v>65.11</v>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>64.59</t>
+          <t>64.61</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>-35.06</t>
+          <t>-26.17</t>
         </is>
       </c>
       <c r="AY5" t="n">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.4</v>
+        <v>0.37</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-71.63</t>
+          <t>-73.37</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
@@ -2558,43 +2558,43 @@
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>1247760.0</t>
+          <t>5851506.0</t>
         </is>
       </c>
       <c r="BF5" t="n">
-        <v>2222219.6</v>
+        <v>3092212.6</v>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>2575084.7</t>
+          <t>2807576.7</t>
         </is>
       </c>
       <c r="BH5" t="n">
-        <v>4689074.64</v>
+        <v>4754950.82</v>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-352865</t>
+          <t>284635</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-408274.1522050498</t>
+          <t>-382714.431245251</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>-563995.8257181002</t>
+          <t>-242135.9659663578</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1247760.0</t>
+          <t>5851506.0</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2614,7 +2614,7 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>1.23</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2659,22 +2659,22 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
@@ -2684,7 +2684,7 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
@@ -2699,12 +2699,12 @@
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
@@ -2724,22 +2724,22 @@
       </c>
       <c r="CL5" t="inlineStr">
         <is>
+          <t>66.1</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
-        <is>
-          <t>66.0</t>
-        </is>
-      </c>
-      <c r="CN5" t="inlineStr">
-        <is>
-          <t>65.6</t>
-        </is>
-      </c>
       <c r="CO5" t="inlineStr">
         <is>
-          <t>65.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CP5" t="inlineStr">
@@ -2771,12 +2771,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.61</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>22.824</t>
+          <t>18.974</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2786,7 +2786,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.21</t>
+          <t>-13.70</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2871,7 +2871,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.20</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2916,17 +2916,17 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>2025-12-08</t>
+          <t>2025-12-09</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>5.78</t>
+          <t>4.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2947,61 +2947,61 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>45.45</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>24.24</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AP6" t="n">
-        <v>-0.03</v>
+        <v>-0.33</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.01</v>
+        <v>-0.33</v>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>66.22</t>
+          <t>66.02000000000001</t>
         </is>
       </c>
       <c r="AU6" t="n">
-        <v>66.22</v>
+        <v>66.23999999999999</v>
       </c>
       <c r="AV6" t="n">
-        <v>65.01000000000001</v>
+        <v>65.06</v>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>64.55</t>
+          <t>64.59</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>-27.32</t>
+          <t>-35.06</t>
         </is>
       </c>
       <c r="AY6" t="n">
-        <v>0.31</v>
+        <v>0.26</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.43</v>
+        <v>0.4</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -3010,7 +3010,7 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-69.15</t>
+          <t>-71.63</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
@@ -3020,43 +3020,43 @@
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="BF6" t="n">
-        <v>2967914.4</v>
+        <v>2222219.6</v>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>2717507.9</t>
+          <t>2575084.7</t>
         </is>
       </c>
       <c r="BH6" t="n">
-        <v>4702861.12</v>
+        <v>4689074.64</v>
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>250406</t>
+          <t>-352865</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-379961.1206572224</t>
+          <t>-408274.1522050498</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>-510394.4173020865</t>
+          <t>-563995.8257181002</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1509985.0</t>
+          <t>1247760.0</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -3121,22 +3121,22 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
@@ -3161,12 +3161,12 @@
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
@@ -3186,22 +3186,22 @@
       </c>
       <c r="CL6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.9</t>
         </is>
       </c>
       <c r="CM6" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CN6" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CO6" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CP6" t="inlineStr">
@@ -3233,12 +3233,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>0.46</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14.779</t>
+          <t>22.824</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3248,7 +3248,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3258,7 +3258,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.9</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -3268,7 +3268,7 @@
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.90</t>
+          <t>9.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.90</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3378,22 +3378,22 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2025-12-05</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>5.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>0.61</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
@@ -3409,28 +3409,28 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>45.45</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>30.3</t>
+          <t>24.24</t>
         </is>
       </c>
       <c r="AP7" t="n">
-        <v>-0.36</v>
+        <v>-0.03</v>
       </c>
       <c r="AQ7" t="n">
-        <v>0.13</v>
+        <v>0.01</v>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.83</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3440,30 +3440,30 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>66.24000000000001</t>
+          <t>66.22</t>
         </is>
       </c>
       <c r="AU7" t="n">
-        <v>66.16</v>
+        <v>66.22</v>
       </c>
       <c r="AV7" t="n">
-        <v>64.97</v>
+        <v>65.01000000000001</v>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>64.5</t>
+          <t>64.55</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-26.34</t>
+          <t>-27.32</t>
         </is>
       </c>
       <c r="AY7" t="n">
-        <v>0.34</v>
+        <v>0.31</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.46</v>
+        <v>0.43</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3472,7 +3472,7 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-67.04</t>
+          <t>-69.15</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
@@ -3482,43 +3482,43 @@
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="BF7" t="n">
-        <v>2948729.4</v>
+        <v>2967914.4</v>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>3100620.6</t>
+          <t>2717507.9</t>
         </is>
       </c>
       <c r="BH7" t="n">
-        <v>4708957.14</v>
+        <v>4702861.12</v>
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-151891</t>
+          <t>250406</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-356245.9758127016</t>
+          <t>-379961.1206572224</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-443688.1403755629</t>
+          <t>-510394.4173020865</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>970968.0</t>
+          <t>1509985.0</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>1.54</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3583,22 +3583,22 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
@@ -3623,12 +3623,12 @@
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
@@ -3648,22 +3648,22 @@
       </c>
       <c r="CL7" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CM7" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CN7" t="inlineStr">
         <is>
-          <t>65.5</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CO7" t="inlineStr">
         <is>
-          <t>66.0</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CP7" t="inlineStr">
@@ -3695,12 +3695,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.05</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>89.077</t>
+          <t>14.779</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3710,124 +3710,124 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
+          <t>66.0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0.3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>-4.90</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1.35</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>-0.90</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>65.7</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>-1.35</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
       <c r="AD8" t="inlineStr">
         <is>
           <t>2025/07/02</t>
@@ -3840,22 +3840,22 @@
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.06</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2025-12-04</t>
+          <t>2025-12-05</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>22.55</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-1.22</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
@@ -3871,24 +3871,24 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>30.3</t>
         </is>
       </c>
       <c r="AP8" t="n">
-        <v>-0.99</v>
+        <v>-0.36</v>
       </c>
       <c r="AQ8" t="n">
-        <v>0.37</v>
+        <v>0.13</v>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
@@ -3897,35 +3897,35 @@
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>66.36</t>
+          <t>66.24000000000001</t>
         </is>
       </c>
       <c r="AU8" t="n">
-        <v>66.11</v>
+        <v>66.16</v>
       </c>
       <c r="AV8" t="n">
-        <v>64.92</v>
+        <v>64.97</v>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>64.46</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-20.99</t>
+          <t>-26.34</t>
         </is>
       </c>
       <c r="AY8" t="n">
-        <v>0.39</v>
+        <v>0.34</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.49</v>
+        <v>0.46</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-64.87</t>
+          <t>-67.04</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
@@ -3944,43 +3944,43 @@
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BF8" t="n">
-        <v>3131906.6</v>
+        <v>2948729.4</v>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>3260313.7</t>
+          <t>3100620.6</t>
         </is>
       </c>
       <c r="BH8" t="n">
-        <v>4743373.54</v>
+        <v>4708957.14</v>
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-128407</t>
+          <t>-151891</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-340347.400437636</t>
+          <t>-356245.9758127016</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-274795.6326099746</t>
+          <t>-443688.1403755629</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>5880844.0</t>
+          <t>970968.0</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>1.08</t>
+          <t>1.54</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -4045,12 +4045,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -4060,7 +4060,7 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
@@ -4070,7 +4070,7 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
@@ -4085,12 +4085,12 @@
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
@@ -4110,22 +4110,22 @@
       </c>
       <c r="CL8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CM8" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CN8" t="inlineStr">
         <is>
-          <t>65.6</t>
+          <t>65.5</t>
         </is>
       </c>
       <c r="CO8" t="inlineStr">
         <is>
-          <t>65.7</t>
+          <t>66.0</t>
         </is>
       </c>
       <c r="CP8" t="inlineStr">
@@ -4157,12 +4157,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.05</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>22.561</t>
+          <t>89.077</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -4172,7 +4172,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -4182,7 +4182,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -4192,7 +4192,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-14.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4302,22 +4302,22 @@
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>-0.02</t>
+          <t>-0.06</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>5.71</t>
+          <t>22.55</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
@@ -4333,61 +4333,61 @@
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>63.64</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>74.55</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AP9" t="n">
-        <v>-0.21</v>
+        <v>-0.99</v>
       </c>
       <c r="AQ9" t="n">
-        <v>0.64</v>
+        <v>0.37</v>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.89</t>
+          <t>1.83</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>66.54</t>
+          <t>66.36</t>
         </is>
       </c>
       <c r="AU9" t="n">
-        <v>66.12</v>
+        <v>66.11</v>
       </c>
       <c r="AV9" t="n">
-        <v>64.89</v>
+        <v>64.92</v>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>64.4</t>
+          <t>64.46</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-8.08</t>
+          <t>-20.99</t>
         </is>
       </c>
       <c r="AY9" t="n">
-        <v>0.47</v>
+        <v>0.39</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.52</v>
+        <v>0.49</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-63.03</t>
+          <t>-64.87</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
@@ -4406,43 +4406,43 @@
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="BF9" t="n">
-        <v>2522940.8</v>
+        <v>3131906.6</v>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>2938653.4</t>
+          <t>3260313.7</t>
         </is>
       </c>
       <c r="BH9" t="n">
-        <v>4638644.26</v>
+        <v>4743373.54</v>
       </c>
       <c r="BI9" t="inlineStr">
         <is>
-          <t>-415712</t>
+          <t>-128407</t>
         </is>
       </c>
       <c r="BJ9" t="inlineStr">
         <is>
-          <t>-352265.903679029</t>
+          <t>-340347.400437636</t>
         </is>
       </c>
       <c r="BK9" t="inlineStr">
         <is>
-          <t>-549764.6346373484</t>
+          <t>-274795.6326099746</t>
         </is>
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1501541.0</t>
+          <t>5880844.0</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.08</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4507,22 +4507,22 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
@@ -4532,7 +4532,7 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
@@ -4572,22 +4572,22 @@
       </c>
       <c r="CL9" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CM9" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="CN9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.6</t>
         </is>
       </c>
       <c r="CO9" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>65.7</t>
         </is>
       </c>
       <c r="CP9" t="inlineStr">
@@ -4619,12 +4619,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>74.845</t>
+          <t>22.561</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-5.95</t>
+          <t>-14.15</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.30</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4764,22 +4764,22 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>-0.02</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>18.95</t>
+          <t>5.71</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>1.06</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
@@ -4795,61 +4795,61 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>63.64</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>83.64</t>
+          <t>74.55</t>
         </is>
       </c>
       <c r="AP10" t="n">
-        <v>0.3</v>
+        <v>-0.21</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.78</v>
+        <v>0.64</v>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.89</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.81</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.54</t>
         </is>
       </c>
       <c r="AU10" t="n">
-        <v>66.09</v>
+        <v>66.12</v>
       </c>
       <c r="AV10" t="n">
-        <v>64.84999999999999</v>
+        <v>64.89</v>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>64.33</t>
+          <t>64.4</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>-3.69</t>
+          <t>-8.08</t>
         </is>
       </c>
       <c r="AY10" t="n">
-        <v>0.51</v>
+        <v>0.47</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.53</v>
+        <v>0.52</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4858,7 +4858,7 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-62.28</t>
+          <t>-63.03</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
@@ -4868,43 +4868,43 @@
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BF10" t="n">
-        <v>2927949.8</v>
+        <v>2522940.8</v>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>3113330.9</t>
+          <t>2938653.4</t>
         </is>
       </c>
       <c r="BH10" t="n">
-        <v>4657185.68</v>
+        <v>4638644.26</v>
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-185381</t>
+          <t>-415712</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-316357.043504789</t>
+          <t>-352265.903679029</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-453732.0077251205</t>
+          <t>-549764.6346373484</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>4976234.0</t>
+          <t>1501541.0</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4924,7 +4924,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>2.77</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4969,7 +4969,7 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4979,12 +4979,12 @@
       </c>
       <c r="CA10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
@@ -4994,7 +4994,7 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
@@ -5034,7 +5034,7 @@
       </c>
       <c r="CL10" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CM10" t="inlineStr">
@@ -5044,12 +5044,12 @@
       </c>
       <c r="CN10" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CO10" t="inlineStr">
         <is>
-          <t>66.8</t>
+          <t>66.4</t>
         </is>
       </c>
       <c r="CP10" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>21.309</t>
+          <t>74.845</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -5116,7 +5116,7 @@
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-17.11</t>
+          <t>-5.95</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>0.30</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -5226,22 +5226,22 @@
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>5.39</t>
+          <t>18.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>1.06</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
@@ -5257,58 +5257,58 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>60.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>80.61</t>
+          <t>83.64</t>
         </is>
       </c>
       <c r="AP11" t="n">
-        <v>-0.36</v>
+        <v>0.3</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.73</v>
+        <v>0.78</v>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>1.97</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>66.53999999999999</t>
+          <t>66.6</t>
         </is>
       </c>
       <c r="AU11" t="n">
-        <v>66.05</v>
+        <v>66.09</v>
       </c>
       <c r="AV11" t="n">
-        <v>64.78</v>
+        <v>64.84999999999999</v>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>64.26</t>
+          <t>64.33</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>-5.79</t>
+          <t>-3.69</t>
         </is>
       </c>
       <c r="AY11" t="n">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="AZ11" t="n">
         <v>0.53</v>
@@ -5320,7 +5320,7 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-61.93</t>
+          <t>-62.28</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
@@ -5330,43 +5330,43 @@
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BF11" t="n">
-        <v>2467101.4</v>
+        <v>2927949.8</v>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>2976246.7</t>
+          <t>3113330.9</t>
         </is>
       </c>
       <c r="BH11" t="n">
-        <v>4582639.88</v>
+        <v>4657185.68</v>
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>-509145</t>
+          <t>-185381</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-291379.7772829105</t>
+          <t>-316357.043504789</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-672626.3618603265</t>
+          <t>-453732.0077251205</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1414060.0</t>
+          <t>4976234.0</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5386,7 +5386,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.77</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
@@ -5471,12 +5471,12 @@
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
@@ -5496,22 +5496,22 @@
       </c>
       <c r="CL11" t="inlineStr">
         <is>
-          <t>66.4</t>
+          <t>66.2</t>
         </is>
       </c>
       <c r="CM11" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CN11" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.1</t>
         </is>
       </c>
       <c r="CO11" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>66.8</t>
         </is>
       </c>
       <c r="CP11" t="inlineStr">
@@ -5543,87 +5543,87 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
+          <t>-0.45</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>21.309</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>66.3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>-0.15</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>28.327</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>-17.11</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>-30.20</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R12" t="inlineStr">
-        <is>
-          <t>66.6</t>
-        </is>
-      </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>66.7</t>
+          <t>0</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
@@ -5638,12 +5638,12 @@
       </c>
       <c r="V12" t="inlineStr">
         <is>
-          <t>-0.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5688,22 +5688,22 @@
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>7.17</t>
+          <t>5.39</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
@@ -5719,61 +5719,61 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>49</t>
+          <t>16</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>90.91</t>
+          <t>60.0</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>93.94</t>
+          <t>80.61</t>
         </is>
       </c>
       <c r="AP12" t="n">
-        <v>0.06</v>
+        <v>-0.36</v>
       </c>
       <c r="AQ12" t="n">
-        <v>0.82</v>
+        <v>0.73</v>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.97</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
         <is>
-          <t>0.84</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>66.56000000000002</t>
+          <t>66.53999999999999</t>
         </is>
       </c>
       <c r="AU12" t="n">
-        <v>66.02</v>
+        <v>66.05</v>
       </c>
       <c r="AV12" t="n">
-        <v>64.73</v>
+        <v>64.78</v>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>64.19</t>
+          <t>64.26</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>-5.79</t>
         </is>
       </c>
       <c r="AY12" t="n">
-        <v>0.54</v>
+        <v>0.5</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.54</v>
+        <v>0.53</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5782,7 +5782,7 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-61.38</t>
+          <t>-61.93</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
@@ -5792,48 +5792,48 @@
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>7668542.729957806</t>
+          <t>7659946.919241574</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BF12" t="n">
-        <v>3252511.8</v>
+        <v>2467101.4</v>
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>4659887.2</t>
+          <t>2976246.7</t>
         </is>
       </c>
       <c r="BH12" t="n">
-        <v>4592706.68</v>
+        <v>4582639.88</v>
       </c>
       <c r="BI12" t="inlineStr">
         <is>
-          <t>-1407375</t>
+          <t>-509145</t>
         </is>
       </c>
       <c r="BJ12" t="inlineStr">
         <is>
-          <t>-222062.2164506531</t>
+          <t>-291379.7772829105</t>
         </is>
       </c>
       <c r="BK12" t="inlineStr">
         <is>
-          <t>-579648.7119870372</t>
+          <t>-672626.3618603265</t>
         </is>
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1886854.0</t>
+          <t>1414060.0</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5903,12 +5903,12 @@
       </c>
       <c r="CA12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="CB12" t="inlineStr">
         <is>
-          <t>6.01</t>
+          <t>6.04</t>
         </is>
       </c>
       <c r="CC12" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>12.11</t>
+          <t>12.04</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>41.09</t>
+          <t>41.03</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
         <is>
-          <t>7033</t>
+          <t>6990</t>
         </is>
       </c>
       <c r="CI12" t="inlineStr">
@@ -5958,14 +5958,14 @@
       </c>
       <c r="CL12" t="inlineStr">
         <is>
+          <t>66.4</t>
+        </is>
+      </c>
+      <c r="CM12" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
-        <is>
-          <t>66.8</t>
-        </is>
-      </c>
       <c r="CN12" t="inlineStr">
         <is>
           <t>66.3</t>
@@ -5973,7 +5973,7 @@
       </c>
       <c r="CO12" t="inlineStr">
         <is>
-          <t>66.6</t>
+          <t>66.3</t>
         </is>
       </c>
       <c r="CP12" t="inlineStr">

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CR12"/>
+  <dimension ref="A1:CV12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -566,345 +566,365 @@
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
+          <t>MACD_hist_diff</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
           <t>MA_death_cross_d</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d收盤價</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>MA_death_cross_d2收盤價</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
-        <is>
-          <t>MACD_hist_diff</t>
-        </is>
-      </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
+          <t>MACD_death_cross_d</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d收盤價</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>MACD_death_cross_d2收盤價</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
           <t>日期</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>量能</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>價能</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>cond_entry</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>text_desc</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>盤後量</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>成交量</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>%K</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>%D</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>MA5_%</t>
         </is>
       </c>
-      <c r="AQ1" s="1" t="inlineStr">
+      <c r="AU1" s="1" t="inlineStr">
         <is>
           <t>均價_%</t>
         </is>
       </c>
-      <c r="AR1" s="1" t="inlineStr">
+      <c r="AV1" s="1" t="inlineStr">
         <is>
           <t>均價long_%</t>
         </is>
       </c>
-      <c r="AS1" s="1" t="inlineStr">
+      <c r="AW1" s="1" t="inlineStr">
         <is>
           <t>均價longlong_%</t>
         </is>
       </c>
-      <c r="AT1" s="1" t="inlineStr">
+      <c r="AX1" s="1" t="inlineStr">
         <is>
           <t>MA_short</t>
         </is>
       </c>
-      <c r="AU1" s="1" t="inlineStr">
+      <c r="AY1" s="1" t="inlineStr">
         <is>
           <t>MA_long</t>
         </is>
       </c>
-      <c r="AV1" s="1" t="inlineStr">
+      <c r="AZ1" s="1" t="inlineStr">
         <is>
           <t>MA_longlong</t>
         </is>
       </c>
-      <c r="AW1" s="1" t="inlineStr">
+      <c r="BA1" s="1" t="inlineStr">
         <is>
           <t>MA_longlonglong</t>
         </is>
       </c>
-      <c r="AX1" s="1" t="inlineStr">
+      <c r="BB1" s="1" t="inlineStr">
         <is>
           <t>MACD_%</t>
         </is>
       </c>
-      <c r="AY1" s="1" t="inlineStr">
+      <c r="BC1" s="1" t="inlineStr">
         <is>
           <t>MACD</t>
         </is>
       </c>
-      <c r="AZ1" s="1" t="inlineStr">
+      <c r="BD1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL</t>
         </is>
       </c>
-      <c r="BA1" s="1" t="inlineStr">
+      <c r="BE1" s="1" t="inlineStr">
         <is>
           <t>MACD-SL_max</t>
         </is>
       </c>
-      <c r="BB1" s="1" t="inlineStr">
+      <c r="BF1" s="1" t="inlineStr">
         <is>
           <t>MACDSL_%</t>
         </is>
       </c>
-      <c r="BC1" s="1" t="inlineStr">
+      <c r="BG1" s="1" t="inlineStr">
         <is>
           <t>MACD_last_cross_date</t>
         </is>
       </c>
-      <c r="BD1" s="1" t="inlineStr">
+      <c r="BH1" s="1" t="inlineStr">
         <is>
           <t>成交金額平均</t>
         </is>
       </c>
-      <c r="BE1" s="1" t="inlineStr">
+      <c r="BI1" s="1" t="inlineStr">
         <is>
           <t>成交金額</t>
         </is>
       </c>
-      <c r="BF1" s="1" t="inlineStr">
+      <c r="BJ1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_short</t>
         </is>
       </c>
-      <c r="BG1" s="1" t="inlineStr">
+      <c r="BK1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long</t>
         </is>
       </c>
-      <c r="BH1" s="1" t="inlineStr">
+      <c r="BL1" s="1" t="inlineStr">
         <is>
           <t>Volume_MA_long50</t>
         </is>
       </c>
-      <c r="BI1" s="1" t="inlineStr">
+      <c r="BM1" s="1" t="inlineStr">
         <is>
           <t>Volume_Oscillator</t>
         </is>
       </c>
-      <c r="BJ1" s="1" t="inlineStr">
+      <c r="BN1" s="1" t="inlineStr">
         <is>
           <t>volume_threshold</t>
         </is>
       </c>
-      <c r="BK1" s="1" t="inlineStr">
+      <c r="BO1" s="1" t="inlineStr">
         <is>
           <t>VPC_MACD</t>
         </is>
       </c>
-      <c r="BL1" s="1" t="inlineStr">
+      <c r="BP1" s="1" t="inlineStr">
         <is>
           <t>Volume_Price_Change</t>
         </is>
       </c>
-      <c r="BM1" s="1" t="inlineStr">
+      <c r="BQ1" s="1" t="inlineStr">
         <is>
           <t>highlight_enddate</t>
         </is>
       </c>
-      <c r="BN1" s="1" t="inlineStr">
+      <c r="BR1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date收盤價</t>
         </is>
       </c>
-      <c r="BO1" s="1" t="inlineStr">
+      <c r="BS1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_date</t>
         </is>
       </c>
-      <c r="BP1" s="1" t="inlineStr">
+      <c r="BT1" s="1" t="inlineStr">
         <is>
           <t>MA_last_cross_%</t>
         </is>
       </c>
-      <c r="BQ1" s="1" t="inlineStr">
+      <c r="BU1" s="1" t="inlineStr">
         <is>
           <t>stock_name</t>
         </is>
       </c>
-      <c r="BR1" s="1" t="inlineStr">
+      <c r="BV1" s="1" t="inlineStr">
         <is>
           <t>Type0</t>
         </is>
       </c>
-      <c r="BS1" s="1" t="inlineStr">
+      <c r="BW1" s="1" t="inlineStr">
         <is>
           <t>Type1</t>
         </is>
       </c>
-      <c r="BT1" s="1" t="inlineStr">
+      <c r="BX1" s="1" t="inlineStr">
         <is>
           <t>Type2</t>
         </is>
       </c>
-      <c r="BU1" s="1" t="inlineStr">
+      <c r="BY1" s="1" t="inlineStr">
         <is>
           <t>貝他值</t>
         </is>
       </c>
-      <c r="BV1" s="1" t="inlineStr">
+      <c r="BZ1" s="1" t="inlineStr">
         <is>
           <t>營業收入-上月比較增減(%)</t>
         </is>
       </c>
-      <c r="BW1" s="1" t="inlineStr">
+      <c r="CA1" s="1" t="inlineStr">
         <is>
           <t>營業收入-去年同月增減(%)</t>
         </is>
       </c>
-      <c r="BX1" s="1" t="inlineStr">
+      <c r="CB1" s="1" t="inlineStr">
         <is>
           <t>累計營業收入-前期比較增減(%)</t>
         </is>
       </c>
-      <c r="BY1" s="1" t="inlineStr">
+      <c r="CC1" s="1" t="inlineStr">
         <is>
           <t>Full_Summary</t>
         </is>
       </c>
-      <c r="BZ1" s="1" t="inlineStr">
+      <c r="CD1" s="1" t="inlineStr">
         <is>
           <t>textdesc</t>
         </is>
       </c>
-      <c r="CA1" s="1" t="inlineStr">
+      <c r="CE1" s="1" t="inlineStr">
         <is>
           <t>淨值倍率</t>
         </is>
       </c>
-      <c r="CB1" s="1" t="inlineStr">
+      <c r="CF1" s="1" t="inlineStr">
         <is>
           <t>殖利率</t>
         </is>
       </c>
-      <c r="CC1" s="1" t="inlineStr">
+      <c r="CG1" s="1" t="inlineStr">
         <is>
           <t>每股營收(元)</t>
         </is>
       </c>
-      <c r="CD1" s="1" t="inlineStr">
+      <c r="CH1" s="1" t="inlineStr">
         <is>
           <t>本益比</t>
         </is>
       </c>
-      <c r="CE1" s="1" t="inlineStr">
+      <c r="CI1" s="1" t="inlineStr">
         <is>
           <t>營業毛利率</t>
         </is>
       </c>
-      <c r="CF1" s="1" t="inlineStr">
+      <c r="CJ1" s="1" t="inlineStr">
         <is>
           <t>營業利益率</t>
         </is>
       </c>
-      <c r="CG1" s="1" t="inlineStr">
+      <c r="CK1" s="1" t="inlineStr">
         <is>
           <t>同業平均本益比</t>
         </is>
       </c>
-      <c r="CH1" s="1" t="inlineStr">
+      <c r="CL1" s="1" t="inlineStr">
         <is>
           <t>總市值</t>
         </is>
       </c>
-      <c r="CI1" s="1" t="inlineStr">
+      <c r="CM1" s="1" t="inlineStr">
         <is>
           <t>營收比重</t>
         </is>
       </c>
-      <c r="CJ1" s="1" t="inlineStr">
+      <c r="CN1" s="1" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="CK1" s="1" t="inlineStr">
+      <c r="CO1" s="1" t="inlineStr">
         <is>
           <t>Typelevel</t>
         </is>
       </c>
-      <c r="CL1" s="1" t="inlineStr">
+      <c r="CP1" s="1" t="inlineStr">
         <is>
           <t>開盤價</t>
         </is>
       </c>
-      <c r="CM1" s="1" t="inlineStr">
+      <c r="CQ1" s="1" t="inlineStr">
         <is>
           <t>最高價</t>
         </is>
       </c>
-      <c r="CN1" s="1" t="inlineStr">
+      <c r="CR1" s="1" t="inlineStr">
         <is>
           <t>最低價</t>
         </is>
       </c>
-      <c r="CO1" s="1" t="inlineStr">
+      <c r="CS1" s="1" t="inlineStr">
         <is>
           <t>收盤價</t>
         </is>
       </c>
-      <c r="CP1" s="1" t="inlineStr">
+      <c r="CT1" s="1" t="inlineStr">
         <is>
           <t>每股淨值(元)</t>
         </is>
       </c>
-      <c r="CQ1" s="1" t="inlineStr">
+      <c r="CU1" s="1" t="inlineStr">
         <is>
           <t>desc</t>
         </is>
       </c>
-      <c r="CR1" s="1" t="inlineStr">
+      <c r="CV1" s="1" t="inlineStr">
         <is>
           <t>flag_stat</t>
         </is>
@@ -1048,325 +1068,345 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AD2" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>-0.01</t>
-        </is>
-      </c>
       <c r="AG2" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
           <t>2025-12-15</t>
         </is>
       </c>
-      <c r="AH2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>3.95</t>
         </is>
       </c>
-      <c r="AI2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ2" t="inlineStr">
+      <c r="AN2" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK2" t="inlineStr"/>
-      <c r="AL2" t="inlineStr">
+      <c r="AO2" t="inlineStr"/>
+      <c r="AP2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
+      <c r="AQ2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN2" t="inlineStr">
+      <c r="AR2" t="inlineStr">
         <is>
           <t>55.56</t>
         </is>
       </c>
-      <c r="AO2" t="inlineStr">
+      <c r="AS2" t="inlineStr">
         <is>
           <t>67.0</t>
         </is>
       </c>
-      <c r="AP2" t="n">
+      <c r="AT2" t="n">
         <v>-0.18</v>
       </c>
-      <c r="AQ2" t="n">
+      <c r="AU2" t="n">
         <v>0.08</v>
       </c>
-      <c r="AR2" t="inlineStr">
+      <c r="AV2" t="inlineStr">
         <is>
           <t>1.52</t>
         </is>
       </c>
-      <c r="AS2" t="inlineStr">
+      <c r="AW2" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="AT2" t="inlineStr">
+      <c r="AX2" t="inlineStr">
         <is>
           <t>66.32000000000001</t>
         </is>
       </c>
-      <c r="AU2" t="n">
+      <c r="AY2" t="n">
         <v>66.27</v>
       </c>
-      <c r="AV2" t="n">
+      <c r="AZ2" t="n">
         <v>65.28</v>
       </c>
-      <c r="AW2" t="inlineStr">
+      <c r="BA2" t="inlineStr">
         <is>
           <t>64.69</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
+      <c r="BB2" t="inlineStr">
         <is>
           <t>-21.94</t>
         </is>
       </c>
-      <c r="AY2" t="n">
+      <c r="BC2" t="n">
         <v>0.25</v>
       </c>
-      <c r="AZ2" t="n">
+      <c r="BD2" t="n">
         <v>0.32</v>
       </c>
-      <c r="BA2" t="inlineStr">
+      <c r="BE2" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB2" t="inlineStr">
+      <c r="BF2" t="inlineStr">
         <is>
           <t>-77.16</t>
         </is>
       </c>
-      <c r="BC2" t="inlineStr">
+      <c r="BG2" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD2" t="inlineStr">
+      <c r="BH2" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE2" t="inlineStr">
+      <c r="BI2" t="inlineStr">
         <is>
           <t>1032217.0</t>
         </is>
       </c>
-      <c r="BF2" t="n">
+      <c r="BJ2" t="n">
         <v>3129239.4</v>
       </c>
-      <c r="BG2" t="inlineStr">
+      <c r="BK2" t="inlineStr">
         <is>
           <t>3048576.9</t>
         </is>
       </c>
-      <c r="BH2" t="n">
+      <c r="BL2" t="n">
         <v>4778355.32</v>
       </c>
-      <c r="BI2" t="inlineStr">
+      <c r="BM2" t="inlineStr">
         <is>
           <t>80662</t>
         </is>
       </c>
-      <c r="BJ2" t="inlineStr">
+      <c r="BN2" t="inlineStr">
         <is>
           <t>-305844.3707094667</t>
         </is>
       </c>
-      <c r="BK2" t="inlineStr">
+      <c r="BO2" t="inlineStr">
         <is>
           <t>-283364.1678135758</t>
         </is>
       </c>
-      <c r="BL2" t="inlineStr">
+      <c r="BP2" t="inlineStr">
         <is>
           <t>1032217.0</t>
         </is>
       </c>
-      <c r="BM2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN2" t="inlineStr">
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO2" t="inlineStr">
+      <c r="BS2" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP2" t="inlineStr">
+      <c r="BT2" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="BQ2" t="inlineStr">
+      <c r="BU2" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR2" t="inlineStr">
+      <c r="BV2" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS2" t="inlineStr">
+      <c r="BW2" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT2" t="inlineStr">
+      <c r="BX2" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU2" t="inlineStr">
+      <c r="BY2" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV2" t="inlineStr">
+      <c r="BZ2" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW2" t="inlineStr">
+      <c r="CA2" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX2" t="inlineStr">
+      <c r="CB2" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY2" t="inlineStr">
+      <c r="CC2" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ2" t="inlineStr">
+      <c r="CD2" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA2" t="inlineStr">
+      <c r="CE2" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="CB2" t="inlineStr">
+      <c r="CF2" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC2" t="inlineStr">
+      <c r="CG2" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD2" t="inlineStr">
+      <c r="CH2" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE2" t="inlineStr">
+      <c r="CI2" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF2" t="inlineStr">
+      <c r="CJ2" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG2" t="inlineStr">
+      <c r="CK2" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH2" t="inlineStr">
+      <c r="CL2" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI2" t="inlineStr">
+      <c r="CM2" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ2" t="inlineStr">
+      <c r="CN2" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK2" t="inlineStr">
+      <c r="CO2" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL2" t="inlineStr">
+      <c r="CP2" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="CM2" t="inlineStr">
+      <c r="CQ2" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="CN2" t="inlineStr">
+      <c r="CR2" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CO2" t="inlineStr">
+      <c r="CS2" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="CP2" t="inlineStr">
+      <c r="CT2" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ2" t="inlineStr">
+      <c r="CU2" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR2" t="inlineStr">
+      <c r="CV2" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1510,325 +1550,345 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
+          <t>0.02</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
       <c r="AG3" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
           <t>2025-12-12</t>
         </is>
       </c>
-      <c r="AH3" t="inlineStr">
+      <c r="AL3" t="inlineStr">
         <is>
           <t>12.32</t>
         </is>
       </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.30</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
+      <c r="AN3" t="inlineStr">
         <is>
           <t>True</t>
         </is>
       </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr">
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
+      <c r="AQ3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN3" t="inlineStr">
+      <c r="AR3" t="inlineStr">
         <is>
           <t>81.82</t>
         </is>
       </c>
-      <c r="AO3" t="inlineStr">
+      <c r="AS3" t="inlineStr">
         <is>
           <t>75.76</t>
         </is>
       </c>
-      <c r="AP3" t="n">
+      <c r="AT3" t="n">
         <v>0.42</v>
       </c>
-      <c r="AQ3" t="n">
+      <c r="AU3" t="n">
         <v>0.04</v>
       </c>
-      <c r="AR3" t="inlineStr">
+      <c r="AV3" t="inlineStr">
         <is>
           <t>1.63</t>
         </is>
       </c>
-      <c r="AS3" t="inlineStr">
+      <c r="AW3" t="inlineStr">
         <is>
           <t>0.89</t>
         </is>
       </c>
-      <c r="AT3" t="inlineStr">
+      <c r="AX3" t="inlineStr">
         <is>
           <t>66.32000000000001</t>
         </is>
       </c>
-      <c r="AU3" t="n">
+      <c r="AY3" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="AV3" t="n">
+      <c r="AZ3" t="n">
         <v>65.23</v>
       </c>
-      <c r="AW3" t="inlineStr">
+      <c r="BA3" t="inlineStr">
         <is>
           <t>64.66</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
+      <c r="BB3" t="inlineStr">
         <is>
           <t>-17.54</t>
         </is>
       </c>
-      <c r="AY3" t="n">
+      <c r="BC3" t="n">
         <v>0.28</v>
       </c>
-      <c r="AZ3" t="n">
+      <c r="BD3" t="n">
         <v>0.34</v>
       </c>
-      <c r="BA3" t="inlineStr">
+      <c r="BE3" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB3" t="inlineStr">
+      <c r="BF3" t="inlineStr">
         <is>
           <t>-75.91</t>
         </is>
       </c>
-      <c r="BC3" t="inlineStr">
+      <c r="BG3" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="BH3" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE3" t="inlineStr">
+      <c r="BI3" t="inlineStr">
         <is>
           <t>3240604.0</t>
         </is>
       </c>
-      <c r="BF3" t="n">
+      <c r="BJ3" t="n">
         <v>3224793</v>
       </c>
-      <c r="BG3" t="inlineStr">
+      <c r="BK3" t="inlineStr">
         <is>
           <t>3086761.2</t>
         </is>
       </c>
-      <c r="BH3" t="n">
+      <c r="BL3" t="n">
         <v>4840807.66</v>
       </c>
-      <c r="BI3" t="inlineStr">
+      <c r="BM3" t="inlineStr">
         <is>
           <t>138031</t>
         </is>
       </c>
-      <c r="BJ3" t="inlineStr">
+      <c r="BN3" t="inlineStr">
         <is>
           <t>-309931.6803269014</t>
         </is>
       </c>
-      <c r="BK3" t="inlineStr">
+      <c r="BO3" t="inlineStr">
         <is>
           <t>-124235.7601834396</t>
         </is>
       </c>
-      <c r="BL3" t="inlineStr">
+      <c r="BP3" t="inlineStr">
         <is>
           <t>3240604.0</t>
         </is>
       </c>
-      <c r="BM3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN3" t="inlineStr">
+      <c r="BQ3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR3" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO3" t="inlineStr">
+      <c r="BS3" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP3" t="inlineStr">
+      <c r="BT3" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="BQ3" t="inlineStr">
+      <c r="BU3" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR3" t="inlineStr">
+      <c r="BV3" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS3" t="inlineStr">
+      <c r="BW3" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT3" t="inlineStr">
+      <c r="BX3" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU3" t="inlineStr">
+      <c r="BY3" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV3" t="inlineStr">
+      <c r="BZ3" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW3" t="inlineStr">
+      <c r="CA3" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX3" t="inlineStr">
+      <c r="CB3" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY3" t="inlineStr">
+      <c r="CC3" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ3" t="inlineStr">
+      <c r="CD3" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA3" t="inlineStr">
+      <c r="CE3" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="CB3" t="inlineStr">
+      <c r="CF3" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC3" t="inlineStr">
+      <c r="CG3" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD3" t="inlineStr">
+      <c r="CH3" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE3" t="inlineStr">
+      <c r="CI3" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF3" t="inlineStr">
+      <c r="CJ3" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG3" t="inlineStr">
+      <c r="CK3" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH3" t="inlineStr">
+      <c r="CL3" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI3" t="inlineStr">
+      <c r="CM3" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ3" t="inlineStr">
+      <c r="CN3" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK3" t="inlineStr">
+      <c r="CO3" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL3" t="inlineStr">
+      <c r="CP3" t="inlineStr">
         <is>
           <t>66.5</t>
         </is>
       </c>
-      <c r="CM3" t="inlineStr">
+      <c r="CQ3" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="CN3" t="inlineStr">
+      <c r="CR3" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="CO3" t="inlineStr">
+      <c r="CS3" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CP3" t="inlineStr">
+      <c r="CT3" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ3" t="inlineStr">
+      <c r="CU3" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR3" t="inlineStr">
+      <c r="CV3" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -1972,325 +2032,345 @@
       </c>
       <c r="AB4" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AD4" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD4" t="inlineStr">
+      <c r="AE4" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG4" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
           <t>2025-12-11</t>
         </is>
       </c>
-      <c r="AH4" t="inlineStr">
+      <c r="AL4" t="inlineStr">
         <is>
           <t>16.26</t>
         </is>
       </c>
-      <c r="AI4" t="inlineStr">
+      <c r="AM4" t="inlineStr">
         <is>
           <t>-0.30</t>
         </is>
       </c>
-      <c r="AJ4" t="inlineStr">
+      <c r="AN4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK4" t="inlineStr"/>
-      <c r="AL4" t="inlineStr">
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
+      <c r="AQ4" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN4" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>63.64</t>
         </is>
       </c>
-      <c r="AO4" t="inlineStr">
+      <c r="AS4" t="inlineStr">
         <is>
           <t>51.52</t>
         </is>
       </c>
-      <c r="AP4" t="n">
+      <c r="AT4" t="n">
         <v>0.3</v>
       </c>
-      <c r="AQ4" t="n">
+      <c r="AU4" t="n">
         <v>-0.14</v>
       </c>
-      <c r="AR4" t="inlineStr">
+      <c r="AV4" t="inlineStr">
         <is>
           <t>1.73</t>
         </is>
       </c>
-      <c r="AS4" t="inlineStr">
+      <c r="AW4" t="inlineStr">
         <is>
           <t>0.84</t>
         </is>
       </c>
-      <c r="AT4" t="inlineStr">
+      <c r="AX4" t="inlineStr">
         <is>
           <t>66.20000000000002</t>
         </is>
       </c>
-      <c r="AU4" t="n">
+      <c r="AY4" t="n">
         <v>66.3</v>
       </c>
-      <c r="AV4" t="n">
+      <c r="AZ4" t="n">
         <v>65.17</v>
       </c>
-      <c r="AW4" t="inlineStr">
+      <c r="BA4" t="inlineStr">
         <is>
           <t>64.63</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
+      <c r="BB4" t="inlineStr">
         <is>
           <t>-23.44</t>
         </is>
       </c>
-      <c r="AY4" t="n">
+      <c r="BC4" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ4" t="n">
+      <c r="BD4" t="n">
         <v>0.35</v>
       </c>
-      <c r="BA4" t="inlineStr">
+      <c r="BE4" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB4" t="inlineStr">
+      <c r="BF4" t="inlineStr">
         <is>
           <t>-74.85</t>
         </is>
       </c>
-      <c r="BC4" t="inlineStr">
+      <c r="BG4" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD4" t="inlineStr">
+      <c r="BH4" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE4" t="inlineStr">
+      <c r="BI4" t="inlineStr">
         <is>
           <t>4274110.0</t>
         </is>
       </c>
-      <c r="BF4" t="n">
+      <c r="BJ4" t="n">
         <v>2770865.8</v>
       </c>
-      <c r="BG4" t="inlineStr">
+      <c r="BK4" t="inlineStr">
         <is>
           <t>2951386.2</t>
         </is>
       </c>
-      <c r="BH4" t="n">
+      <c r="BL4" t="n">
         <v>4790918.58</v>
       </c>
-      <c r="BI4" t="inlineStr">
+      <c r="BM4" t="inlineStr">
         <is>
           <t>-180520</t>
         </is>
       </c>
-      <c r="BJ4" t="inlineStr">
+      <c r="BN4" t="inlineStr">
         <is>
           <t>-343694.5748984399</t>
         </is>
       </c>
-      <c r="BK4" t="inlineStr">
+      <c r="BO4" t="inlineStr">
         <is>
           <t>-129085.364990979</t>
         </is>
       </c>
-      <c r="BL4" t="inlineStr">
+      <c r="BP4" t="inlineStr">
         <is>
           <t>4274110.0</t>
         </is>
       </c>
-      <c r="BM4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN4" t="inlineStr">
+      <c r="BQ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR4" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO4" t="inlineStr">
+      <c r="BS4" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP4" t="inlineStr">
+      <c r="BT4" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="BQ4" t="inlineStr">
+      <c r="BU4" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR4" t="inlineStr">
+      <c r="BV4" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS4" t="inlineStr">
+      <c r="BW4" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT4" t="inlineStr">
+      <c r="BX4" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU4" t="inlineStr">
+      <c r="BY4" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV4" t="inlineStr">
+      <c r="BZ4" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW4" t="inlineStr">
+      <c r="CA4" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX4" t="inlineStr">
+      <c r="CB4" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY4" t="inlineStr">
+      <c r="CC4" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ4" t="inlineStr">
+      <c r="CD4" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA4" t="inlineStr">
+      <c r="CE4" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="CB4" t="inlineStr">
+      <c r="CF4" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC4" t="inlineStr">
+      <c r="CG4" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD4" t="inlineStr">
+      <c r="CH4" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE4" t="inlineStr">
+      <c r="CI4" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF4" t="inlineStr">
+      <c r="CJ4" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG4" t="inlineStr">
+      <c r="CK4" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH4" t="inlineStr">
+      <c r="CL4" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI4" t="inlineStr">
+      <c r="CM4" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ4" t="inlineStr">
+      <c r="CN4" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK4" t="inlineStr">
+      <c r="CO4" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL4" t="inlineStr">
+      <c r="CP4" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CM4" t="inlineStr">
+      <c r="CQ4" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="CN4" t="inlineStr">
+      <c r="CR4" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="CO4" t="inlineStr">
+      <c r="CS4" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CP4" t="inlineStr">
+      <c r="CT4" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ4" t="inlineStr">
+      <c r="CU4" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR4" t="inlineStr">
+      <c r="CV4" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2434,325 +2514,345 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
+          <t>0.04</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AE5" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
+      <c r="AF5" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>0.04</t>
-        </is>
-      </c>
       <c r="AG5" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
           <t>2025-12-10</t>
         </is>
       </c>
-      <c r="AH5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>22.30</t>
         </is>
       </c>
-      <c r="AI5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>0.91</t>
         </is>
       </c>
-      <c r="AJ5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr">
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>81.82</t>
         </is>
       </c>
-      <c r="AO5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>45.45</t>
         </is>
       </c>
-      <c r="AP5" t="n">
+      <c r="AT5" t="n">
         <v>0.82</v>
       </c>
-      <c r="AQ5" t="n">
+      <c r="AU5" t="n">
         <v>-0.35</v>
       </c>
-      <c r="AR5" t="inlineStr">
+      <c r="AV5" t="inlineStr">
         <is>
           <t>1.81</t>
         </is>
       </c>
-      <c r="AS5" t="inlineStr">
+      <c r="AW5" t="inlineStr">
         <is>
           <t>0.78</t>
         </is>
       </c>
-      <c r="AT5" t="inlineStr">
+      <c r="AX5" t="inlineStr">
         <is>
           <t>66.06</t>
         </is>
       </c>
-      <c r="AU5" t="n">
+      <c r="AY5" t="n">
         <v>66.29000000000001</v>
       </c>
-      <c r="AV5" t="n">
+      <c r="AZ5" t="n">
         <v>65.11</v>
       </c>
-      <c r="AW5" t="inlineStr">
+      <c r="BA5" t="inlineStr">
         <is>
           <t>64.61</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="BB5" t="inlineStr">
         <is>
           <t>-26.17</t>
         </is>
       </c>
-      <c r="AY5" t="n">
+      <c r="BC5" t="n">
         <v>0.27</v>
       </c>
-      <c r="AZ5" t="n">
+      <c r="BD5" t="n">
         <v>0.37</v>
       </c>
-      <c r="BA5" t="inlineStr">
+      <c r="BE5" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB5" t="inlineStr">
+      <c r="BF5" t="inlineStr">
         <is>
           <t>-73.37</t>
         </is>
       </c>
-      <c r="BC5" t="inlineStr">
+      <c r="BG5" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD5" t="inlineStr">
+      <c r="BH5" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE5" t="inlineStr">
+      <c r="BI5" t="inlineStr">
         <is>
           <t>5851506.0</t>
         </is>
       </c>
-      <c r="BF5" t="n">
+      <c r="BJ5" t="n">
         <v>3092212.6</v>
       </c>
-      <c r="BG5" t="inlineStr">
+      <c r="BK5" t="inlineStr">
         <is>
           <t>2807576.7</t>
         </is>
       </c>
-      <c r="BH5" t="n">
+      <c r="BL5" t="n">
         <v>4754950.82</v>
       </c>
-      <c r="BI5" t="inlineStr">
+      <c r="BM5" t="inlineStr">
         <is>
           <t>284635</t>
         </is>
       </c>
-      <c r="BJ5" t="inlineStr">
+      <c r="BN5" t="inlineStr">
         <is>
           <t>-382714.431245251</t>
         </is>
       </c>
-      <c r="BK5" t="inlineStr">
+      <c r="BO5" t="inlineStr">
         <is>
           <t>-242135.9659663578</t>
         </is>
       </c>
-      <c r="BL5" t="inlineStr">
+      <c r="BP5" t="inlineStr">
         <is>
           <t>5851506.0</t>
         </is>
       </c>
-      <c r="BM5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN5" t="inlineStr">
+      <c r="BQ5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR5" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO5" t="inlineStr">
+      <c r="BS5" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP5" t="inlineStr">
+      <c r="BT5" t="inlineStr">
         <is>
           <t>2.46</t>
         </is>
       </c>
-      <c r="BQ5" t="inlineStr">
+      <c r="BU5" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR5" t="inlineStr">
+      <c r="BV5" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS5" t="inlineStr">
+      <c r="BW5" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT5" t="inlineStr">
+      <c r="BX5" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU5" t="inlineStr">
+      <c r="BY5" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV5" t="inlineStr">
+      <c r="BZ5" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW5" t="inlineStr">
+      <c r="CA5" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX5" t="inlineStr">
+      <c r="CB5" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY5" t="inlineStr">
+      <c r="CC5" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ5" t="inlineStr">
+      <c r="CD5" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA5" t="inlineStr">
+      <c r="CE5" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="CB5" t="inlineStr">
+      <c r="CF5" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC5" t="inlineStr">
+      <c r="CG5" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD5" t="inlineStr">
+      <c r="CH5" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE5" t="inlineStr">
+      <c r="CI5" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF5" t="inlineStr">
+      <c r="CJ5" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG5" t="inlineStr">
+      <c r="CK5" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH5" t="inlineStr">
+      <c r="CL5" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI5" t="inlineStr">
+      <c r="CM5" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ5" t="inlineStr">
+      <c r="CN5" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK5" t="inlineStr">
+      <c r="CO5" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL5" t="inlineStr">
+      <c r="CP5" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CM5" t="inlineStr">
+      <c r="CQ5" t="inlineStr">
         <is>
           <t>66.7</t>
         </is>
       </c>
-      <c r="CN5" t="inlineStr">
+      <c r="CR5" t="inlineStr">
         <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="CO5" t="inlineStr">
+      <c r="CS5" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CP5" t="inlineStr">
+      <c r="CT5" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ5" t="inlineStr">
+      <c r="CU5" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR5" t="inlineStr">
+      <c r="CV5" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -2896,325 +2996,345 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD6" t="inlineStr">
+      <c r="AE6" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE6" t="inlineStr">
+      <c r="AF6" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG6" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
           <t>2025-12-09</t>
         </is>
       </c>
-      <c r="AH6" t="inlineStr">
+      <c r="AL6" t="inlineStr">
         <is>
           <t>4.80</t>
         </is>
       </c>
-      <c r="AI6" t="inlineStr">
+      <c r="AM6" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ6" t="inlineStr">
+      <c r="AN6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK6" t="inlineStr"/>
-      <c r="AL6" t="inlineStr">
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
+      <c r="AQ6" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN6" t="inlineStr">
+      <c r="AR6" t="inlineStr">
         <is>
           <t>9.09</t>
         </is>
       </c>
-      <c r="AO6" t="inlineStr">
+      <c r="AS6" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AP6" t="n">
+      <c r="AT6" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AQ6" t="n">
+      <c r="AU6" t="n">
         <v>-0.33</v>
       </c>
-      <c r="AR6" t="inlineStr">
+      <c r="AV6" t="inlineStr">
         <is>
           <t>1.82</t>
         </is>
       </c>
-      <c r="AS6" t="inlineStr">
+      <c r="AW6" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="AT6" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>66.02000000000001</t>
         </is>
       </c>
-      <c r="AU6" t="n">
+      <c r="AY6" t="n">
         <v>66.23999999999999</v>
       </c>
-      <c r="AV6" t="n">
+      <c r="AZ6" t="n">
         <v>65.06</v>
       </c>
-      <c r="AW6" t="inlineStr">
+      <c r="BA6" t="inlineStr">
         <is>
           <t>64.59</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
+      <c r="BB6" t="inlineStr">
         <is>
           <t>-35.06</t>
         </is>
       </c>
-      <c r="AY6" t="n">
+      <c r="BC6" t="n">
         <v>0.26</v>
       </c>
-      <c r="AZ6" t="n">
+      <c r="BD6" t="n">
         <v>0.4</v>
       </c>
-      <c r="BA6" t="inlineStr">
+      <c r="BE6" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB6" t="inlineStr">
+      <c r="BF6" t="inlineStr">
         <is>
           <t>-71.63</t>
         </is>
       </c>
-      <c r="BC6" t="inlineStr">
+      <c r="BG6" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD6" t="inlineStr">
+      <c r="BH6" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE6" t="inlineStr">
+      <c r="BI6" t="inlineStr">
         <is>
           <t>1247760.0</t>
         </is>
       </c>
-      <c r="BF6" t="n">
+      <c r="BJ6" t="n">
         <v>2222219.6</v>
       </c>
-      <c r="BG6" t="inlineStr">
+      <c r="BK6" t="inlineStr">
         <is>
           <t>2575084.7</t>
         </is>
       </c>
-      <c r="BH6" t="n">
+      <c r="BL6" t="n">
         <v>4689074.64</v>
       </c>
-      <c r="BI6" t="inlineStr">
+      <c r="BM6" t="inlineStr">
         <is>
           <t>-352865</t>
         </is>
       </c>
-      <c r="BJ6" t="inlineStr">
+      <c r="BN6" t="inlineStr">
         <is>
           <t>-408274.1522050498</t>
         </is>
       </c>
-      <c r="BK6" t="inlineStr">
+      <c r="BO6" t="inlineStr">
         <is>
           <t>-563995.8257181002</t>
         </is>
       </c>
-      <c r="BL6" t="inlineStr">
+      <c r="BP6" t="inlineStr">
         <is>
           <t>1247760.0</t>
         </is>
       </c>
-      <c r="BM6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN6" t="inlineStr">
+      <c r="BQ6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR6" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO6" t="inlineStr">
+      <c r="BS6" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP6" t="inlineStr">
+      <c r="BT6" t="inlineStr">
         <is>
           <t>1.23</t>
         </is>
       </c>
-      <c r="BQ6" t="inlineStr">
+      <c r="BU6" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR6" t="inlineStr">
+      <c r="BV6" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS6" t="inlineStr">
+      <c r="BW6" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT6" t="inlineStr">
+      <c r="BX6" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU6" t="inlineStr">
+      <c r="BY6" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV6" t="inlineStr">
+      <c r="BZ6" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW6" t="inlineStr">
+      <c r="CA6" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX6" t="inlineStr">
+      <c r="CB6" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY6" t="inlineStr">
+      <c r="CC6" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ6" t="inlineStr">
+      <c r="CD6" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA6" t="inlineStr">
+      <c r="CE6" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="CB6" t="inlineStr">
+      <c r="CF6" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC6" t="inlineStr">
+      <c r="CG6" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD6" t="inlineStr">
+      <c r="CH6" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE6" t="inlineStr">
+      <c r="CI6" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF6" t="inlineStr">
+      <c r="CJ6" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG6" t="inlineStr">
+      <c r="CK6" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH6" t="inlineStr">
+      <c r="CL6" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI6" t="inlineStr">
+      <c r="CM6" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ6" t="inlineStr">
+      <c r="CN6" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK6" t="inlineStr">
+      <c r="CO6" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL6" t="inlineStr">
+      <c r="CP6" t="inlineStr">
         <is>
           <t>65.9</t>
         </is>
       </c>
-      <c r="CM6" t="inlineStr">
+      <c r="CQ6" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CN6" t="inlineStr">
+      <c r="CR6" t="inlineStr">
         <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CO6" t="inlineStr">
+      <c r="CS6" t="inlineStr">
         <is>
           <t>65.8</t>
         </is>
       </c>
-      <c r="CP6" t="inlineStr">
+      <c r="CT6" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ6" t="inlineStr">
+      <c r="CU6" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR6" t="inlineStr">
+      <c r="CV6" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3358,325 +3478,345 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
+      <c r="AD7" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD7" t="inlineStr">
+      <c r="AE7" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE7" t="inlineStr">
+      <c r="AF7" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AG7" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
           <t>2025-12-08</t>
         </is>
       </c>
-      <c r="AH7" t="inlineStr">
+      <c r="AL7" t="inlineStr">
         <is>
           <t>5.78</t>
         </is>
       </c>
-      <c r="AI7" t="inlineStr">
+      <c r="AM7" t="inlineStr">
         <is>
           <t>0.00</t>
         </is>
       </c>
-      <c r="AJ7" t="inlineStr">
+      <c r="AN7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK7" t="inlineStr"/>
-      <c r="AL7" t="inlineStr">
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
+      <c r="AQ7" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN7" t="inlineStr">
+      <c r="AR7" t="inlineStr">
         <is>
           <t>45.45</t>
         </is>
       </c>
-      <c r="AO7" t="inlineStr">
+      <c r="AS7" t="inlineStr">
         <is>
           <t>24.24</t>
         </is>
       </c>
-      <c r="AP7" t="n">
+      <c r="AT7" t="n">
         <v>-0.03</v>
       </c>
-      <c r="AQ7" t="n">
+      <c r="AU7" t="n">
         <v>0.01</v>
       </c>
-      <c r="AR7" t="inlineStr">
+      <c r="AV7" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="AS7" t="inlineStr">
+      <c r="AW7" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AT7" t="inlineStr">
+      <c r="AX7" t="inlineStr">
         <is>
           <t>66.22</t>
         </is>
       </c>
-      <c r="AU7" t="n">
+      <c r="AY7" t="n">
         <v>66.22</v>
       </c>
-      <c r="AV7" t="n">
+      <c r="AZ7" t="n">
         <v>65.01000000000001</v>
       </c>
-      <c r="AW7" t="inlineStr">
+      <c r="BA7" t="inlineStr">
         <is>
           <t>64.55</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
+      <c r="BB7" t="inlineStr">
         <is>
           <t>-27.32</t>
         </is>
       </c>
-      <c r="AY7" t="n">
+      <c r="BC7" t="n">
         <v>0.31</v>
       </c>
-      <c r="AZ7" t="n">
+      <c r="BD7" t="n">
         <v>0.43</v>
       </c>
-      <c r="BA7" t="inlineStr">
+      <c r="BE7" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB7" t="inlineStr">
+      <c r="BF7" t="inlineStr">
         <is>
           <t>-69.15</t>
         </is>
       </c>
-      <c r="BC7" t="inlineStr">
+      <c r="BG7" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD7" t="inlineStr">
+      <c r="BH7" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE7" t="inlineStr">
+      <c r="BI7" t="inlineStr">
         <is>
           <t>1509985.0</t>
         </is>
       </c>
-      <c r="BF7" t="n">
+      <c r="BJ7" t="n">
         <v>2967914.4</v>
       </c>
-      <c r="BG7" t="inlineStr">
+      <c r="BK7" t="inlineStr">
         <is>
           <t>2717507.9</t>
         </is>
       </c>
-      <c r="BH7" t="n">
+      <c r="BL7" t="n">
         <v>4702861.12</v>
       </c>
-      <c r="BI7" t="inlineStr">
+      <c r="BM7" t="inlineStr">
         <is>
           <t>250406</t>
         </is>
       </c>
-      <c r="BJ7" t="inlineStr">
+      <c r="BN7" t="inlineStr">
         <is>
           <t>-379961.1206572224</t>
         </is>
       </c>
-      <c r="BK7" t="inlineStr">
+      <c r="BO7" t="inlineStr">
         <is>
           <t>-510394.4173020865</t>
         </is>
       </c>
-      <c r="BL7" t="inlineStr">
+      <c r="BP7" t="inlineStr">
         <is>
           <t>1509985.0</t>
         </is>
       </c>
-      <c r="BM7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN7" t="inlineStr">
+      <c r="BQ7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR7" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO7" t="inlineStr">
+      <c r="BS7" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP7" t="inlineStr">
+      <c r="BT7" t="inlineStr">
         <is>
           <t>1.85</t>
         </is>
       </c>
-      <c r="BQ7" t="inlineStr">
+      <c r="BU7" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR7" t="inlineStr">
+      <c r="BV7" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS7" t="inlineStr">
+      <c r="BW7" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT7" t="inlineStr">
+      <c r="BX7" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU7" t="inlineStr">
+      <c r="BY7" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV7" t="inlineStr">
+      <c r="BZ7" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW7" t="inlineStr">
+      <c r="CA7" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX7" t="inlineStr">
+      <c r="CB7" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY7" t="inlineStr">
+      <c r="CC7" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ7" t="inlineStr">
+      <c r="CD7" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA7" t="inlineStr">
+      <c r="CE7" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="CB7" t="inlineStr">
+      <c r="CF7" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC7" t="inlineStr">
+      <c r="CG7" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD7" t="inlineStr">
+      <c r="CH7" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE7" t="inlineStr">
+      <c r="CI7" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF7" t="inlineStr">
+      <c r="CJ7" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG7" t="inlineStr">
+      <c r="CK7" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH7" t="inlineStr">
+      <c r="CL7" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI7" t="inlineStr">
+      <c r="CM7" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ7" t="inlineStr">
+      <c r="CN7" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK7" t="inlineStr">
+      <c r="CO7" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL7" t="inlineStr">
+      <c r="CP7" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CM7" t="inlineStr">
+      <c r="CQ7" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CN7" t="inlineStr">
+      <c r="CR7" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CO7" t="inlineStr">
+      <c r="CS7" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="CP7" t="inlineStr">
+      <c r="CT7" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ7" t="inlineStr">
+      <c r="CU7" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR7" t="inlineStr">
+      <c r="CV7" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -3820,325 +3960,345 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
+      <c r="AD8" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD8" t="inlineStr">
+      <c r="AE8" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE8" t="inlineStr">
+      <c r="AF8" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG8" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
           <t>2025-12-05</t>
         </is>
       </c>
-      <c r="AH8" t="inlineStr">
+      <c r="AL8" t="inlineStr">
         <is>
           <t>3.74</t>
         </is>
       </c>
-      <c r="AI8" t="inlineStr">
+      <c r="AM8" t="inlineStr">
         <is>
           <t>0.61</t>
         </is>
       </c>
-      <c r="AJ8" t="inlineStr">
+      <c r="AN8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr">
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
+      <c r="AQ8" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN8" t="inlineStr">
+      <c r="AR8" t="inlineStr">
         <is>
           <t>27.27</t>
         </is>
       </c>
-      <c r="AO8" t="inlineStr">
+      <c r="AS8" t="inlineStr">
         <is>
           <t>30.3</t>
         </is>
       </c>
-      <c r="AP8" t="n">
+      <c r="AT8" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AQ8" t="n">
+      <c r="AU8" t="n">
         <v>0.13</v>
       </c>
-      <c r="AR8" t="inlineStr">
+      <c r="AV8" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="AS8" t="inlineStr">
+      <c r="AW8" t="inlineStr">
         <is>
           <t>0.72</t>
         </is>
       </c>
-      <c r="AT8" t="inlineStr">
+      <c r="AX8" t="inlineStr">
         <is>
           <t>66.24000000000001</t>
         </is>
       </c>
-      <c r="AU8" t="n">
+      <c r="AY8" t="n">
         <v>66.16</v>
       </c>
-      <c r="AV8" t="n">
+      <c r="AZ8" t="n">
         <v>64.97</v>
       </c>
-      <c r="AW8" t="inlineStr">
+      <c r="BA8" t="inlineStr">
         <is>
           <t>64.5</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
+      <c r="BB8" t="inlineStr">
         <is>
           <t>-26.34</t>
         </is>
       </c>
-      <c r="AY8" t="n">
+      <c r="BC8" t="n">
         <v>0.34</v>
       </c>
-      <c r="AZ8" t="n">
+      <c r="BD8" t="n">
         <v>0.46</v>
       </c>
-      <c r="BA8" t="inlineStr">
+      <c r="BE8" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB8" t="inlineStr">
+      <c r="BF8" t="inlineStr">
         <is>
           <t>-67.04</t>
         </is>
       </c>
-      <c r="BC8" t="inlineStr">
+      <c r="BG8" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD8" t="inlineStr">
+      <c r="BH8" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE8" t="inlineStr">
+      <c r="BI8" t="inlineStr">
         <is>
           <t>970968.0</t>
         </is>
       </c>
-      <c r="BF8" t="n">
+      <c r="BJ8" t="n">
         <v>2948729.4</v>
       </c>
-      <c r="BG8" t="inlineStr">
+      <c r="BK8" t="inlineStr">
         <is>
           <t>3100620.6</t>
         </is>
       </c>
-      <c r="BH8" t="n">
+      <c r="BL8" t="n">
         <v>4708957.14</v>
       </c>
-      <c r="BI8" t="inlineStr">
+      <c r="BM8" t="inlineStr">
         <is>
           <t>-151891</t>
         </is>
       </c>
-      <c r="BJ8" t="inlineStr">
+      <c r="BN8" t="inlineStr">
         <is>
           <t>-356245.9758127016</t>
         </is>
       </c>
-      <c r="BK8" t="inlineStr">
+      <c r="BO8" t="inlineStr">
         <is>
           <t>-443688.1403755629</t>
         </is>
       </c>
-      <c r="BL8" t="inlineStr">
+      <c r="BP8" t="inlineStr">
         <is>
           <t>970968.0</t>
         </is>
       </c>
-      <c r="BM8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN8" t="inlineStr">
+      <c r="BQ8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR8" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO8" t="inlineStr">
+      <c r="BS8" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP8" t="inlineStr">
+      <c r="BT8" t="inlineStr">
         <is>
           <t>1.54</t>
         </is>
       </c>
-      <c r="BQ8" t="inlineStr">
+      <c r="BU8" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR8" t="inlineStr">
+      <c r="BV8" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS8" t="inlineStr">
+      <c r="BW8" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT8" t="inlineStr">
+      <c r="BX8" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU8" t="inlineStr">
+      <c r="BY8" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV8" t="inlineStr">
+      <c r="BZ8" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW8" t="inlineStr">
+      <c r="CA8" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX8" t="inlineStr">
+      <c r="CB8" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY8" t="inlineStr">
+      <c r="CC8" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ8" t="inlineStr">
+      <c r="CD8" t="inlineStr">
         <is>
           <t>價-量縮</t>
         </is>
       </c>
-      <c r="CA8" t="inlineStr">
+      <c r="CE8" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="CB8" t="inlineStr">
+      <c r="CF8" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC8" t="inlineStr">
+      <c r="CG8" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD8" t="inlineStr">
+      <c r="CH8" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE8" t="inlineStr">
+      <c r="CI8" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF8" t="inlineStr">
+      <c r="CJ8" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG8" t="inlineStr">
+      <c r="CK8" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH8" t="inlineStr">
+      <c r="CL8" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI8" t="inlineStr">
+      <c r="CM8" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ8" t="inlineStr">
+      <c r="CN8" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK8" t="inlineStr">
+      <c r="CO8" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL8" t="inlineStr">
+      <c r="CP8" t="inlineStr">
         <is>
           <t>65.5</t>
         </is>
       </c>
-      <c r="CM8" t="inlineStr">
+      <c r="CQ8" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CN8" t="inlineStr">
+      <c r="CR8" t="inlineStr">
         <is>
           <t>65.5</t>
         </is>
       </c>
-      <c r="CO8" t="inlineStr">
+      <c r="CS8" t="inlineStr">
         <is>
           <t>66.0</t>
         </is>
       </c>
-      <c r="CP8" t="inlineStr">
+      <c r="CT8" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ8" t="inlineStr">
+      <c r="CU8" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR8" t="inlineStr">
+      <c r="CV8" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4282,325 +4442,345 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
+          <t>-0.06</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
+      <c r="AD9" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD9" t="inlineStr">
+      <c r="AE9" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE9" t="inlineStr">
+      <c r="AF9" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>-0.06</t>
-        </is>
-      </c>
       <c r="AG9" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
           <t>2025-12-04</t>
         </is>
       </c>
-      <c r="AH9" t="inlineStr">
+      <c r="AL9" t="inlineStr">
         <is>
           <t>22.55</t>
         </is>
       </c>
-      <c r="AI9" t="inlineStr">
+      <c r="AM9" t="inlineStr">
         <is>
           <t>-1.22</t>
         </is>
       </c>
-      <c r="AJ9" t="inlineStr">
+      <c r="AN9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK9" t="inlineStr"/>
-      <c r="AL9" t="inlineStr">
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
+      <c r="AQ9" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN9" t="inlineStr">
+      <c r="AR9" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO9" t="inlineStr">
+      <c r="AS9" t="inlineStr">
         <is>
           <t>54.55</t>
         </is>
       </c>
-      <c r="AP9" t="n">
+      <c r="AT9" t="n">
         <v>-0.99</v>
       </c>
-      <c r="AQ9" t="n">
+      <c r="AU9" t="n">
         <v>0.37</v>
       </c>
-      <c r="AR9" t="inlineStr">
+      <c r="AV9" t="inlineStr">
         <is>
           <t>1.83</t>
         </is>
       </c>
-      <c r="AS9" t="inlineStr">
+      <c r="AW9" t="inlineStr">
         <is>
           <t>0.73</t>
         </is>
       </c>
-      <c r="AT9" t="inlineStr">
+      <c r="AX9" t="inlineStr">
         <is>
           <t>66.36</t>
         </is>
       </c>
-      <c r="AU9" t="n">
+      <c r="AY9" t="n">
         <v>66.11</v>
       </c>
-      <c r="AV9" t="n">
+      <c r="AZ9" t="n">
         <v>64.92</v>
       </c>
-      <c r="AW9" t="inlineStr">
+      <c r="BA9" t="inlineStr">
         <is>
           <t>64.46</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="BB9" t="inlineStr">
         <is>
           <t>-20.99</t>
         </is>
       </c>
-      <c r="AY9" t="n">
+      <c r="BC9" t="n">
         <v>0.39</v>
       </c>
-      <c r="AZ9" t="n">
+      <c r="BD9" t="n">
         <v>0.49</v>
       </c>
-      <c r="BA9" t="inlineStr">
+      <c r="BE9" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB9" t="inlineStr">
+      <c r="BF9" t="inlineStr">
         <is>
           <t>-64.87</t>
         </is>
       </c>
-      <c r="BC9" t="inlineStr">
+      <c r="BG9" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD9" t="inlineStr">
+      <c r="BH9" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE9" t="inlineStr">
+      <c r="BI9" t="inlineStr">
         <is>
           <t>5880844.0</t>
         </is>
       </c>
-      <c r="BF9" t="n">
+      <c r="BJ9" t="n">
         <v>3131906.6</v>
       </c>
-      <c r="BG9" t="inlineStr">
+      <c r="BK9" t="inlineStr">
         <is>
           <t>3260313.7</t>
         </is>
       </c>
-      <c r="BH9" t="n">
+      <c r="BL9" t="n">
         <v>4743373.54</v>
       </c>
-      <c r="BI9" t="inlineStr">
+      <c r="BM9" t="inlineStr">
         <is>
           <t>-128407</t>
         </is>
       </c>
-      <c r="BJ9" t="inlineStr">
+      <c r="BN9" t="inlineStr">
         <is>
           <t>-340347.400437636</t>
         </is>
       </c>
-      <c r="BK9" t="inlineStr">
+      <c r="BO9" t="inlineStr">
         <is>
           <t>-274795.6326099746</t>
         </is>
       </c>
-      <c r="BL9" t="inlineStr">
+      <c r="BP9" t="inlineStr">
         <is>
           <t>5880844.0</t>
         </is>
       </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO9" t="inlineStr">
+      <c r="BS9" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP9" t="inlineStr">
+      <c r="BT9" t="inlineStr">
         <is>
           <t>1.08</t>
         </is>
       </c>
-      <c r="BQ9" t="inlineStr">
+      <c r="BU9" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR9" t="inlineStr">
+      <c r="BV9" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS9" t="inlineStr">
+      <c r="BW9" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT9" t="inlineStr">
+      <c r="BX9" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU9" t="inlineStr">
+      <c r="BY9" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV9" t="inlineStr">
+      <c r="BZ9" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW9" t="inlineStr">
+      <c r="CA9" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX9" t="inlineStr">
+      <c r="CB9" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY9" t="inlineStr">
+      <c r="CC9" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ9" t="inlineStr">
+      <c r="CD9" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA9" t="inlineStr">
+      <c r="CE9" t="inlineStr">
         <is>
           <t>1.29</t>
         </is>
       </c>
-      <c r="CB9" t="inlineStr">
+      <c r="CF9" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC9" t="inlineStr">
+      <c r="CG9" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD9" t="inlineStr">
+      <c r="CH9" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE9" t="inlineStr">
+      <c r="CI9" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF9" t="inlineStr">
+      <c r="CJ9" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG9" t="inlineStr">
+      <c r="CK9" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH9" t="inlineStr">
+      <c r="CL9" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI9" t="inlineStr">
+      <c r="CM9" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ9" t="inlineStr">
+      <c r="CN9" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK9" t="inlineStr">
+      <c r="CO9" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL9" t="inlineStr">
+      <c r="CP9" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CM9" t="inlineStr">
+      <c r="CQ9" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CN9" t="inlineStr">
+      <c r="CR9" t="inlineStr">
         <is>
           <t>65.6</t>
         </is>
       </c>
-      <c r="CO9" t="inlineStr">
+      <c r="CS9" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="CP9" t="inlineStr">
+      <c r="CT9" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ9" t="inlineStr">
+      <c r="CU9" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR9" t="inlineStr">
+      <c r="CV9" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -4744,325 +4924,345 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
+          <t>-0.02</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC10" t="inlineStr">
+      <c r="AD10" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD10" t="inlineStr">
+      <c r="AE10" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE10" t="inlineStr">
+      <c r="AF10" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>-0.02</t>
-        </is>
-      </c>
       <c r="AG10" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
           <t>2025-12-03</t>
         </is>
       </c>
-      <c r="AH10" t="inlineStr">
+      <c r="AL10" t="inlineStr">
         <is>
           <t>5.71</t>
         </is>
       </c>
-      <c r="AI10" t="inlineStr">
+      <c r="AM10" t="inlineStr">
         <is>
           <t>-0.60</t>
         </is>
       </c>
-      <c r="AJ10" t="inlineStr">
+      <c r="AN10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK10" t="inlineStr"/>
-      <c r="AL10" t="inlineStr">
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
+      <c r="AQ10" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN10" t="inlineStr">
+      <c r="AR10" t="inlineStr">
         <is>
           <t>63.64</t>
         </is>
       </c>
-      <c r="AO10" t="inlineStr">
+      <c r="AS10" t="inlineStr">
         <is>
           <t>74.55</t>
         </is>
       </c>
-      <c r="AP10" t="n">
+      <c r="AT10" t="n">
         <v>-0.21</v>
       </c>
-      <c r="AQ10" t="n">
+      <c r="AU10" t="n">
         <v>0.64</v>
       </c>
-      <c r="AR10" t="inlineStr">
+      <c r="AV10" t="inlineStr">
         <is>
           <t>1.89</t>
         </is>
       </c>
-      <c r="AS10" t="inlineStr">
+      <c r="AW10" t="inlineStr">
         <is>
           <t>0.77</t>
         </is>
       </c>
-      <c r="AT10" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>66.54</t>
         </is>
       </c>
-      <c r="AU10" t="n">
+      <c r="AY10" t="n">
         <v>66.12</v>
       </c>
-      <c r="AV10" t="n">
+      <c r="AZ10" t="n">
         <v>64.89</v>
       </c>
-      <c r="AW10" t="inlineStr">
+      <c r="BA10" t="inlineStr">
         <is>
           <t>64.4</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
+      <c r="BB10" t="inlineStr">
         <is>
           <t>-8.08</t>
         </is>
       </c>
-      <c r="AY10" t="n">
+      <c r="BC10" t="n">
         <v>0.47</v>
       </c>
-      <c r="AZ10" t="n">
+      <c r="BD10" t="n">
         <v>0.52</v>
       </c>
-      <c r="BA10" t="inlineStr">
+      <c r="BE10" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB10" t="inlineStr">
+      <c r="BF10" t="inlineStr">
         <is>
           <t>-63.03</t>
         </is>
       </c>
-      <c r="BC10" t="inlineStr">
+      <c r="BG10" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD10" t="inlineStr">
+      <c r="BH10" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE10" t="inlineStr">
+      <c r="BI10" t="inlineStr">
         <is>
           <t>1501541.0</t>
         </is>
       </c>
-      <c r="BF10" t="n">
+      <c r="BJ10" t="n">
         <v>2522940.8</v>
       </c>
-      <c r="BG10" t="inlineStr">
+      <c r="BK10" t="inlineStr">
         <is>
           <t>2938653.4</t>
         </is>
       </c>
-      <c r="BH10" t="n">
+      <c r="BL10" t="n">
         <v>4638644.26</v>
       </c>
-      <c r="BI10" t="inlineStr">
+      <c r="BM10" t="inlineStr">
         <is>
           <t>-415712</t>
         </is>
       </c>
-      <c r="BJ10" t="inlineStr">
+      <c r="BN10" t="inlineStr">
         <is>
           <t>-352265.903679029</t>
         </is>
       </c>
-      <c r="BK10" t="inlineStr">
+      <c r="BO10" t="inlineStr">
         <is>
           <t>-549764.6346373484</t>
         </is>
       </c>
-      <c r="BL10" t="inlineStr">
+      <c r="BP10" t="inlineStr">
         <is>
           <t>1501541.0</t>
         </is>
       </c>
-      <c r="BM10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN10" t="inlineStr">
+      <c r="BQ10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR10" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO10" t="inlineStr">
+      <c r="BS10" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP10" t="inlineStr">
+      <c r="BT10" t="inlineStr">
         <is>
           <t>2.15</t>
         </is>
       </c>
-      <c r="BQ10" t="inlineStr">
+      <c r="BU10" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR10" t="inlineStr">
+      <c r="BV10" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS10" t="inlineStr">
+      <c r="BW10" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT10" t="inlineStr">
+      <c r="BX10" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU10" t="inlineStr">
+      <c r="BY10" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV10" t="inlineStr">
+      <c r="BZ10" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW10" t="inlineStr">
+      <c r="CA10" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX10" t="inlineStr">
+      <c r="CB10" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY10" t="inlineStr">
+      <c r="CC10" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ10" t="inlineStr">
+      <c r="CD10" t="inlineStr">
         <is>
           <t>價-量增</t>
         </is>
       </c>
-      <c r="CA10" t="inlineStr">
+      <c r="CE10" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="CB10" t="inlineStr">
+      <c r="CF10" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC10" t="inlineStr">
+      <c r="CG10" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD10" t="inlineStr">
+      <c r="CH10" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE10" t="inlineStr">
+      <c r="CI10" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF10" t="inlineStr">
+      <c r="CJ10" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG10" t="inlineStr">
+      <c r="CK10" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH10" t="inlineStr">
+      <c r="CL10" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI10" t="inlineStr">
+      <c r="CM10" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ10" t="inlineStr">
+      <c r="CN10" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK10" t="inlineStr">
+      <c r="CO10" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL10" t="inlineStr">
+      <c r="CP10" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="CM10" t="inlineStr">
+      <c r="CQ10" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="CN10" t="inlineStr">
+      <c r="CR10" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CO10" t="inlineStr">
+      <c r="CS10" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CP10" t="inlineStr">
+      <c r="CT10" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ10" t="inlineStr">
+      <c r="CU10" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR10" t="inlineStr">
+      <c r="CV10" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5206,325 +5406,345 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
+          <t>0.01</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC11" t="inlineStr">
+      <c r="AD11" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD11" t="inlineStr">
+      <c r="AE11" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE11" t="inlineStr">
+      <c r="AF11" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>0.01</t>
-        </is>
-      </c>
       <c r="AG11" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
           <t>2025-12-02</t>
         </is>
       </c>
-      <c r="AH11" t="inlineStr">
+      <c r="AL11" t="inlineStr">
         <is>
           <t>18.95</t>
         </is>
       </c>
-      <c r="AI11" t="inlineStr">
+      <c r="AM11" t="inlineStr">
         <is>
           <t>1.06</t>
         </is>
       </c>
-      <c r="AJ11" t="inlineStr">
+      <c r="AN11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK11" t="inlineStr"/>
-      <c r="AL11" t="inlineStr">
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
+      <c r="AQ11" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN11" t="inlineStr">
+      <c r="AR11" t="inlineStr">
         <is>
           <t>100.0</t>
         </is>
       </c>
-      <c r="AO11" t="inlineStr">
+      <c r="AS11" t="inlineStr">
         <is>
           <t>83.64</t>
         </is>
       </c>
-      <c r="AP11" t="n">
+      <c r="AT11" t="n">
         <v>0.3</v>
       </c>
-      <c r="AQ11" t="n">
+      <c r="AU11" t="n">
         <v>0.78</v>
       </c>
-      <c r="AR11" t="inlineStr">
+      <c r="AV11" t="inlineStr">
         <is>
           <t>1.91</t>
         </is>
       </c>
-      <c r="AS11" t="inlineStr">
+      <c r="AW11" t="inlineStr">
         <is>
           <t>0.81</t>
         </is>
       </c>
-      <c r="AT11" t="inlineStr">
+      <c r="AX11" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="AU11" t="n">
+      <c r="AY11" t="n">
         <v>66.09</v>
       </c>
-      <c r="AV11" t="n">
+      <c r="AZ11" t="n">
         <v>64.84999999999999</v>
       </c>
-      <c r="AW11" t="inlineStr">
+      <c r="BA11" t="inlineStr">
         <is>
           <t>64.33</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
+      <c r="BB11" t="inlineStr">
         <is>
           <t>-3.69</t>
         </is>
       </c>
-      <c r="AY11" t="n">
+      <c r="BC11" t="n">
         <v>0.51</v>
       </c>
-      <c r="AZ11" t="n">
+      <c r="BD11" t="n">
         <v>0.53</v>
       </c>
-      <c r="BA11" t="inlineStr">
+      <c r="BE11" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB11" t="inlineStr">
+      <c r="BF11" t="inlineStr">
         <is>
           <t>-62.28</t>
         </is>
       </c>
-      <c r="BC11" t="inlineStr">
+      <c r="BG11" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD11" t="inlineStr">
+      <c r="BH11" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE11" t="inlineStr">
+      <c r="BI11" t="inlineStr">
         <is>
           <t>4976234.0</t>
         </is>
       </c>
-      <c r="BF11" t="n">
+      <c r="BJ11" t="n">
         <v>2927949.8</v>
       </c>
-      <c r="BG11" t="inlineStr">
+      <c r="BK11" t="inlineStr">
         <is>
           <t>3113330.9</t>
         </is>
       </c>
-      <c r="BH11" t="n">
+      <c r="BL11" t="n">
         <v>4657185.68</v>
       </c>
-      <c r="BI11" t="inlineStr">
+      <c r="BM11" t="inlineStr">
         <is>
           <t>-185381</t>
         </is>
       </c>
-      <c r="BJ11" t="inlineStr">
+      <c r="BN11" t="inlineStr">
         <is>
           <t>-316357.043504789</t>
         </is>
       </c>
-      <c r="BK11" t="inlineStr">
+      <c r="BO11" t="inlineStr">
         <is>
           <t>-453732.0077251205</t>
         </is>
       </c>
-      <c r="BL11" t="inlineStr">
+      <c r="BP11" t="inlineStr">
         <is>
           <t>4976234.0</t>
         </is>
       </c>
-      <c r="BM11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN11" t="inlineStr">
+      <c r="BQ11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR11" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO11" t="inlineStr">
+      <c r="BS11" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP11" t="inlineStr">
+      <c r="BT11" t="inlineStr">
         <is>
           <t>2.77</t>
         </is>
       </c>
-      <c r="BQ11" t="inlineStr">
+      <c r="BU11" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR11" t="inlineStr">
+      <c r="BV11" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS11" t="inlineStr">
+      <c r="BW11" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT11" t="inlineStr">
+      <c r="BX11" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU11" t="inlineStr">
+      <c r="BY11" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV11" t="inlineStr">
+      <c r="BZ11" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW11" t="inlineStr">
+      <c r="CA11" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX11" t="inlineStr">
+      <c r="CB11" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY11" t="inlineStr">
+      <c r="CC11" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;建議關注買點&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;2&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ11" t="inlineStr">
+      <c r="CD11" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA11" t="inlineStr">
+      <c r="CE11" t="inlineStr">
         <is>
           <t>1.31</t>
         </is>
       </c>
-      <c r="CB11" t="inlineStr">
+      <c r="CF11" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC11" t="inlineStr">
+      <c r="CG11" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD11" t="inlineStr">
+      <c r="CH11" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE11" t="inlineStr">
+      <c r="CI11" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF11" t="inlineStr">
+      <c r="CJ11" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG11" t="inlineStr">
+      <c r="CK11" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH11" t="inlineStr">
+      <c r="CL11" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI11" t="inlineStr">
+      <c r="CM11" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ11" t="inlineStr">
+      <c r="CN11" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK11" t="inlineStr">
+      <c r="CO11" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL11" t="inlineStr">
+      <c r="CP11" t="inlineStr">
         <is>
           <t>66.2</t>
         </is>
       </c>
-      <c r="CM11" t="inlineStr">
+      <c r="CQ11" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="CN11" t="inlineStr">
+      <c r="CR11" t="inlineStr">
         <is>
           <t>66.1</t>
         </is>
       </c>
-      <c r="CO11" t="inlineStr">
+      <c r="CS11" t="inlineStr">
         <is>
           <t>66.8</t>
         </is>
       </c>
-      <c r="CP11" t="inlineStr">
+      <c r="CT11" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ11" t="inlineStr">
+      <c r="CU11" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR11" t="inlineStr">
+      <c r="CV11" t="inlineStr">
         <is>
           <t>False</t>
         </is>
@@ -5668,325 +5888,345 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
+          <t>-0.03</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
           <t>2025/10/21</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
+      <c r="AD12" t="inlineStr">
         <is>
           <t>64.1</t>
         </is>
       </c>
-      <c r="AD12" t="inlineStr">
+      <c r="AE12" t="inlineStr">
         <is>
           <t>2025/07/02</t>
         </is>
       </c>
-      <c r="AE12" t="inlineStr">
+      <c r="AF12" t="inlineStr">
         <is>
           <t>59.9</t>
         </is>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
       <c r="AG12" t="inlineStr">
         <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>66.6</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
           <t>2025-12-01</t>
         </is>
       </c>
-      <c r="AH12" t="inlineStr">
+      <c r="AL12" t="inlineStr">
         <is>
           <t>5.39</t>
         </is>
       </c>
-      <c r="AI12" t="inlineStr">
+      <c r="AM12" t="inlineStr">
         <is>
           <t>-0.45</t>
         </is>
       </c>
-      <c r="AJ12" t="inlineStr">
+      <c r="AN12" t="inlineStr">
         <is>
           <t>False</t>
         </is>
       </c>
-      <c r="AK12" t="inlineStr"/>
-      <c r="AL12" t="inlineStr">
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
+      <c r="AQ12" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AN12" t="inlineStr">
+      <c r="AR12" t="inlineStr">
         <is>
           <t>60.0</t>
         </is>
       </c>
-      <c r="AO12" t="inlineStr">
+      <c r="AS12" t="inlineStr">
         <is>
           <t>80.61</t>
         </is>
       </c>
-      <c r="AP12" t="n">
+      <c r="AT12" t="n">
         <v>-0.36</v>
       </c>
-      <c r="AQ12" t="n">
+      <c r="AU12" t="n">
         <v>0.73</v>
       </c>
-      <c r="AR12" t="inlineStr">
+      <c r="AV12" t="inlineStr">
         <is>
           <t>1.97</t>
         </is>
       </c>
-      <c r="AS12" t="inlineStr">
+      <c r="AW12" t="inlineStr">
         <is>
           <t>0.82</t>
         </is>
       </c>
-      <c r="AT12" t="inlineStr">
+      <c r="AX12" t="inlineStr">
         <is>
           <t>66.53999999999999</t>
         </is>
       </c>
-      <c r="AU12" t="n">
+      <c r="AY12" t="n">
         <v>66.05</v>
       </c>
-      <c r="AV12" t="n">
+      <c r="AZ12" t="n">
         <v>64.78</v>
       </c>
-      <c r="AW12" t="inlineStr">
+      <c r="BA12" t="inlineStr">
         <is>
           <t>64.26</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
+      <c r="BB12" t="inlineStr">
         <is>
           <t>-5.79</t>
         </is>
       </c>
-      <c r="AY12" t="n">
+      <c r="BC12" t="n">
         <v>0.5</v>
       </c>
-      <c r="AZ12" t="n">
+      <c r="BD12" t="n">
         <v>0.53</v>
       </c>
-      <c r="BA12" t="inlineStr">
+      <c r="BE12" t="inlineStr">
         <is>
           <t>1.39</t>
         </is>
       </c>
-      <c r="BB12" t="inlineStr">
+      <c r="BF12" t="inlineStr">
         <is>
           <t>-61.93</t>
         </is>
       </c>
-      <c r="BC12" t="inlineStr">
+      <c r="BG12" t="inlineStr">
         <is>
           <t>2025/11/26</t>
         </is>
       </c>
-      <c r="BD12" t="inlineStr">
+      <c r="BH12" t="inlineStr">
         <is>
           <t>7659946.919241574</t>
         </is>
       </c>
-      <c r="BE12" t="inlineStr">
+      <c r="BI12" t="inlineStr">
         <is>
           <t>1414060.0</t>
         </is>
       </c>
-      <c r="BF12" t="n">
+      <c r="BJ12" t="n">
         <v>2467101.4</v>
       </c>
-      <c r="BG12" t="inlineStr">
+      <c r="BK12" t="inlineStr">
         <is>
           <t>2976246.7</t>
         </is>
       </c>
-      <c r="BH12" t="n">
+      <c r="BL12" t="n">
         <v>4582639.88</v>
       </c>
-      <c r="BI12" t="inlineStr">
+      <c r="BM12" t="inlineStr">
         <is>
           <t>-509145</t>
         </is>
       </c>
-      <c r="BJ12" t="inlineStr">
+      <c r="BN12" t="inlineStr">
         <is>
           <t>-291379.7772829105</t>
         </is>
       </c>
-      <c r="BK12" t="inlineStr">
+      <c r="BO12" t="inlineStr">
         <is>
           <t>-672626.3618603265</t>
         </is>
       </c>
-      <c r="BL12" t="inlineStr">
+      <c r="BP12" t="inlineStr">
         <is>
           <t>1414060.0</t>
         </is>
       </c>
-      <c r="BM12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BN12" t="inlineStr">
+      <c r="BQ12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BR12" t="inlineStr">
         <is>
           <t>65.0</t>
         </is>
       </c>
-      <c r="BO12" t="inlineStr">
+      <c r="BS12" t="inlineStr">
         <is>
           <t>2025/10/29</t>
         </is>
       </c>
-      <c r="BP12" t="inlineStr">
+      <c r="BT12" t="inlineStr">
         <is>
           <t>2.00</t>
         </is>
       </c>
-      <c r="BQ12" t="inlineStr">
+      <c r="BU12" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BR12" t="inlineStr">
+      <c r="BV12" t="inlineStr">
         <is>
           <t>敦吉</t>
         </is>
       </c>
-      <c r="BS12" t="inlineStr">
+      <c r="BW12" t="inlineStr">
         <is>
           <t>其他電子業</t>
         </is>
       </c>
-      <c r="BT12" t="inlineStr">
+      <c r="BX12" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BU12" t="inlineStr">
+      <c r="BY12" t="inlineStr">
         <is>
           <t>0.52</t>
         </is>
       </c>
-      <c r="BV12" t="inlineStr">
+      <c r="BZ12" t="inlineStr">
         <is>
           <t>-6.762392378742623</t>
         </is>
       </c>
-      <c r="BW12" t="inlineStr">
+      <c r="CA12" t="inlineStr">
         <is>
           <t>-2.51519879485662</t>
         </is>
       </c>
-      <c r="BX12" t="inlineStr">
+      <c r="CB12" t="inlineStr">
         <is>
           <t>-8.12262189377373</t>
         </is>
       </c>
-      <c r="BY12" t="inlineStr">
+      <c r="CC12" t="inlineStr">
         <is>
           <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
-      <c r="BZ12" t="inlineStr">
+      <c r="CD12" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="CA12" t="inlineStr">
+      <c r="CE12" t="inlineStr">
         <is>
           <t>1.30</t>
         </is>
       </c>
-      <c r="CB12" t="inlineStr">
+      <c r="CF12" t="inlineStr">
         <is>
           <t>6.04</t>
         </is>
       </c>
-      <c r="CC12" t="inlineStr">
+      <c r="CG12" t="inlineStr">
         <is>
           <t>11.84</t>
         </is>
       </c>
-      <c r="CD12" t="inlineStr">
+      <c r="CH12" t="inlineStr">
         <is>
           <t>12.04</t>
         </is>
       </c>
-      <c r="CE12" t="inlineStr">
+      <c r="CI12" t="inlineStr">
         <is>
           <t>31.81%</t>
         </is>
       </c>
-      <c r="CF12" t="inlineStr">
+      <c r="CJ12" t="inlineStr">
         <is>
           <t>15.81%</t>
         </is>
       </c>
-      <c r="CG12" t="inlineStr">
+      <c r="CK12" t="inlineStr">
         <is>
           <t>41.03</t>
         </is>
       </c>
-      <c r="CH12" t="inlineStr">
+      <c r="CL12" t="inlineStr">
         <is>
           <t>6990</t>
         </is>
       </c>
-      <c r="CI12" t="inlineStr">
+      <c r="CM12" t="inlineStr">
         <is>
           <t>模具成型組裝等38.02%、其他22.96%、安規及電磁相容驗證14.45%、車用設備6.43%、繼電器5.90%、Home MCH-家電用品3.84%、醫療器材3.64%、ODD-光儲存裝置2.54%、工業控制2.22% (2024年)</t>
         </is>
       </c>
-      <c r="CJ12" t="inlineStr">
+      <c r="CN12" t="inlineStr">
         <is>
           <t>敦吉-其他電子業-上市</t>
         </is>
       </c>
-      <c r="CK12" t="inlineStr">
+      <c r="CO12" t="inlineStr">
         <is>
           <t>其他電子業平上市</t>
         </is>
       </c>
-      <c r="CL12" t="inlineStr">
+      <c r="CP12" t="inlineStr">
         <is>
           <t>66.4</t>
         </is>
       </c>
-      <c r="CM12" t="inlineStr">
+      <c r="CQ12" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="CN12" t="inlineStr">
+      <c r="CR12" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="CO12" t="inlineStr">
+      <c r="CS12" t="inlineStr">
         <is>
           <t>66.3</t>
         </is>
       </c>
-      <c r="CP12" t="inlineStr">
+      <c r="CT12" t="inlineStr">
         <is>
           <t>51.01</t>
         </is>
       </c>
-      <c r="CQ12" t="inlineStr">
+      <c r="CU12" t="inlineStr">
         <is>
           <t>** 半導體 - 基板、IC通路** 電腦及週邊設備 - 面板、散熱片、風扇馬達、散熱模組、光學鏡片、鏡頭、連接線、金屬、塑膠模具、其他電腦及週邊設備之零組件** 平面顯示器 - 驅動IC、其他零組件、面板** 觸控面板 - 控制IC、觸控面板** 通信網路 - 網路IC、主/被動元件、塑膠/金屬機殼、線材、其他零組件** 被動元件 - 電感器材料(如鐵氧體、導電漿墨)、濾波器、振盪器** 連接器 - 連接器設計、組裝及製造** 電機機械 - 電控元件、機械設備之沖壓零組件、輸送機械及零配件、冷凍空調設備及零件** 其他 - 其他電子產品及電子服務產業、特殊照明業、農業科技業** 汽車 - 車燈、其他** 雲端運算 - 電力設備** 運動科技 - 裝置/器材顯示器、裝置/器材零組件、感測裝置** 體驗科技 - 光學元件/模組、微型顯示器/光機引擎(Light Engine)** LED照明產業 - 生產製程、檢測設備及原物料** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 能源元件 - 電池模組** 智慧電網 - 高/低壓輸電設施、配電管理設施** 醫療器材 - 塑化材料</t>
         </is>
       </c>
-      <c r="CR12" t="inlineStr">
+      <c r="CV12" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/裝置_器材顯示器.xlsx
+++ b/Result/checksun_type/裝置_器材顯示器.xlsx
@@ -943,12 +943,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.6</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>15.593</t>
+          <t>82.984</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -958,7 +958,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>28.13</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-2.10</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -1068,7 +1068,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.01</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -1113,17 +1113,17 @@
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>2025-12-15</t>
+          <t>2025-12-16</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>3.95</t>
+          <t>21.01</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
@@ -1134,33 +1134,33 @@
       <c r="AO2" t="inlineStr"/>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>55.56</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>67.0</t>
+          <t>45.79</t>
         </is>
       </c>
       <c r="AT2" t="n">
-        <v>-0.18</v>
+        <v>-1.51</v>
       </c>
       <c r="AU2" t="n">
-        <v>0.08</v>
+        <v>-0.08</v>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
@@ -1170,30 +1170,30 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>66.32000000000001</t>
+          <t>66.20000000000002</t>
         </is>
       </c>
       <c r="AY2" t="n">
-        <v>66.27</v>
+        <v>66.25</v>
       </c>
       <c r="AZ2" t="n">
-        <v>65.28</v>
+        <v>65.31</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>64.69</t>
+          <t>64.72</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-21.94</t>
+          <t>-49.31</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>0.25</v>
+        <v>0.14</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.32</v>
+        <v>0.28</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1202,7 +1202,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-77.16</t>
+          <t>-79.66</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
@@ -1212,43 +1212,43 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>7659946.919241574</t>
+          <t>7660581.85203366</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>1032217.0</t>
+          <t>5408436.0</t>
         </is>
       </c>
       <c r="BJ2" t="n">
-        <v>3129239.4</v>
+        <v>3961374.6</v>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>3048576.9</t>
+          <t>3091797.1</t>
         </is>
       </c>
       <c r="BL2" t="n">
-        <v>4778355.32</v>
+        <v>4859726.04</v>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>80662</t>
+          <t>869577</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-305844.3707094667</t>
+          <t>-267938.0865940613</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-283364.1678135758</t>
+          <t>-59453.52395933168</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>1032217.0</t>
+          <t>5408436.0</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
@@ -1268,7 +1268,7 @@
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.31</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1313,22 +1313,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>1.30</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>6.04</t>
+          <t>6.13</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>12.04</t>
+          <t>11.85</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
@@ -1353,12 +1353,12 @@
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>41.03</t>
+          <t>40.95</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>6990</t>
+          <t>6885</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
@@ -1378,22 +1378,22 @@
       </c>
       <c r="CP2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CQ2" t="inlineStr">
         <is>
-          <t>66.3</t>
+          <t>65.8</t>
         </is>
       </c>
       <c r="CR2" t="inlineStr">
         <is>
-          <t>66.1</t>
+          <t>64.5</t>
         </is>
       </c>
       <c r="CS2" t="inlineStr">
         <is>
-          <t>66.2</t>
+          <t>65.2</t>
         </is>
       </c>
       <c r="CT2" t="inlineStr">
@@ -1425,12 +1425,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>-0.6</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>48.667</t>
+          <t>15.593</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1440,172 +1440,172 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
+          <t>66.2</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>-1.53</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>40.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-11-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-11-28 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-10-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-11-21 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>66.7</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>-0.6</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4.47</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>40.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-11-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-11-28 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-10-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-11-21 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>66.7</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>65.7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-0.60</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025/08/15</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>64.6</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>-0.01</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2025/10/21</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>64.1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2025/07/02</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>59.9</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2025/11/28</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
         <is>
           <t>66.6</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>2025/11/21</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>65.7</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2025-12-15</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>3.95</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
         <is>
           <t>0.00</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025/08/15</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>64.6</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>0.02</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>2025/10/21</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>64.1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>2025/07/02</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>59.9</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2025/11/28</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
- 